--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D200657-5FB3-444F-9B0E-E17801608C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D06A440-B62E-43A7-9129-9FFF7E6EA440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="130">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -404,6 +404,15 @@
   </si>
   <si>
     <t>Raheem Store EME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thoker Risen </t>
+  </si>
+  <si>
+    <t>Raheem Store J-Height</t>
+  </si>
+  <si>
+    <t>Al Rehmat</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1776,6 +1785,16 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4158,22 +4177,22 @@
       <c r="B25" s="47">
         <v>21</v>
       </c>
-      <c r="C25" s="145" t="s">
+      <c r="C25" s="184" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="146"/>
-      <c r="E25" s="147"/>
-      <c r="F25" s="148"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="147"/>
-      <c r="I25" s="150"/>
-      <c r="J25" s="149">
+      <c r="D25" s="185"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="187"/>
+      <c r="G25" s="188"/>
+      <c r="H25" s="186"/>
+      <c r="I25" s="189"/>
+      <c r="J25" s="188">
         <v>40</v>
       </c>
-      <c r="K25" s="147">
+      <c r="K25" s="186">
         <v>80</v>
       </c>
-      <c r="L25" s="148">
+      <c r="L25" s="187">
         <v>80</v>
       </c>
       <c r="M25" s="48">
@@ -4236,26 +4255,26 @@
       <c r="B26" s="47">
         <v>22</v>
       </c>
-      <c r="C26" s="145" t="s">
+      <c r="C26" s="184" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="146"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="149">
+      <c r="D26" s="185"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="187"/>
+      <c r="G26" s="188">
         <v>80</v>
       </c>
-      <c r="H26" s="147">
+      <c r="H26" s="186">
         <v>80</v>
       </c>
-      <c r="I26" s="150"/>
-      <c r="J26" s="149">
+      <c r="I26" s="189"/>
+      <c r="J26" s="188">
         <v>80</v>
       </c>
-      <c r="K26" s="147">
+      <c r="K26" s="186">
         <v>80</v>
       </c>
-      <c r="L26" s="148">
+      <c r="L26" s="187">
         <v>80</v>
       </c>
       <c r="M26" s="48">
@@ -4318,22 +4337,22 @@
       <c r="B27" s="47">
         <v>23</v>
       </c>
-      <c r="C27" s="145" t="s">
+      <c r="C27" s="184" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="146"/>
-      <c r="E27" s="147"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="149"/>
-      <c r="H27" s="147"/>
-      <c r="I27" s="150"/>
-      <c r="J27" s="149">
+      <c r="D27" s="185"/>
+      <c r="E27" s="186"/>
+      <c r="F27" s="187"/>
+      <c r="G27" s="188"/>
+      <c r="H27" s="186"/>
+      <c r="I27" s="189"/>
+      <c r="J27" s="188">
         <v>40</v>
       </c>
-      <c r="K27" s="147">
+      <c r="K27" s="186">
         <v>120</v>
       </c>
-      <c r="L27" s="148">
+      <c r="L27" s="187">
         <v>160</v>
       </c>
       <c r="M27" s="48">
@@ -4394,19 +4413,31 @@
       <c r="B28" s="47">
         <v>24</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="75"/>
-      <c r="L28" s="76"/>
+      <c r="C28" s="145" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="146"/>
+      <c r="E28" s="147"/>
+      <c r="F28" s="148"/>
+      <c r="G28" s="149">
+        <v>40</v>
+      </c>
+      <c r="H28" s="147">
+        <v>40</v>
+      </c>
+      <c r="I28" s="150"/>
+      <c r="J28" s="149">
+        <v>40</v>
+      </c>
+      <c r="K28" s="147">
+        <v>40</v>
+      </c>
+      <c r="L28" s="148">
+        <v>40</v>
+      </c>
       <c r="M28" s="48">
         <f t="shared" ref="M28:M60" si="52">SUM(D28:L28)/40</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N28" s="39">
         <f t="shared" si="18"/>
@@ -4418,11 +4449,11 @@
       </c>
       <c r="P28" s="73">
         <f t="shared" ref="P28:P60" si="53">SUM(G28:I28)/20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" ref="Q28:Q60" si="54">SUM(J28:L28)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R28" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4462,19 +4493,31 @@
       <c r="B29" s="47">
         <v>25</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="75"/>
-      <c r="L29" s="76"/>
+      <c r="C29" s="145" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="146"/>
+      <c r="E29" s="147"/>
+      <c r="F29" s="148"/>
+      <c r="G29" s="149">
+        <v>80</v>
+      </c>
+      <c r="H29" s="147">
+        <v>120</v>
+      </c>
+      <c r="I29" s="150"/>
+      <c r="J29" s="149">
+        <v>120</v>
+      </c>
+      <c r="K29" s="147">
+        <v>200</v>
+      </c>
+      <c r="L29" s="148">
+        <v>360</v>
+      </c>
       <c r="M29" s="48">
         <f t="shared" ref="M29" si="60">SUM(D29:L29)/40</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N29" s="39">
         <f t="shared" si="18"/>
@@ -4486,11 +4529,11 @@
       </c>
       <c r="P29" s="73">
         <f t="shared" ref="P29" si="61">SUM(G29:I29)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q29" s="40">
         <f t="shared" ref="Q29" si="62">SUM(J29:L29)/20</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R29" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4530,19 +4573,27 @@
       <c r="B30" s="47">
         <v>26</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="76"/>
+      <c r="C30" s="145" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="146"/>
+      <c r="E30" s="147"/>
+      <c r="F30" s="148"/>
+      <c r="G30" s="149"/>
+      <c r="H30" s="147"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="149">
+        <v>40</v>
+      </c>
+      <c r="K30" s="147">
+        <v>40</v>
+      </c>
+      <c r="L30" s="148">
+        <v>80</v>
+      </c>
       <c r="M30" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N30" s="39">
         <f t="shared" si="18"/>
@@ -4558,7 +4609,7 @@
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R30" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4598,19 +4649,33 @@
       <c r="B31" s="47">
         <v>27</v>
       </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="76"/>
+      <c r="C31" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="146">
+        <v>200</v>
+      </c>
+      <c r="E31" s="147"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="149">
+        <v>200</v>
+      </c>
+      <c r="H31" s="147">
+        <v>200</v>
+      </c>
+      <c r="I31" s="150"/>
+      <c r="J31" s="149">
+        <v>200</v>
+      </c>
+      <c r="K31" s="147">
+        <v>200</v>
+      </c>
+      <c r="L31" s="148">
+        <v>200</v>
+      </c>
       <c r="M31" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N31" s="39">
         <f t="shared" si="18"/>
@@ -4622,11 +4687,11 @@
       </c>
       <c r="P31" s="73">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q31" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R31" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4666,19 +4731,27 @@
       <c r="B32" s="47">
         <v>28</v>
       </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="76"/>
+      <c r="C32" s="145" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="146"/>
+      <c r="E32" s="147"/>
+      <c r="F32" s="148"/>
+      <c r="G32" s="149"/>
+      <c r="H32" s="147"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="149">
+        <v>120</v>
+      </c>
+      <c r="K32" s="147">
+        <v>120</v>
+      </c>
+      <c r="L32" s="148">
+        <v>120</v>
+      </c>
       <c r="M32" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N32" s="39">
         <f t="shared" si="18"/>
@@ -4694,7 +4767,7 @@
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R32" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4734,19 +4807,27 @@
       <c r="B33" s="47">
         <v>29</v>
       </c>
-      <c r="C33" s="57"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="76"/>
+      <c r="C33" s="145" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="146"/>
+      <c r="E33" s="147"/>
+      <c r="F33" s="148"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="147"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="149">
+        <v>80</v>
+      </c>
+      <c r="K33" s="147">
+        <v>40</v>
+      </c>
+      <c r="L33" s="148">
+        <v>40</v>
+      </c>
       <c r="M33" s="48">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N33" s="39">
         <f t="shared" si="18"/>
@@ -4762,7 +4843,7 @@
       </c>
       <c r="Q33" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R33" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11201,7 +11282,7 @@
       <c r="C132" s="176"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E132" s="88">
         <f t="shared" si="104"/>
@@ -11213,11 +11294,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>958</v>
+        <v>1278</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>957</v>
+        <v>1317</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11225,19 +11306,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>1479</v>
+        <v>2079</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>1318</v>
+        <v>1958</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>1718</v>
+        <v>2558</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>160.75</v>
+        <v>234.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11249,11 +11330,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>95.75</v>
+        <v>129.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>225.75</v>
+        <v>329.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11562,7 +11643,7 @@
       <c r="C137" s="153"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E137" s="89">
         <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
@@ -11574,11 +11655,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>958</v>
+        <v>1278</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>957</v>
+        <v>1317</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -11586,19 +11667,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>1479</v>
+        <v>2079</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>1318</v>
+        <v>1958</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>1718</v>
+        <v>2558</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>160.75</v>
+        <v>234.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11610,11 +11691,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>195.5</v>
+        <v>263.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>457.5</v>
+        <v>665.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12657,7 +12738,7 @@
         <v>5</v>
       </c>
       <c r="K16" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L16" s="134"/>
     </row>
@@ -12673,7 +12754,7 @@
         <v>4</v>
       </c>
       <c r="K17" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -12688,7 +12769,7 @@
         <v>9</v>
       </c>
       <c r="K18" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12703,7 +12784,7 @@
         <v>6</v>
       </c>
       <c r="K19" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12718,7 +12799,7 @@
         <v>30</v>
       </c>
       <c r="K20" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -12729,7 +12810,7 @@
         <v>22</v>
       </c>
       <c r="K21" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D06A440-B62E-43A7-9129-9FFF7E6EA440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202AFD12-E7FA-4866-A718-ADAED16F4AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="132">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -355,9 +355,6 @@
     <t xml:space="preserve">Rainbow Shadra </t>
   </si>
   <si>
-    <t xml:space="preserve">On the way </t>
-  </si>
-  <si>
     <t>Manawan (Risen)</t>
   </si>
   <si>
@@ -413,6 +410,15 @@
   </si>
   <si>
     <t>Al Rehmat</t>
+  </si>
+  <si>
+    <t>Jalal Sons Askari 10</t>
+  </si>
+  <si>
+    <t>Naimat Khana</t>
+  </si>
+  <si>
+    <t>Risen Manawan</t>
   </si>
 </sst>
 </file>
@@ -517,7 +523,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -584,6 +590,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="58">
     <border>
@@ -1307,7 +1319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1687,7 +1699,46 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1729,42 +1780,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1785,16 +1800,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2331,14 +2336,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="165">
+      <c r="B1" s="153">
         <f ca="1">TODAY()</f>
-        <v>46213</v>
-      </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
+        <v>46214</v>
+      </c>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2360,10 +2365,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="154" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2396,13 +2401,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="154"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="157" t="s">
+      <c r="M2" s="167"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="158"/>
+      <c r="Q2" s="171"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2421,8 +2426,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="162"/>
-      <c r="B3" s="167"/>
+      <c r="A3" s="175"/>
+      <c r="B3" s="155"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2453,29 +2458,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="159" t="s">
+      <c r="M3" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="161"/>
+      <c r="N3" s="173"/>
+      <c r="O3" s="174"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="169" t="s">
+      <c r="R3" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="170"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="171"/>
-      <c r="V3" s="172" t="s">
+      <c r="S3" s="158"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="159"/>
+      <c r="V3" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="173"/>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="174"/>
+      <c r="W3" s="161"/>
+      <c r="X3" s="161"/>
+      <c r="Y3" s="162"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="162"/>
-      <c r="B4" s="168"/>
+      <c r="A4" s="175"/>
+      <c r="B4" s="156"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3620,7 +3625,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D18" s="74"/>
       <c r="E18" s="75"/>
@@ -3702,7 +3707,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D19" s="74"/>
       <c r="E19" s="75"/>
@@ -3858,7 +3863,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" s="74"/>
       <c r="E21" s="75"/>
@@ -4018,7 +4023,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
@@ -4177,22 +4182,22 @@
       <c r="B25" s="47">
         <v>21</v>
       </c>
-      <c r="C25" s="184" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="185"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="187"/>
-      <c r="G25" s="188"/>
-      <c r="H25" s="186"/>
-      <c r="I25" s="189"/>
-      <c r="J25" s="188">
+      <c r="C25" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="74"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="50">
         <v>40</v>
       </c>
-      <c r="K25" s="186">
+      <c r="K25" s="75">
         <v>80</v>
       </c>
-      <c r="L25" s="187">
+      <c r="L25" s="76">
         <v>80</v>
       </c>
       <c r="M25" s="48">
@@ -4255,26 +4260,26 @@
       <c r="B26" s="47">
         <v>22</v>
       </c>
-      <c r="C26" s="184" t="s">
+      <c r="C26" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="185"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="187"/>
-      <c r="G26" s="188">
+      <c r="D26" s="74"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="50">
         <v>80</v>
       </c>
-      <c r="H26" s="186">
+      <c r="H26" s="75">
         <v>80</v>
       </c>
-      <c r="I26" s="189"/>
-      <c r="J26" s="188">
+      <c r="I26" s="49"/>
+      <c r="J26" s="50">
         <v>80</v>
       </c>
-      <c r="K26" s="186">
+      <c r="K26" s="75">
         <v>80</v>
       </c>
-      <c r="L26" s="187">
+      <c r="L26" s="76">
         <v>80</v>
       </c>
       <c r="M26" s="48">
@@ -4337,22 +4342,22 @@
       <c r="B27" s="47">
         <v>23</v>
       </c>
-      <c r="C27" s="184" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="185"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="187"/>
-      <c r="G27" s="188"/>
-      <c r="H27" s="186"/>
-      <c r="I27" s="189"/>
-      <c r="J27" s="188">
+      <c r="C27" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="74"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="50">
         <v>40</v>
       </c>
-      <c r="K27" s="186">
+      <c r="K27" s="75">
         <v>120</v>
       </c>
-      <c r="L27" s="187">
+      <c r="L27" s="76">
         <v>160</v>
       </c>
       <c r="M27" s="48">
@@ -4414,7 +4419,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="145" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" s="146"/>
       <c r="E28" s="147"/>
@@ -4574,7 +4579,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="145" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D30" s="146"/>
       <c r="E30" s="147"/>
@@ -4650,7 +4655,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="145" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D31" s="146">
         <v>200</v>
@@ -4732,7 +4737,7 @@
         <v>28</v>
       </c>
       <c r="C32" s="145" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D32" s="146"/>
       <c r="E32" s="147"/>
@@ -4808,7 +4813,7 @@
         <v>29</v>
       </c>
       <c r="C33" s="145" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D33" s="146"/>
       <c r="E33" s="147"/>
@@ -4883,19 +4888,31 @@
       <c r="B34" s="47">
         <v>30</v>
       </c>
-      <c r="C34" s="57"/>
+      <c r="C34" s="57" t="s">
+        <v>99</v>
+      </c>
       <c r="D34" s="74"/>
       <c r="E34" s="75"/>
       <c r="F34" s="76"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="75"/>
+      <c r="G34" s="50">
+        <v>120</v>
+      </c>
+      <c r="H34" s="75">
+        <v>120</v>
+      </c>
       <c r="I34" s="49"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="76"/>
+      <c r="J34" s="50">
+        <v>120</v>
+      </c>
+      <c r="K34" s="75">
+        <v>120</v>
+      </c>
+      <c r="L34" s="76">
+        <v>120</v>
+      </c>
       <c r="M34" s="48">
         <f t="shared" ref="M34:M46" si="68">SUM(D34:L34)/40</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N34" s="39">
         <f t="shared" si="18"/>
@@ -4907,11 +4924,11 @@
       </c>
       <c r="P34" s="73">
         <f t="shared" ref="P34:P46" si="69">SUM(G34:I34)/20</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q34" s="40">
         <f t="shared" ref="Q34:Q46" si="70">SUM(J34:L34)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R34" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4951,19 +4968,27 @@
       <c r="B35" s="47">
         <v>31</v>
       </c>
-      <c r="C35" s="57"/>
+      <c r="C35" s="57" t="s">
+        <v>129</v>
+      </c>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
       <c r="F35" s="76"/>
       <c r="G35" s="50"/>
       <c r="H35" s="75"/>
       <c r="I35" s="49"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="76"/>
+      <c r="J35" s="50">
+        <v>40</v>
+      </c>
+      <c r="K35" s="75">
+        <v>40</v>
+      </c>
+      <c r="L35" s="76">
+        <v>80</v>
+      </c>
       <c r="M35" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N35" s="39">
         <f t="shared" si="18"/>
@@ -4979,7 +5004,7 @@
       </c>
       <c r="Q35" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R35" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5019,19 +5044,31 @@
       <c r="B36" s="47">
         <v>32</v>
       </c>
-      <c r="C36" s="57"/>
+      <c r="C36" s="57" t="s">
+        <v>130</v>
+      </c>
       <c r="D36" s="74"/>
       <c r="E36" s="75"/>
       <c r="F36" s="76"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="75"/>
+      <c r="G36" s="50">
+        <v>400</v>
+      </c>
+      <c r="H36" s="75">
+        <v>400</v>
+      </c>
       <c r="I36" s="49"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="75"/>
-      <c r="L36" s="76"/>
+      <c r="J36" s="50">
+        <v>400</v>
+      </c>
+      <c r="K36" s="75">
+        <v>400</v>
+      </c>
+      <c r="L36" s="76">
+        <v>400</v>
+      </c>
       <c r="M36" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N36" s="39">
         <f t="shared" si="18"/>
@@ -5043,11 +5080,11 @@
       </c>
       <c r="P36" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R36" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5087,19 +5124,27 @@
       <c r="B37" s="47">
         <v>33</v>
       </c>
-      <c r="C37" s="57"/>
+      <c r="C37" s="57" t="s">
+        <v>131</v>
+      </c>
       <c r="D37" s="74"/>
       <c r="E37" s="75"/>
       <c r="F37" s="76"/>
       <c r="G37" s="50"/>
-      <c r="H37" s="75"/>
+      <c r="H37" s="75">
+        <v>40</v>
+      </c>
       <c r="I37" s="49"/>
-      <c r="J37" s="50"/>
+      <c r="J37" s="50">
+        <v>40</v>
+      </c>
       <c r="K37" s="75"/>
-      <c r="L37" s="76"/>
+      <c r="L37" s="76">
+        <v>120</v>
+      </c>
       <c r="M37" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N37" s="39">
         <f t="shared" si="18"/>
@@ -5111,11 +5156,11 @@
       </c>
       <c r="P37" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R37" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11276,10 +11321,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="175" t="s">
+      <c r="B132" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="176"/>
+      <c r="C132" s="164"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>200</v>
@@ -11294,11 +11339,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>1278</v>
+        <v>1798</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>1317</v>
+        <v>1877</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11306,19 +11351,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>2079</v>
+        <v>2679</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>1958</v>
+        <v>2518</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>2558</v>
+        <v>3278</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>234.75</v>
+        <v>308.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11330,11 +11375,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>129.75</v>
+        <v>183.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>329.75</v>
+        <v>423.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11543,10 +11588,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="163" t="s">
+      <c r="B136" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="164"/>
+      <c r="C136" s="177"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11637,10 +11682,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="152" t="s">
+      <c r="B137" s="165" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="153"/>
+      <c r="C137" s="166"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>200</v>
@@ -11655,11 +11700,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>1278</v>
+        <v>1798</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>1317</v>
+        <v>1877</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -11667,19 +11712,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>2079</v>
+        <v>2679</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>1958</v>
+        <v>2518</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>2558</v>
+        <v>3278</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>234.75</v>
+        <v>308.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11691,11 +11736,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>263.5</v>
+        <v>371.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>665.5</v>
+        <v>853.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11732,17 +11777,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11773,24 +11818,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="179" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="180"/>
-      <c r="H3" s="182" t="s">
+      <c r="D3" s="180"/>
+      <c r="E3" s="180"/>
+      <c r="F3" s="180"/>
+      <c r="G3" s="181"/>
+      <c r="H3" s="183" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="183"/>
-      <c r="K3" s="177" t="s">
+      <c r="I3" s="184"/>
+      <c r="K3" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="177"/>
-      <c r="M3" s="177"/>
-      <c r="N3" s="177"/>
-      <c r="O3" s="177"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="178"/>
+      <c r="O3" s="178"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -11833,22 +11878,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>350</v>
+        <v>406</v>
       </c>
       <c r="E5" s="79">
-        <v>206</v>
+        <v>354</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>856</v>
+        <v>1060</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>856</v>
+        <v>1060</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11873,11 +11918,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>14000</v>
+        <v>16240</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>8240</v>
+        <v>14160</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -11885,7 +11930,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>34240</v>
+        <v>42400</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11893,7 +11938,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>34240</v>
+        <v>42400</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11958,11 +12003,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-350</v>
+        <v>-406</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-206</v>
+        <v>-354</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12000,14 +12045,14 @@
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="181" t="s">
+      <c r="C11" s="182" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="181"/>
-      <c r="F11" s="181" t="s">
+      <c r="D11" s="182"/>
+      <c r="F11" s="182" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="181"/>
+      <c r="G11" s="182"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12037,7 +12082,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>4290</v>
+        <v>4494</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12069,7 +12114,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>171600</v>
+        <v>179760</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12137,7 +12182,7 @@
     </row>
     <row r="19" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>3</v>
@@ -12162,13 +12207,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="177" t="s">
+      <c r="D20" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="177"/>
-      <c r="F20" s="177"/>
-      <c r="G20" s="177"/>
-      <c r="H20" s="177"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="178"/>
+      <c r="H20" s="178"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -12460,7 +12505,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -12473,7 +12518,7 @@
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -12496,7 +12541,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>79</v>
       </c>
@@ -12516,7 +12561,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -12531,7 +12576,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -12546,7 +12591,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -12561,7 +12606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -12576,7 +12621,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -12591,16 +12636,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="81" t="s">
-        <v>105</v>
-      </c>
+      <c r="H8" s="81"/>
       <c r="I8" s="81" t="s">
         <v>107</v>
       </c>
@@ -12612,14 +12655,11 @@
       </c>
       <c r="L8" s="133"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="H9" t="s">
-        <v>105</v>
-      </c>
       <c r="I9" s="81" t="s">
         <v>108</v>
       </c>
@@ -12631,61 +12671,67 @@
       </c>
       <c r="L9" s="133"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="I10" s="151" t="s">
+      <c r="H10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="152" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="151">
+      <c r="J10" s="152">
         <v>12</v>
       </c>
-      <c r="K10" s="151" t="s">
-        <v>110</v>
+      <c r="K10" s="152" t="s">
+        <v>100</v>
       </c>
       <c r="L10" s="133"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="I11" s="151" t="s">
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="152" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="151">
+      <c r="J11" s="152">
         <v>19</v>
       </c>
-      <c r="K11" s="151" t="s">
-        <v>110</v>
+      <c r="K11" s="152" t="s">
+        <v>100</v>
       </c>
       <c r="L11" s="133"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="I12" s="81" t="s">
+      <c r="I12" s="151" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="151">
+        <v>13</v>
+      </c>
+      <c r="K12" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="J12" s="81">
-        <v>13</v>
-      </c>
-      <c r="K12" s="81" t="s">
-        <v>117</v>
-      </c>
       <c r="L12" s="133"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="I13" s="81" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J13" s="81">
         <v>5</v>
@@ -12694,14 +12740,17 @@
         <v>100</v>
       </c>
       <c r="L13" s="133"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M13">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="I14" s="81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J14" s="81">
         <v>8</v>
@@ -12710,8 +12759,11 @@
         <v>100</v>
       </c>
       <c r="L14" s="133"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -12725,19 +12777,23 @@
       <c r="K15" s="139" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M15">
+        <f>M13+M14</f>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="I16" s="81" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J16" s="81">
         <v>5</v>
       </c>
-      <c r="K16" s="81" t="s">
+      <c r="K16" s="139" t="s">
         <v>100</v>
       </c>
       <c r="L16" s="134"/>
@@ -12748,12 +12804,12 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="I17" s="81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J17" s="81">
         <v>4</v>
       </c>
-      <c r="K17" s="81" t="s">
+      <c r="K17" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12763,12 +12819,12 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="I18" s="81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J18" s="81">
         <v>9</v>
       </c>
-      <c r="K18" s="81" t="s">
+      <c r="K18" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12778,12 +12834,12 @@
       <c r="C19" s="83"/>
       <c r="D19" s="83"/>
       <c r="I19" s="81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J19" s="81">
         <v>6</v>
       </c>
-      <c r="K19" s="81" t="s">
+      <c r="K19" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12793,12 +12849,12 @@
       <c r="C20" s="85"/>
       <c r="D20" s="86"/>
       <c r="I20" s="81" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J20" s="81">
         <v>30</v>
       </c>
-      <c r="K20" s="81" t="s">
+      <c r="K20" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12809,29 +12865,79 @@
       <c r="J21" s="81">
         <v>22</v>
       </c>
-      <c r="K21" s="81" t="s">
+      <c r="K21" s="139" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
+      <c r="I22" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="J22" s="81">
+        <v>15</v>
+      </c>
+      <c r="K22" s="81" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
+      <c r="I23" s="81" t="s">
+        <v>129</v>
+      </c>
+      <c r="J23" s="81">
+        <v>4</v>
+      </c>
+      <c r="K23" s="81" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
+      <c r="I24" s="81" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24" s="81">
+        <v>50</v>
+      </c>
+      <c r="K24" s="81" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I25" s="81"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="81"/>
+      <c r="F25">
+        <v>3640</v>
+      </c>
+      <c r="I25" s="81" t="s">
+        <v>131</v>
+      </c>
+      <c r="J25" s="81">
+        <v>5</v>
+      </c>
+      <c r="K25" s="81" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>680</v>
+      </c>
+      <c r="J26" s="133">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <f>F25-F26</f>
+        <v>2960</v>
+      </c>
+      <c r="J27" s="133">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <f>F27/40</f>
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202AFD12-E7FA-4866-A718-ADAED16F4AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2A1D84-1C69-4300-B60B-B11D00A79090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="143">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -262,9 +262,6 @@
     <t>DIFF</t>
   </si>
   <si>
-    <t>20-06-26</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -419,6 +416,42 @@
   </si>
   <si>
     <t>Risen Manawan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hotpot Souces </t>
+  </si>
+  <si>
+    <t>Family Store</t>
+  </si>
+  <si>
+    <t>Shahwar Mega Mart</t>
+  </si>
+  <si>
+    <t>Easy Mart</t>
+  </si>
+  <si>
+    <t>Jalal Sons Behria Orchard</t>
+  </si>
+  <si>
+    <t>Sana C &amp; C Nespark Society</t>
+  </si>
+  <si>
+    <t>Nagina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagina </t>
+  </si>
+  <si>
+    <t>The Hotpot Souces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shehwar Mega Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sana C &amp; C Denpak Society </t>
   </si>
 </sst>
 </file>
@@ -1705,6 +1738,45 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1739,45 +1811,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2310,14 +2343,14 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="131" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="130" t="s">
         <v>83</v>
-      </c>
-      <c r="C24" s="130" t="s">
-        <v>84</v>
       </c>
       <c r="D24" s="130"/>
       <c r="E24" s="130" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2336,14 +2369,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="153">
+      <c r="B1" s="166">
         <f ca="1">TODAY()</f>
-        <v>46214</v>
-      </c>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
+        <v>46216</v>
+      </c>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2365,10 +2398,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="167" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2401,13 +2434,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="167"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="170" t="s">
+      <c r="M2" s="155"/>
+      <c r="N2" s="156"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="171"/>
+      <c r="Q2" s="159"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2426,8 +2459,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="175"/>
-      <c r="B3" s="155"/>
+      <c r="A3" s="163"/>
+      <c r="B3" s="168"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2458,29 +2491,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="173"/>
-      <c r="O3" s="174"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="162"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="157" t="s">
+      <c r="R3" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="158"/>
-      <c r="T3" s="158"/>
-      <c r="U3" s="159"/>
-      <c r="V3" s="160" t="s">
+      <c r="S3" s="171"/>
+      <c r="T3" s="171"/>
+      <c r="U3" s="172"/>
+      <c r="V3" s="173" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="161"/>
-      <c r="X3" s="161"/>
-      <c r="Y3" s="162"/>
+      <c r="W3" s="174"/>
+      <c r="X3" s="174"/>
+      <c r="Y3" s="175"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="175"/>
-      <c r="B4" s="156"/>
+      <c r="A4" s="163"/>
+      <c r="B4" s="169"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2559,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="140" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" s="141"/>
       <c r="E5" s="142"/>
@@ -2641,7 +2674,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" s="74"/>
       <c r="E6" s="75"/>
@@ -2723,7 +2756,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" s="74"/>
       <c r="E7" s="75"/>
@@ -2805,7 +2838,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" s="74"/>
       <c r="E8" s="75"/>
@@ -2887,7 +2920,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" s="74"/>
       <c r="E9" s="75"/>
@@ -2969,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D10" s="74"/>
       <c r="E10" s="75"/>
@@ -3051,7 +3084,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" s="74"/>
       <c r="E11" s="75"/>
@@ -3133,7 +3166,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="74"/>
       <c r="E12" s="75"/>
@@ -3215,7 +3248,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D13" s="74"/>
       <c r="E13" s="75"/>
@@ -3297,7 +3330,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D14" s="74"/>
       <c r="E14" s="75"/>
@@ -3379,7 +3412,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D15" s="74"/>
       <c r="E15" s="75"/>
@@ -3461,7 +3494,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16" s="74"/>
       <c r="E16" s="75"/>
@@ -3543,7 +3576,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D17" s="74"/>
       <c r="E17" s="75"/>
@@ -3625,7 +3658,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" s="74"/>
       <c r="E18" s="75"/>
@@ -3707,7 +3740,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D19" s="74"/>
       <c r="E19" s="75"/>
@@ -3785,7 +3818,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="74"/>
       <c r="E20" s="75"/>
@@ -3863,7 +3896,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D21" s="74"/>
       <c r="E21" s="75"/>
@@ -3943,7 +3976,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D22" s="74"/>
       <c r="E22" s="75"/>
@@ -4023,7 +4056,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
@@ -4101,7 +4134,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
@@ -4183,7 +4216,7 @@
         <v>21</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" s="74"/>
       <c r="E25" s="75"/>
@@ -4261,7 +4294,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D26" s="74"/>
       <c r="E26" s="75"/>
@@ -4343,7 +4376,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" s="74"/>
       <c r="E27" s="75"/>
@@ -4414,30 +4447,32 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="78"/>
+      <c r="A28" s="78">
+        <v>46213</v>
+      </c>
       <c r="B28" s="47">
         <v>24</v>
       </c>
-      <c r="C28" s="145" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="146"/>
-      <c r="E28" s="147"/>
-      <c r="F28" s="148"/>
-      <c r="G28" s="149">
+      <c r="C28" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="74"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="50">
         <v>40</v>
       </c>
-      <c r="H28" s="147">
+      <c r="H28" s="75">
         <v>40</v>
       </c>
-      <c r="I28" s="150"/>
-      <c r="J28" s="149">
+      <c r="I28" s="49"/>
+      <c r="J28" s="50">
         <v>40</v>
       </c>
-      <c r="K28" s="147">
+      <c r="K28" s="75">
         <v>40</v>
       </c>
-      <c r="L28" s="148">
+      <c r="L28" s="76">
         <v>40</v>
       </c>
       <c r="M28" s="48">
@@ -4494,30 +4529,32 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="78"/>
+      <c r="A29" s="78">
+        <v>46213</v>
+      </c>
       <c r="B29" s="47">
         <v>25</v>
       </c>
-      <c r="C29" s="145" t="s">
+      <c r="C29" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="146"/>
-      <c r="E29" s="147"/>
-      <c r="F29" s="148"/>
-      <c r="G29" s="149">
+      <c r="D29" s="74"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="50">
         <v>80</v>
       </c>
-      <c r="H29" s="147">
+      <c r="H29" s="75">
         <v>120</v>
       </c>
-      <c r="I29" s="150"/>
-      <c r="J29" s="149">
+      <c r="I29" s="49"/>
+      <c r="J29" s="50">
         <v>120</v>
       </c>
-      <c r="K29" s="147">
+      <c r="K29" s="75">
         <v>200</v>
       </c>
-      <c r="L29" s="148">
+      <c r="L29" s="76">
         <v>360</v>
       </c>
       <c r="M29" s="48">
@@ -4574,26 +4611,28 @@
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A30" s="78"/>
+      <c r="A30" s="78">
+        <v>46213</v>
+      </c>
       <c r="B30" s="47">
         <v>26</v>
       </c>
-      <c r="C30" s="145" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="146"/>
-      <c r="E30" s="147"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="149"/>
-      <c r="H30" s="147"/>
-      <c r="I30" s="150"/>
-      <c r="J30" s="149">
+      <c r="C30" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="74"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="50">
         <v>40</v>
       </c>
-      <c r="K30" s="147">
+      <c r="K30" s="75">
         <v>40</v>
       </c>
-      <c r="L30" s="148">
+      <c r="L30" s="76">
         <v>80</v>
       </c>
       <c r="M30" s="48">
@@ -4650,32 +4689,34 @@
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A31" s="78"/>
+      <c r="A31" s="78">
+        <v>46213</v>
+      </c>
       <c r="B31" s="47">
         <v>27</v>
       </c>
-      <c r="C31" s="145" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="146">
+      <c r="C31" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="74">
         <v>200</v>
       </c>
-      <c r="E31" s="147"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="149">
+      <c r="E31" s="75"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="50">
         <v>200</v>
       </c>
-      <c r="H31" s="147">
+      <c r="H31" s="75">
         <v>200</v>
       </c>
-      <c r="I31" s="150"/>
-      <c r="J31" s="149">
+      <c r="I31" s="49"/>
+      <c r="J31" s="50">
         <v>200</v>
       </c>
-      <c r="K31" s="147">
+      <c r="K31" s="75">
         <v>200</v>
       </c>
-      <c r="L31" s="148">
+      <c r="L31" s="76">
         <v>200</v>
       </c>
       <c r="M31" s="48">
@@ -4732,26 +4773,28 @@
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A32" s="78"/>
+      <c r="A32" s="78">
+        <v>46213</v>
+      </c>
       <c r="B32" s="47">
         <v>28</v>
       </c>
-      <c r="C32" s="145" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="146"/>
-      <c r="E32" s="147"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="149"/>
-      <c r="H32" s="147"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="149">
+      <c r="C32" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="74"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="50">
         <v>120</v>
       </c>
-      <c r="K32" s="147">
+      <c r="K32" s="75">
         <v>120</v>
       </c>
-      <c r="L32" s="148">
+      <c r="L32" s="76">
         <v>120</v>
       </c>
       <c r="M32" s="48">
@@ -4808,26 +4851,28 @@
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A33" s="78"/>
+      <c r="A33" s="78">
+        <v>46213</v>
+      </c>
       <c r="B33" s="47">
         <v>29</v>
       </c>
-      <c r="C33" s="145" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" s="146"/>
-      <c r="E33" s="147"/>
-      <c r="F33" s="148"/>
-      <c r="G33" s="149"/>
-      <c r="H33" s="147"/>
-      <c r="I33" s="150"/>
-      <c r="J33" s="149">
+      <c r="C33" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="74"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="50">
         <v>80</v>
       </c>
-      <c r="K33" s="147">
+      <c r="K33" s="75">
         <v>40</v>
       </c>
-      <c r="L33" s="148">
+      <c r="L33" s="76">
         <v>40</v>
       </c>
       <c r="M33" s="48">
@@ -4884,12 +4929,14 @@
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A34" s="78"/>
+      <c r="A34" s="78">
+        <v>11</v>
+      </c>
       <c r="B34" s="47">
         <v>30</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" s="74"/>
       <c r="E34" s="75"/>
@@ -4964,12 +5011,14 @@
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="78"/>
+      <c r="A35" s="78">
+        <v>11</v>
+      </c>
       <c r="B35" s="47">
         <v>31</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
@@ -5040,12 +5089,14 @@
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A36" s="78"/>
+      <c r="A36" s="78">
+        <v>11</v>
+      </c>
       <c r="B36" s="47">
         <v>32</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D36" s="74"/>
       <c r="E36" s="75"/>
@@ -5120,12 +5171,14 @@
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A37" s="78"/>
+      <c r="A37" s="78">
+        <v>11</v>
+      </c>
       <c r="B37" s="47">
         <v>33</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D37" s="74"/>
       <c r="E37" s="75"/>
@@ -5196,12 +5249,18 @@
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A38" s="78"/>
+      <c r="A38" s="78">
+        <v>11</v>
+      </c>
       <c r="B38" s="47">
         <v>34</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="74"/>
+      <c r="C38" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="74">
+        <v>2000</v>
+      </c>
       <c r="E38" s="75"/>
       <c r="F38" s="76"/>
       <c r="G38" s="50"/>
@@ -5212,7 +5271,7 @@
       <c r="L38" s="76"/>
       <c r="M38" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N38" s="39">
         <f t="shared" si="18"/>
@@ -5264,23 +5323,37 @@
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A39" s="78"/>
+      <c r="A39" s="78">
+        <v>13</v>
+      </c>
       <c r="B39" s="47">
         <v>35</v>
       </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="75"/>
-      <c r="L39" s="76"/>
+      <c r="C39" s="145" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="146"/>
+      <c r="E39" s="147"/>
+      <c r="F39" s="148"/>
+      <c r="G39" s="149">
+        <v>20</v>
+      </c>
+      <c r="H39" s="147">
+        <v>80</v>
+      </c>
+      <c r="I39" s="150"/>
+      <c r="J39" s="149">
+        <v>20</v>
+      </c>
+      <c r="K39" s="147">
+        <v>80</v>
+      </c>
+      <c r="L39" s="148">
+        <v>80</v>
+      </c>
       <c r="M39" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N39" s="39">
         <f t="shared" si="18"/>
@@ -5292,11 +5365,11 @@
       </c>
       <c r="P39" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q39" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R39" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5332,23 +5405,29 @@
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A40" s="78"/>
+      <c r="A40" s="78">
+        <v>13</v>
+      </c>
       <c r="B40" s="47">
         <v>36</v>
       </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="76"/>
+      <c r="C40" s="145" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="146"/>
+      <c r="E40" s="147"/>
+      <c r="F40" s="148"/>
+      <c r="G40" s="149"/>
+      <c r="H40" s="147"/>
+      <c r="I40" s="150"/>
+      <c r="J40" s="149">
+        <v>200</v>
+      </c>
+      <c r="K40" s="147"/>
+      <c r="L40" s="148"/>
       <c r="M40" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N40" s="39">
         <f t="shared" si="18"/>
@@ -5364,7 +5443,7 @@
       </c>
       <c r="Q40" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R40" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5400,23 +5479,39 @@
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A41" s="78"/>
+      <c r="A41" s="78">
+        <v>13</v>
+      </c>
       <c r="B41" s="47">
         <v>37</v>
       </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="75"/>
-      <c r="L41" s="76"/>
+      <c r="C41" s="145" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="146">
+        <v>160</v>
+      </c>
+      <c r="E41" s="147"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>120</v>
+      </c>
+      <c r="H41" s="147">
+        <v>120</v>
+      </c>
+      <c r="I41" s="150"/>
+      <c r="J41" s="149">
+        <v>120</v>
+      </c>
+      <c r="K41" s="147">
+        <v>120</v>
+      </c>
+      <c r="L41" s="148">
+        <v>200</v>
+      </c>
       <c r="M41" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N41" s="39">
         <f t="shared" si="18"/>
@@ -5428,11 +5523,11 @@
       </c>
       <c r="P41" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q41" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R41" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5468,23 +5563,35 @@
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A42" s="78"/>
+      <c r="A42" s="78">
+        <v>13</v>
+      </c>
       <c r="B42" s="47">
         <v>38</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="75"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="75"/>
-      <c r="L42" s="76"/>
+      <c r="C42" s="145" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="146">
+        <v>80</v>
+      </c>
+      <c r="E42" s="147"/>
+      <c r="F42" s="148"/>
+      <c r="G42" s="149"/>
+      <c r="H42" s="147"/>
+      <c r="I42" s="150"/>
+      <c r="J42" s="149">
+        <v>80</v>
+      </c>
+      <c r="K42" s="147">
+        <v>80</v>
+      </c>
+      <c r="L42" s="148">
+        <v>80</v>
+      </c>
       <c r="M42" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N42" s="39">
         <f t="shared" si="18"/>
@@ -5500,7 +5607,7 @@
       </c>
       <c r="Q42" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R42" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5536,23 +5643,33 @@
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A43" s="78"/>
+      <c r="A43" s="78">
+        <v>13</v>
+      </c>
       <c r="B43" s="47">
         <v>39</v>
       </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="75"/>
-      <c r="L43" s="76"/>
+      <c r="C43" s="145" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" s="146"/>
+      <c r="E43" s="147"/>
+      <c r="F43" s="148"/>
+      <c r="G43" s="149"/>
+      <c r="H43" s="147"/>
+      <c r="I43" s="150"/>
+      <c r="J43" s="149">
+        <v>40</v>
+      </c>
+      <c r="K43" s="147">
+        <v>40</v>
+      </c>
+      <c r="L43" s="148">
+        <v>80</v>
+      </c>
       <c r="M43" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N43" s="39">
         <f t="shared" si="18"/>
@@ -5568,7 +5685,7 @@
       </c>
       <c r="Q43" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R43" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5604,23 +5721,33 @@
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A44" s="78"/>
+      <c r="A44" s="78">
+        <v>13</v>
+      </c>
       <c r="B44" s="47">
         <v>40</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="75"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="75"/>
-      <c r="L44" s="76"/>
+      <c r="C44" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="146"/>
+      <c r="E44" s="147"/>
+      <c r="F44" s="148"/>
+      <c r="G44" s="149"/>
+      <c r="H44" s="147">
+        <v>80</v>
+      </c>
+      <c r="I44" s="150"/>
+      <c r="J44" s="149">
+        <v>40</v>
+      </c>
+      <c r="K44" s="147"/>
+      <c r="L44" s="148">
+        <v>40</v>
+      </c>
       <c r="M44" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N44" s="39">
         <f t="shared" si="18"/>
@@ -5632,11 +5759,11 @@
       </c>
       <c r="P44" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R44" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11321,13 +11448,13 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="163" t="s">
+      <c r="B132" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="164"/>
+      <c r="C132" s="177"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
-        <v>200</v>
+        <v>2440</v>
       </c>
       <c r="E132" s="88">
         <f t="shared" si="104"/>
@@ -11339,11 +11466,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>1798</v>
+        <v>1938</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>1877</v>
+        <v>2157</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11351,19 +11478,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>2679</v>
+        <v>3179</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>2518</v>
+        <v>2838</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>3278</v>
+        <v>3758</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>308.75</v>
+        <v>407.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11375,11 +11502,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>183.75</v>
+        <v>204.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>423.75</v>
+        <v>488.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11588,10 +11715,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="176" t="s">
+      <c r="B136" s="164" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="177"/>
+      <c r="C136" s="165"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11682,13 +11809,13 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="165" t="s">
+      <c r="B137" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="166"/>
+      <c r="C137" s="154"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
-        <v>200</v>
+        <v>2440</v>
       </c>
       <c r="E137" s="89">
         <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
@@ -11700,11 +11827,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>1798</v>
+        <v>1938</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>1877</v>
+        <v>2157</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -11712,19 +11839,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>2679</v>
+        <v>3179</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>2518</v>
+        <v>2838</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>3278</v>
+        <v>3758</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>308.75</v>
+        <v>407.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11736,11 +11863,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>371.5</v>
+        <v>413.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>853.5</v>
+        <v>983.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11777,17 +11904,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11799,7 +11926,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C2:Q29"/>
+  <dimension ref="C2:Q31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -11878,22 +12005,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>406</v>
+        <v>467.4</v>
       </c>
       <c r="E5" s="79">
-        <v>354</v>
+        <v>506</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>1060</v>
+        <v>1273.4000000000001</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>1060</v>
+        <v>1273.4000000000001</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11918,11 +12045,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>16240</v>
+        <v>18696</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>14160</v>
+        <v>20240</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -11930,7 +12057,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>42400</v>
+        <v>50936</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11938,7 +12065,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>42400</v>
+        <v>50936</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12003,11 +12130,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-406</v>
+        <v>-467.4</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-354</v>
+        <v>-506</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12082,7 +12209,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>4494</v>
+        <v>4707.3999999999996</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12114,7 +12241,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>179760</v>
+        <v>188296</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12182,7 +12309,7 @@
     </row>
     <row r="19" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>3</v>
@@ -12488,6 +12615,23 @@
       <c r="H29" s="9">
         <f>SUM(H22:H28)</f>
         <v>548</v>
+      </c>
+      <c r="K29">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="J30">
+        <f>K30+K29</f>
+        <v>1067</v>
+      </c>
+      <c r="K30">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="31" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="K31">
+        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -12505,7 +12649,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -12513,9 +12657,9 @@
     <col min="4" max="4" width="5.6328125" customWidth="1"/>
     <col min="6" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.81640625" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -12532,33 +12676,31 @@
         <v>9</v>
       </c>
       <c r="I1" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="128" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="128" t="s">
-        <v>82</v>
-      </c>
       <c r="K1" s="128" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>79</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="I2" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J2" s="81">
         <v>70</v>
       </c>
       <c r="K2" s="81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -12567,13 +12709,13 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="I3" s="139" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J3" s="139">
         <v>10</v>
       </c>
       <c r="K3" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -12582,13 +12724,13 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="I4" s="139" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="139">
         <v>9</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -12597,13 +12739,13 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="I5" s="139" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J5" s="139">
         <v>18</v>
       </c>
       <c r="K5" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -12612,13 +12754,13 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="I6" s="139" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J6" s="139">
         <v>5</v>
       </c>
       <c r="K6" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -12627,13 +12769,13 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="I7" s="81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J7" s="81">
         <v>14</v>
       </c>
       <c r="K7" s="81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -12645,13 +12787,13 @@
       <c r="G8" s="81"/>
       <c r="H8" s="81"/>
       <c r="I8" s="81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J8" s="81">
         <v>13</v>
       </c>
       <c r="K8" s="81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L8" s="133"/>
     </row>
@@ -12661,13 +12803,13 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="I9" s="81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9" s="81">
         <v>4</v>
       </c>
       <c r="K9" s="81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L9" s="133"/>
     </row>
@@ -12677,16 +12819,16 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I10" s="152" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J10" s="152">
         <v>12</v>
       </c>
       <c r="K10" s="152" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L10" s="133"/>
     </row>
@@ -12696,16 +12838,16 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I11" s="152" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J11" s="152">
         <v>19</v>
       </c>
       <c r="K11" s="152" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L11" s="133"/>
     </row>
@@ -12715,13 +12857,13 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="I12" s="151" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J12" s="151">
         <v>13</v>
       </c>
       <c r="K12" s="151" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L12" s="133"/>
     </row>
@@ -12731,13 +12873,13 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="I13" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J13" s="81">
         <v>5</v>
       </c>
       <c r="K13" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L13" s="133"/>
       <c r="M13">
@@ -12750,13 +12892,13 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="I14" s="81" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J14" s="81">
         <v>8</v>
       </c>
       <c r="K14" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L14" s="133"/>
       <c r="M14">
@@ -12769,13 +12911,13 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="I15" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J15" s="81">
         <v>10</v>
       </c>
       <c r="K15" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M15">
         <f>M13+M14</f>
@@ -12788,77 +12930,77 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="I16" s="81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J16" s="81">
         <v>5</v>
       </c>
       <c r="K16" s="139" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L16" s="134"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="I17" s="81" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J17" s="81">
         <v>4</v>
       </c>
       <c r="K17" s="139" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="I18" s="81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J18" s="81">
         <v>9</v>
       </c>
       <c r="K18" s="139" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="83"/>
       <c r="C19" s="83"/>
       <c r="D19" s="83"/>
       <c r="I19" s="81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J19" s="81">
         <v>6</v>
       </c>
       <c r="K19" s="139" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="84"/>
       <c r="B20" s="85"/>
       <c r="C20" s="85"/>
       <c r="D20" s="86"/>
       <c r="I20" s="81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J20" s="81">
         <v>30</v>
       </c>
       <c r="K20" s="139" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I21" s="81" t="s">
         <v>25</v>
       </c>
@@ -12866,84 +13008,162 @@
         <v>22</v>
       </c>
       <c r="K21" s="139" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I22" s="81" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I22" s="79" t="s">
+        <v>98</v>
       </c>
       <c r="J22" s="81">
         <v>15</v>
       </c>
       <c r="K22" s="81" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I23" s="81" t="s">
-        <v>129</v>
+        <v>99</v>
+      </c>
+      <c r="L22">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I23" s="79" t="s">
+        <v>128</v>
       </c>
       <c r="J23" s="81">
         <v>4</v>
       </c>
       <c r="K23" s="81" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I24" s="81" t="s">
-        <v>130</v>
+        <v>99</v>
+      </c>
+      <c r="L23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I24" s="79" t="s">
+        <v>129</v>
       </c>
       <c r="J24" s="81">
         <v>50</v>
       </c>
       <c r="K24" s="81" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="F25">
-        <v>3640</v>
-      </c>
-      <c r="I25" s="81" t="s">
-        <v>131</v>
+        <v>99</v>
+      </c>
+      <c r="L24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I25" s="79" t="s">
+        <v>130</v>
       </c>
       <c r="J25" s="81">
         <v>5</v>
       </c>
       <c r="K25" s="81" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="F26">
-        <v>680</v>
-      </c>
-      <c r="J26" s="133">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="F27">
-        <f>F25-F26</f>
-        <v>2960</v>
-      </c>
-      <c r="J27" s="133">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="F28">
-        <f>F27/40</f>
-        <v>74</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="L25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I26" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="J26" s="81">
+        <v>50</v>
+      </c>
+      <c r="K26" s="81" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I27" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="J27" s="79">
+        <v>5</v>
+      </c>
+      <c r="K27" s="152" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I28" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="J28" s="79">
+        <v>7</v>
+      </c>
+      <c r="K28" s="152" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I29" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="J29" s="79">
+        <v>21</v>
+      </c>
+      <c r="K29" s="152" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I30" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="J30" s="79">
+        <v>8</v>
+      </c>
+      <c r="K30" s="152" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I31" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31" s="79">
+        <v>4</v>
+      </c>
+      <c r="K31" s="152" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I32" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="J32" s="79">
+        <v>4</v>
+      </c>
+      <c r="K32" s="152" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80DF3CCA-0793-4D04-8BF6-1A26354907F3}">
           <x14:formula1>
             <xm:f>Sheet1!$B$10:$B$22</xm:f>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2A1D84-1C69-4300-B60B-B11D00A79090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F81EA2-236C-49CA-91A7-12007423DEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="148">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -451,7 +451,22 @@
     <t xml:space="preserve">Easy Mart </t>
   </si>
   <si>
-    <t xml:space="preserve">Sana C &amp; C Denpak Society </t>
+    <t xml:space="preserve">Raheem </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On The Way </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Fateh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sana C &amp; C Nespak Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem  Iqbal Town </t>
+  </si>
+  <si>
+    <t>Jalal Sons warehouse</t>
   </si>
 </sst>
 </file>
@@ -1738,6 +1753,42 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1775,42 +1826,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2369,14 +2384,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="166">
+      <c r="B1" s="153">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
-      </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
+        <v>46218</v>
+      </c>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2398,10 +2413,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="154" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2434,13 +2449,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="155"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158" t="s">
+      <c r="M2" s="167"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="159"/>
+      <c r="Q2" s="171"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2459,8 +2474,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="163"/>
-      <c r="B3" s="168"/>
+      <c r="A3" s="175"/>
+      <c r="B3" s="155"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2491,29 +2506,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="161"/>
-      <c r="O3" s="162"/>
+      <c r="N3" s="173"/>
+      <c r="O3" s="174"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="170" t="s">
+      <c r="R3" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="171"/>
-      <c r="T3" s="171"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="173" t="s">
+      <c r="S3" s="158"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="159"/>
+      <c r="V3" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="175"/>
+      <c r="W3" s="161"/>
+      <c r="X3" s="161"/>
+      <c r="Y3" s="162"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="163"/>
-      <c r="B4" s="169"/>
+      <c r="A4" s="175"/>
+      <c r="B4" s="156"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -5728,7 +5743,7 @@
         <v>40</v>
       </c>
       <c r="C44" s="145" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D44" s="146"/>
       <c r="E44" s="147"/>
@@ -5799,23 +5814,35 @@
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A45" s="78"/>
+      <c r="A45" s="78">
+        <v>14</v>
+      </c>
       <c r="B45" s="47">
         <v>41</v>
       </c>
-      <c r="C45" s="57"/>
+      <c r="C45" s="57" t="s">
+        <v>146</v>
+      </c>
       <c r="D45" s="74"/>
       <c r="E45" s="75"/>
       <c r="F45" s="76"/>
-      <c r="G45" s="50"/>
+      <c r="G45" s="50">
+        <v>120</v>
+      </c>
       <c r="H45" s="75"/>
       <c r="I45" s="49"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="75"/>
-      <c r="L45" s="76"/>
+      <c r="J45" s="50">
+        <v>360</v>
+      </c>
+      <c r="K45" s="75">
+        <v>600</v>
+      </c>
+      <c r="L45" s="76">
+        <v>320</v>
+      </c>
       <c r="M45" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N45" s="39">
         <f t="shared" si="18"/>
@@ -5827,11 +5854,11 @@
       </c>
       <c r="P45" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R45" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11448,10 +11475,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="176" t="s">
+      <c r="B132" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="177"/>
+      <c r="C132" s="164"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11466,7 +11493,7 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>1938</v>
+        <v>2058</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
@@ -11478,19 +11505,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>3179</v>
+        <v>3539</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>2838</v>
+        <v>3438</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>3758</v>
+        <v>4078</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>407.75</v>
+        <v>442.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11502,11 +11529,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>204.75</v>
+        <v>210.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>488.75</v>
+        <v>552.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11715,10 +11742,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="164" t="s">
+      <c r="B136" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="165"/>
+      <c r="C136" s="177"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11809,10 +11836,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="153" t="s">
+      <c r="B137" s="165" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="154"/>
+      <c r="C137" s="166"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -11827,7 +11854,7 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>1938</v>
+        <v>2058</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
@@ -11839,19 +11866,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>3179</v>
+        <v>3539</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>2838</v>
+        <v>3438</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>3758</v>
+        <v>4078</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>407.75</v>
+        <v>442.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11863,11 +11890,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>413.5</v>
+        <v>425.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>983.5</v>
+        <v>1111.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11904,17 +11931,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12005,22 +12032,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>467.4</v>
+        <v>510</v>
       </c>
       <c r="E5" s="79">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>1273.4000000000001</v>
+        <v>1352</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>1273.4000000000001</v>
+        <v>1352</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12029,11 +12056,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>6173</v>
+        <v>3739</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>154.32499999999999</v>
+        <v>93.474999999999994</v>
       </c>
       <c r="O5" s="81">
         <v>188</v>
@@ -12045,11 +12072,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>18696</v>
+        <v>20400</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>20240</v>
+        <v>21680</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12057,7 +12084,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>50936</v>
+        <v>54080</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12065,7 +12092,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>50936</v>
+        <v>54080</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12074,11 +12101,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>7443</v>
+        <v>5073</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>186.07499999999999</v>
+        <v>126.825</v>
       </c>
       <c r="O6" s="81">
         <v>109</v>
@@ -12092,9 +12119,7 @@
       <c r="L7" s="7">
         <v>70</v>
       </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
+      <c r="M7" s="5"/>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -12114,11 +12139,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>34701</v>
+        <v>22094</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>867.52499999999998</v>
+        <v>552.35</v>
       </c>
       <c r="O8" s="81">
         <v>64</v>
@@ -12130,11 +12155,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-467.4</v>
+        <v>-510</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-506</v>
+        <v>-542</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12143,11 +12168,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>8422</v>
+        <v>3609</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>210.55</v>
+        <v>90.224999999999994</v>
       </c>
       <c r="O9" s="81">
         <v>133</v>
@@ -12161,11 +12186,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>42523</v>
+        <v>27018</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>1063.075</v>
+        <v>675.45</v>
       </c>
       <c r="O10" s="81">
         <v>15</v>
@@ -12187,11 +12212,11 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>60810</v>
+        <v>55832</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>1520.25</v>
+        <v>1395.8</v>
       </c>
       <c r="O11" s="81">
         <v>20</v>
@@ -12209,7 +12234,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>4707.3999999999996</v>
+        <v>4786</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12217,11 +12242,11 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>160072</v>
+        <v>117365</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>4001.8</v>
+        <v>2934.125</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -12241,7 +12266,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>188296</v>
+        <v>191440</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12274,7 +12299,7 @@
       </c>
       <c r="O17" s="127">
         <f>N17-M5</f>
-        <v>2081</v>
+        <v>4515</v>
       </c>
       <c r="P17">
         <v>188</v>
@@ -12297,7 +12322,7 @@
       </c>
       <c r="O18" s="127">
         <f>N18-M6</f>
-        <v>1375</v>
+        <v>3745</v>
       </c>
       <c r="P18">
         <v>109</v>
@@ -12353,7 +12378,7 @@
       </c>
       <c r="O20" s="127">
         <f t="shared" si="2"/>
-        <v>4127</v>
+        <v>16734</v>
       </c>
       <c r="P20">
         <v>64</v>
@@ -12391,7 +12416,7 @@
       </c>
       <c r="O21" s="127">
         <f t="shared" si="2"/>
-        <v>3359</v>
+        <v>8172</v>
       </c>
       <c r="P21">
         <v>133</v>
@@ -12430,7 +12455,7 @@
       </c>
       <c r="O22" s="127">
         <f t="shared" si="2"/>
-        <v>2820</v>
+        <v>18325</v>
       </c>
       <c r="P22">
         <v>15</v>
@@ -12469,7 +12494,7 @@
       </c>
       <c r="O23" s="127">
         <f t="shared" si="2"/>
-        <v>3968</v>
+        <v>8946</v>
       </c>
       <c r="P23">
         <v>20</v>
@@ -12508,7 +12533,7 @@
       </c>
       <c r="O24" s="122">
         <f>SUM(O17:O23)</f>
-        <v>17730</v>
+        <v>60437</v>
       </c>
     </row>
     <row r="25" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12542,7 +12567,7 @@
       </c>
       <c r="O25" s="122">
         <f>O24/40</f>
-        <v>443.25</v>
+        <v>1510.925</v>
       </c>
     </row>
     <row r="26" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13145,19 +13170,37 @@
       </c>
     </row>
     <row r="33" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
+      <c r="I33" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="J33" s="79">
+        <v>35</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="34" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+      <c r="I34" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="J34" s="79">
+        <v>305</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="35" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
+      <c r="I35" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="J35" s="2">
+        <v>125</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F81EA2-236C-49CA-91A7-12007423DEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776F4FE7-7A92-46BD-A189-7EC19653CEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="157">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -467,6 +467,33 @@
   </si>
   <si>
     <t>Jalal Sons warehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon </t>
+  </si>
+  <si>
+    <t>Waseem</t>
+  </si>
+  <si>
+    <t>Chk</t>
+  </si>
+  <si>
+    <t>CHk</t>
+  </si>
+  <si>
+    <t>indomie</t>
+  </si>
+  <si>
+    <t>Indomie</t>
+  </si>
+  <si>
+    <t>Total Ctns</t>
+  </si>
+  <si>
+    <t>Flavour</t>
+  </si>
+  <si>
+    <t>Gram</t>
   </si>
 </sst>
 </file>
@@ -1367,7 +1394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1753,6 +1780,45 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1789,45 +1855,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1847,6 +1874,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2384,14 +2432,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="153">
+      <c r="B1" s="166">
         <f ca="1">TODAY()</f>
         <v>46218</v>
       </c>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2413,10 +2461,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="167" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2449,13 +2497,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="167"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="170" t="s">
+      <c r="M2" s="155"/>
+      <c r="N2" s="156"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="171"/>
+      <c r="Q2" s="159"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2474,8 +2522,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="175"/>
-      <c r="B3" s="155"/>
+      <c r="A3" s="163"/>
+      <c r="B3" s="168"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2506,29 +2554,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="173"/>
-      <c r="O3" s="174"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="162"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="157" t="s">
+      <c r="R3" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="158"/>
-      <c r="T3" s="158"/>
-      <c r="U3" s="159"/>
-      <c r="V3" s="160" t="s">
+      <c r="S3" s="171"/>
+      <c r="T3" s="171"/>
+      <c r="U3" s="172"/>
+      <c r="V3" s="173" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="161"/>
-      <c r="X3" s="161"/>
-      <c r="Y3" s="162"/>
+      <c r="W3" s="174"/>
+      <c r="X3" s="174"/>
+      <c r="Y3" s="175"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="175"/>
-      <c r="B4" s="156"/>
+      <c r="A4" s="163"/>
+      <c r="B4" s="169"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11475,10 +11523,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="163" t="s">
+      <c r="B132" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="164"/>
+      <c r="C132" s="177"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11742,10 +11790,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="176" t="s">
+      <c r="B136" s="164" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="177"/>
+      <c r="C136" s="165"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11836,10 +11884,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="165" t="s">
+      <c r="B137" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="166"/>
+      <c r="C137" s="154"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -11931,17 +11979,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11953,7 +12001,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C2:Q31"/>
+  <dimension ref="C2:Z31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -11968,10 +12016,14 @@
     <col min="12" max="12" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C3" s="179" t="s">
         <v>50</v>
       </c>
@@ -11991,7 +12043,7 @@
       <c r="N3" s="178"/>
       <c r="O3" s="178"/>
     </row>
-    <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
       <c r="D4" s="80" t="s">
         <v>46</v>
@@ -12027,7 +12079,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="3:26" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C5" s="105" t="s">
         <v>51</v>
       </c>
@@ -12056,17 +12108,17 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>3739</v>
+        <v>2323</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>93.474999999999994</v>
+        <v>58.075000000000003</v>
       </c>
       <c r="O5" s="81">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="3:15" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C6" s="107" t="s">
         <v>52</v>
       </c>
@@ -12101,17 +12153,34 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>5073</v>
+        <v>4236</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>126.825</v>
+        <v>105.9</v>
       </c>
       <c r="O6" s="81">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>129</v>
+      </c>
+      <c r="S6" s="130"/>
+      <c r="T6" s="130"/>
+      <c r="U6" s="190">
+        <v>46180</v>
+      </c>
+      <c r="V6" s="191">
+        <v>46180</v>
+      </c>
+      <c r="W6" s="191">
+        <v>46333</v>
+      </c>
+      <c r="X6" s="191">
+        <v>46210</v>
+      </c>
+      <c r="Y6" s="191">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="7" spans="3:26" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C7" s="90"/>
       <c r="K7" s="1" t="s">
         <v>3</v>
@@ -12125,10 +12194,34 @@
         <v>0</v>
       </c>
       <c r="O7" s="81">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>35</v>
+      </c>
+      <c r="S7" s="186" t="s">
+        <v>156</v>
+      </c>
+      <c r="T7" s="186" t="s">
+        <v>155</v>
+      </c>
+      <c r="U7" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="V7" s="186" t="s">
+        <v>153</v>
+      </c>
+      <c r="W7" s="186" t="s">
+        <v>152</v>
+      </c>
+      <c r="X7" s="186" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y7" s="186" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z7" s="186" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C8" s="82" t="s">
         <v>54</v>
       </c>
@@ -12139,17 +12232,40 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>22094</v>
+        <v>26749</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>552.35</v>
+        <v>668.72500000000002</v>
       </c>
       <c r="O8" s="81">
         <v>64</v>
       </c>
-    </row>
-    <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="S8" s="79">
+        <v>120</v>
+      </c>
+      <c r="T8" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="U8" s="185">
+        <v>50</v>
+      </c>
+      <c r="V8" s="79">
+        <v>3</v>
+      </c>
+      <c r="W8" s="79">
+        <v>1</v>
+      </c>
+      <c r="X8" s="79">
+        <v>20</v>
+      </c>
+      <c r="Y8" s="79"/>
+      <c r="Z8" s="79">
+        <f>SUM(U8:Y8)</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C9" s="82" t="s">
         <v>55</v>
       </c>
@@ -12168,17 +12284,42 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>3609</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>90.224999999999994</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O9" s="81">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>135</v>
+      </c>
+      <c r="S9" s="79">
+        <v>120</v>
+      </c>
+      <c r="T9" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" s="185">
+        <v>50</v>
+      </c>
+      <c r="V9" s="79">
+        <v>3</v>
+      </c>
+      <c r="W9" s="79">
+        <v>1</v>
+      </c>
+      <c r="X9" s="79">
+        <v>25</v>
+      </c>
+      <c r="Y9" s="79">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="79">
+        <f t="shared" ref="Z9:Z13" si="1">SUM(U9:Y9)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K10" s="1" t="s">
         <v>6</v>
       </c>
@@ -12186,17 +12327,38 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>27018</v>
+        <v>34795</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>675.45</v>
+        <v>869.875</v>
       </c>
       <c r="O10" s="81">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="S10" s="79">
+        <v>120</v>
+      </c>
+      <c r="T10" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="U10" s="185"/>
+      <c r="V10" s="79">
+        <v>3</v>
+      </c>
+      <c r="W10" s="79">
+        <v>1</v>
+      </c>
+      <c r="X10" s="79">
+        <v>20</v>
+      </c>
+      <c r="Y10" s="79"/>
+      <c r="Z10" s="79">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C11" s="182" t="s">
         <v>62</v>
       </c>
@@ -12212,17 +12374,36 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>55832</v>
+        <v>54914</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>1395.8</v>
+        <v>1372.85</v>
       </c>
       <c r="O11" s="81">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="S11" s="79">
+        <v>70</v>
+      </c>
+      <c r="T11" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="U11" s="185"/>
+      <c r="V11" s="79"/>
+      <c r="W11" s="79"/>
+      <c r="X11" s="79">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="79">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="79">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="93" t="s">
         <v>51</v>
       </c>
@@ -12242,18 +12423,37 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>117365</v>
+        <v>123018</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>2934.125</v>
+        <v>3075.45</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
-        <v>562</v>
-      </c>
-    </row>
-    <row r="13" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
+        <v>657</v>
+      </c>
+      <c r="S12" s="79">
+        <v>70</v>
+      </c>
+      <c r="T12" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="U12" s="185"/>
+      <c r="V12" s="79"/>
+      <c r="W12" s="79"/>
+      <c r="X12" s="79">
+        <v>6</v>
+      </c>
+      <c r="Y12" s="79">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="79">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="3:26" ht="18.5" x14ac:dyDescent="0.35">
       <c r="C13" s="94" t="s">
         <v>52</v>
       </c>
@@ -12268,8 +12468,36 @@
         <f>G12*40</f>
         <v>191440</v>
       </c>
-    </row>
-    <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="S13" s="187" t="s">
+        <v>154</v>
+      </c>
+      <c r="T13" s="187"/>
+      <c r="U13" s="188">
+        <f>SUM(U8:U12)</f>
+        <v>100</v>
+      </c>
+      <c r="V13" s="189">
+        <f t="shared" ref="V13:Y13" si="2">SUM(V8:V12)</f>
+        <v>9</v>
+      </c>
+      <c r="W13" s="189">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="X13" s="189">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y13" s="189">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="1"/>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="3:26" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="K16" s="122" t="s">
         <v>77</v>
       </c>
@@ -12299,7 +12527,7 @@
       </c>
       <c r="O17" s="127">
         <f>N17-M5</f>
-        <v>4515</v>
+        <v>5931</v>
       </c>
       <c r="P17">
         <v>188</v>
@@ -12322,13 +12550,13 @@
       </c>
       <c r="O18" s="127">
         <f>N18-M6</f>
-        <v>3745</v>
+        <v>4582</v>
       </c>
       <c r="P18">
         <v>109</v>
       </c>
       <c r="Q18">
-        <f t="shared" ref="Q18:Q23" si="1">N18/40</f>
+        <f t="shared" ref="Q18:Q23" si="3">N18/40</f>
         <v>220.45</v>
       </c>
     </row>
@@ -12347,14 +12575,14 @@
         <v>0</v>
       </c>
       <c r="O19" s="127">
-        <f t="shared" ref="O19:O23" si="2">N19-M7</f>
+        <f t="shared" ref="O19:O23" si="4">N19-M7</f>
         <v>0</v>
       </c>
       <c r="P19">
         <v>33</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -12377,14 +12605,14 @@
         <v>38828</v>
       </c>
       <c r="O20" s="127">
-        <f t="shared" si="2"/>
-        <v>16734</v>
+        <f t="shared" si="4"/>
+        <v>12079</v>
       </c>
       <c r="P20">
         <v>64</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>970.7</v>
       </c>
     </row>
@@ -12415,14 +12643,14 @@
         <v>11781</v>
       </c>
       <c r="O21" s="127">
-        <f t="shared" si="2"/>
-        <v>8172</v>
+        <f t="shared" si="4"/>
+        <v>11780</v>
       </c>
       <c r="P21">
         <v>133</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>294.52499999999998</v>
       </c>
     </row>
@@ -12437,7 +12665,7 @@
         <v>9586</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" ref="G22:G28" si="3">F22/40</f>
+        <f t="shared" ref="G22:G28" si="5">F22/40</f>
         <v>239.65</v>
       </c>
       <c r="H22" s="81">
@@ -12454,14 +12682,14 @@
         <v>45343</v>
       </c>
       <c r="O22" s="127">
-        <f t="shared" si="2"/>
-        <v>18325</v>
+        <f t="shared" si="4"/>
+        <v>10548</v>
       </c>
       <c r="P22">
         <v>15</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1133.575</v>
       </c>
     </row>
@@ -12476,7 +12704,7 @@
         <v>10668</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>266.7</v>
       </c>
       <c r="H23" s="81">
@@ -12493,14 +12721,14 @@
         <v>64778</v>
       </c>
       <c r="O23" s="127">
-        <f t="shared" si="2"/>
-        <v>8946</v>
+        <f t="shared" si="4"/>
+        <v>9864</v>
       </c>
       <c r="P23">
         <v>20</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1619.45</v>
       </c>
     </row>
@@ -12513,7 +12741,7 @@
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H24" s="81">
@@ -12533,7 +12761,7 @@
       </c>
       <c r="O24" s="122">
         <f>SUM(O17:O23)</f>
-        <v>60437</v>
+        <v>54784</v>
       </c>
     </row>
     <row r="25" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12547,7 +12775,7 @@
         <v>10905</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>272.625</v>
       </c>
       <c r="H25" s="81">
@@ -12567,7 +12795,7 @@
       </c>
       <c r="O25" s="122">
         <f>O24/40</f>
-        <v>1510.925</v>
+        <v>1369.6</v>
       </c>
     </row>
     <row r="26" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12581,7 +12809,7 @@
         <v>5595</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>139.875</v>
       </c>
       <c r="H26" s="81">
@@ -12599,7 +12827,7 @@
         <v>7110</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>177.75</v>
       </c>
       <c r="H27" s="81">
@@ -12617,7 +12845,7 @@
         <v>66124</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1653.1</v>
       </c>
       <c r="H28" s="81">
@@ -12660,7 +12888,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="S13:T13"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C11:D11"/>
@@ -13169,7 +13398,10 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="9:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="8:11" x14ac:dyDescent="0.35">
+      <c r="H33">
+        <v>14</v>
+      </c>
       <c r="I33" s="79" t="s">
         <v>142</v>
       </c>
@@ -13180,7 +13412,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="9:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="8:11" x14ac:dyDescent="0.35">
       <c r="I34" s="79" t="s">
         <v>144</v>
       </c>
@@ -13191,7 +13423,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="9:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="8:11" x14ac:dyDescent="0.35">
       <c r="I35" s="79" t="s">
         <v>147</v>
       </c>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776F4FE7-7A92-46BD-A189-7EC19653CEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7992348-113E-45EB-A5EB-9F9BB45229D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1394,7 +1394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1780,6 +1780,51 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1819,41 +1864,8 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1874,27 +1886,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2432,14 +2423,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="166">
+      <c r="B1" s="156">
         <f ca="1">TODAY()</f>
         <v>46218</v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2461,10 +2452,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="178" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="157" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2497,13 +2488,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="155"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158" t="s">
+      <c r="M2" s="170"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="159"/>
+      <c r="Q2" s="174"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2522,8 +2513,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="163"/>
-      <c r="B3" s="168"/>
+      <c r="A3" s="178"/>
+      <c r="B3" s="158"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2554,29 +2545,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="161"/>
-      <c r="O3" s="162"/>
+      <c r="N3" s="176"/>
+      <c r="O3" s="177"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="170" t="s">
+      <c r="R3" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="171"/>
-      <c r="T3" s="171"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="173" t="s">
+      <c r="S3" s="161"/>
+      <c r="T3" s="161"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="163" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="175"/>
+      <c r="W3" s="164"/>
+      <c r="X3" s="164"/>
+      <c r="Y3" s="165"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="163"/>
-      <c r="B4" s="169"/>
+      <c r="A4" s="178"/>
+      <c r="B4" s="159"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11523,10 +11514,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="176" t="s">
+      <c r="B132" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="177"/>
+      <c r="C132" s="167"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11790,10 +11781,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="164" t="s">
+      <c r="B136" s="179" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="165"/>
+      <c r="C136" s="180"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11884,10 +11875,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="153" t="s">
+      <c r="B137" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="154"/>
+      <c r="C137" s="169"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -11979,17 +11970,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12024,24 +12015,24 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="183" t="s">
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="184"/>
-      <c r="K3" s="178" t="s">
+      <c r="I3" s="188"/>
+      <c r="K3" s="182" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="178"/>
-      <c r="O3" s="178"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12084,22 +12075,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>510</v>
+        <v>608</v>
       </c>
       <c r="E5" s="79">
-        <v>542</v>
+        <v>664</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>1352</v>
+        <v>1572</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>1352</v>
+        <v>1572</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12124,11 +12115,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>20400</v>
+        <v>24320</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>21680</v>
+        <v>26560</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12136,7 +12127,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>54080</v>
+        <v>62880</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12144,7 +12135,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>54080</v>
+        <v>62880</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12164,19 +12155,19 @@
       </c>
       <c r="S6" s="130"/>
       <c r="T6" s="130"/>
-      <c r="U6" s="190">
+      <c r="U6" s="155">
         <v>46180</v>
       </c>
-      <c r="V6" s="191">
+      <c r="V6" s="155">
         <v>46180</v>
       </c>
-      <c r="W6" s="191">
+      <c r="W6" s="155">
         <v>46333</v>
       </c>
-      <c r="X6" s="191">
+      <c r="X6" s="155">
         <v>46210</v>
       </c>
-      <c r="Y6" s="191">
+      <c r="Y6" s="155">
         <v>46210</v>
       </c>
     </row>
@@ -12196,28 +12187,28 @@
       <c r="O7" s="81">
         <v>35</v>
       </c>
-      <c r="S7" s="186" t="s">
+      <c r="S7" s="154" t="s">
         <v>156</v>
       </c>
-      <c r="T7" s="186" t="s">
+      <c r="T7" s="154" t="s">
         <v>155</v>
       </c>
       <c r="U7" s="77" t="s">
         <v>149</v>
       </c>
-      <c r="V7" s="186" t="s">
+      <c r="V7" s="154" t="s">
         <v>153</v>
       </c>
-      <c r="W7" s="186" t="s">
+      <c r="W7" s="154" t="s">
         <v>152</v>
       </c>
-      <c r="X7" s="186" t="s">
+      <c r="X7" s="154" t="s">
         <v>152</v>
       </c>
-      <c r="Y7" s="186" t="s">
+      <c r="Y7" s="154" t="s">
         <v>152</v>
       </c>
-      <c r="Z7" s="186" t="s">
+      <c r="Z7" s="154" t="s">
         <v>154</v>
       </c>
     </row>
@@ -12247,7 +12238,7 @@
       <c r="T8" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="U8" s="185">
+      <c r="U8" s="153">
         <v>50</v>
       </c>
       <c r="V8" s="79">
@@ -12271,11 +12262,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-510</v>
+        <v>-608</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-542</v>
+        <v>-664</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12299,7 +12290,7 @@
       <c r="T9" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="185">
+      <c r="U9" s="153">
         <v>50</v>
       </c>
       <c r="V9" s="79">
@@ -12342,7 +12333,7 @@
       <c r="T10" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="U10" s="185"/>
+      <c r="U10" s="153"/>
       <c r="V10" s="79">
         <v>3</v>
       </c>
@@ -12359,14 +12350,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="182" t="s">
+      <c r="C11" s="186" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="182"/>
-      <c r="F11" s="182" t="s">
+      <c r="D11" s="186"/>
+      <c r="F11" s="186" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="182"/>
+      <c r="G11" s="186"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12389,7 +12380,7 @@
       <c r="T11" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="U11" s="185"/>
+      <c r="U11" s="153"/>
       <c r="V11" s="79"/>
       <c r="W11" s="79"/>
       <c r="X11" s="79">
@@ -12415,7 +12406,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>4786</v>
+        <v>5006</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12439,7 +12430,7 @@
       <c r="T12" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="U12" s="185"/>
+      <c r="U12" s="153"/>
       <c r="V12" s="79"/>
       <c r="W12" s="79"/>
       <c r="X12" s="79">
@@ -12466,29 +12457,29 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>191440</v>
-      </c>
-      <c r="S13" s="187" t="s">
+        <v>200240</v>
+      </c>
+      <c r="S13" s="181" t="s">
         <v>154</v>
       </c>
-      <c r="T13" s="187"/>
-      <c r="U13" s="188">
+      <c r="T13" s="181"/>
+      <c r="U13" s="153">
         <f>SUM(U8:U12)</f>
         <v>100</v>
       </c>
-      <c r="V13" s="189">
+      <c r="V13" s="79">
         <f t="shared" ref="V13:Y13" si="2">SUM(V8:V12)</f>
         <v>9</v>
       </c>
-      <c r="W13" s="189">
+      <c r="W13" s="79">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="X13" s="189">
+      <c r="X13" s="79">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="Y13" s="189">
+      <c r="Y13" s="79">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -12587,13 +12578,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="178" t="s">
+      <c r="D20" s="182" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="178"/>
-      <c r="F20" s="178"/>
-      <c r="G20" s="178"/>
-      <c r="H20" s="178"/>
+      <c r="E20" s="182"/>
+      <c r="F20" s="182"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="182"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7992348-113E-45EB-A5EB-9F9BB45229D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4394095D-65EB-441D-A30D-A8EE46B99386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1789,6 +1789,45 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1823,45 +1862,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2423,14 +2423,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="156">
+      <c r="B1" s="169">
         <f ca="1">TODAY()</f>
-        <v>46218</v>
-      </c>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
+        <v>46219</v>
+      </c>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2452,10 +2452,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="166" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="170" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2488,13 +2488,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="170"/>
-      <c r="N2" s="171"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="173" t="s">
+      <c r="M2" s="158"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="160"/>
+      <c r="P2" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="174"/>
+      <c r="Q2" s="162"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2513,8 +2513,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="178"/>
-      <c r="B3" s="158"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="171"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2545,29 +2545,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="175" t="s">
+      <c r="M3" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="176"/>
-      <c r="O3" s="177"/>
+      <c r="N3" s="164"/>
+      <c r="O3" s="165"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="160" t="s">
+      <c r="R3" s="173" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="161"/>
-      <c r="T3" s="161"/>
-      <c r="U3" s="162"/>
-      <c r="V3" s="163" t="s">
+      <c r="S3" s="174"/>
+      <c r="T3" s="174"/>
+      <c r="U3" s="175"/>
+      <c r="V3" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="164"/>
-      <c r="X3" s="164"/>
-      <c r="Y3" s="165"/>
+      <c r="W3" s="177"/>
+      <c r="X3" s="177"/>
+      <c r="Y3" s="178"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="178"/>
-      <c r="B4" s="159"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="172"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11514,10 +11514,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="166" t="s">
+      <c r="B132" s="179" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="167"/>
+      <c r="C132" s="180"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11781,10 +11781,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="179" t="s">
+      <c r="B136" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="180"/>
+      <c r="C136" s="168"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11875,10 +11875,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="168" t="s">
+      <c r="B137" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="169"/>
+      <c r="C137" s="157"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -11970,17 +11970,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12075,7 +12075,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="E5" s="79">
         <v>664</v>
@@ -12085,12 +12085,12 @@
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>1572</v>
+        <v>1589</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>1572</v>
+        <v>1589</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>24320</v>
+        <v>25000</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>62880</v>
+        <v>63560</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>62880</v>
+        <v>63560</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-608</v>
+        <v>-625</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>5006</v>
+        <v>5023</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>200240</v>
+        <v>200920</v>
       </c>
       <c r="S13" s="181" t="s">
         <v>154</v>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4394095D-65EB-441D-A30D-A8EE46B99386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FA2408-9757-4C0A-90F5-6C6B251B00A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,15 @@
     <sheet name="S-P" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet2!$H$1:$M$40</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="168">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -436,9 +439,6 @@
     <t>Sana C &amp; C Nespark Society</t>
   </si>
   <si>
-    <t>Nagina</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nagina </t>
   </si>
   <si>
@@ -494,6 +494,42 @@
   </si>
   <si>
     <t>Gram</t>
+  </si>
+  <si>
+    <t>Rainbow Shakhupura</t>
+  </si>
+  <si>
+    <t>Rainbow Gujjrawala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown </t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Execution </t>
+  </si>
+  <si>
+    <t>Received</t>
+  </si>
+  <si>
+    <t>In Pcs</t>
+  </si>
+  <si>
+    <t>Nagina Asif SB</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>Rainbow Shadbagh</t>
   </si>
 </sst>
 </file>
@@ -505,7 +541,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,6 +633,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -667,7 +710,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1394,7 +1437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1721,9 +1764,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1736,12 +1776,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1752,9 +1786,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1774,12 +1805,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1789,6 +1814,42 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1828,42 +1889,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1887,6 +1912,30 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2237,7 +2286,7 @@
       <c r="D9" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="129" t="s">
+      <c r="E9" s="128" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="96" t="s">
@@ -2254,7 +2303,7 @@
       <c r="D10" s="92">
         <v>3520247902365</v>
       </c>
-      <c r="E10" s="130"/>
+      <c r="E10" s="129"/>
       <c r="F10">
         <v>10000</v>
       </c>
@@ -2265,7 +2314,7 @@
       </c>
       <c r="C11" s="79"/>
       <c r="D11" s="79"/>
-      <c r="E11" s="130"/>
+      <c r="E11" s="129"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="79" t="s">
@@ -2277,7 +2326,7 @@
       <c r="D12" s="92">
         <v>300426949714</v>
       </c>
-      <c r="E12" s="130"/>
+      <c r="E12" s="129"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="79" t="s">
@@ -2289,7 +2338,7 @@
       <c r="D13" s="92">
         <v>3277876126916</v>
       </c>
-      <c r="E13" s="130"/>
+      <c r="E13" s="129"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="79" t="s">
@@ -2301,7 +2350,7 @@
       <c r="D14" s="92">
         <v>3520255124113</v>
       </c>
-      <c r="E14" s="130"/>
+      <c r="E14" s="129"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="79" t="s">
@@ -2313,7 +2362,7 @@
       <c r="D15" s="92">
         <v>3520255124113</v>
       </c>
-      <c r="E15" s="130"/>
+      <c r="E15" s="129"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="79" t="s">
@@ -2325,7 +2374,7 @@
       <c r="D16" s="92">
         <v>3520268948847</v>
       </c>
-      <c r="E16" s="130"/>
+      <c r="E16" s="129"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="79" t="s">
@@ -2335,7 +2384,7 @@
         <v>44</v>
       </c>
       <c r="D17" s="79"/>
-      <c r="E17" s="130"/>
+      <c r="E17" s="129"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="79" t="s">
@@ -2347,63 +2396,63 @@
       <c r="D18" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="130"/>
+      <c r="E18" s="129"/>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="131" t="s">
+      <c r="B19" s="130" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="130" t="s">
+      <c r="C19" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="129"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="131" t="s">
+      <c r="B20" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="130"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="129"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="131" t="s">
+      <c r="B21" s="130" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="130"/>
-      <c r="D21" s="130"/>
-      <c r="E21" s="130"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="129"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="131" t="s">
+      <c r="B22" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="131" t="s">
+      <c r="B23" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="130" t="s">
+      <c r="C23" s="129" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="132">
+      <c r="D23" s="131">
         <v>3277876231301</v>
       </c>
-      <c r="E23" s="130"/>
+      <c r="E23" s="129"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="131" t="s">
+      <c r="B24" s="130" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="130" t="s">
+      <c r="C24" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="129" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2423,14 +2472,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="169">
+      <c r="B1" s="150">
         <f ca="1">TODAY()</f>
-        <v>46219</v>
-      </c>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
+        <v>46220</v>
+      </c>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2452,10 +2501,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="172" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="151" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2488,13 +2537,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="158"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="161" t="s">
+      <c r="M2" s="164"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="166"/>
+      <c r="P2" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="162"/>
+      <c r="Q2" s="168"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2513,8 +2562,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="166"/>
-      <c r="B3" s="171"/>
+      <c r="A3" s="172"/>
+      <c r="B3" s="152"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2545,29 +2594,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="163" t="s">
+      <c r="M3" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="164"/>
-      <c r="O3" s="165"/>
+      <c r="N3" s="170"/>
+      <c r="O3" s="171"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="173" t="s">
+      <c r="R3" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="175"/>
-      <c r="V3" s="176" t="s">
+      <c r="S3" s="155"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="156"/>
+      <c r="V3" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="177"/>
-      <c r="X3" s="177"/>
-      <c r="Y3" s="178"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="159"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="166"/>
-      <c r="B4" s="172"/>
+      <c r="A4" s="172"/>
+      <c r="B4" s="153"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2645,26 +2694,26 @@
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="140" t="s">
+      <c r="C5" s="136" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="141"/>
-      <c r="E5" s="142"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="138"/>
       <c r="F5" s="38"/>
-      <c r="G5" s="143">
+      <c r="G5" s="139">
         <v>40</v>
       </c>
-      <c r="H5" s="142">
+      <c r="H5" s="138">
         <v>40</v>
       </c>
       <c r="I5" s="38"/>
-      <c r="J5" s="143">
+      <c r="J5" s="139">
         <v>40</v>
       </c>
-      <c r="K5" s="142">
+      <c r="K5" s="138">
         <v>40</v>
       </c>
-      <c r="L5" s="144">
+      <c r="L5" s="140">
         <v>40</v>
       </c>
       <c r="M5" s="37">
@@ -5310,7 +5359,7 @@
         <v>34</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D38" s="74">
         <v>2000</v>
@@ -5383,26 +5432,26 @@
       <c r="B39" s="47">
         <v>35</v>
       </c>
-      <c r="C39" s="145" t="s">
+      <c r="C39" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="146"/>
-      <c r="E39" s="147"/>
-      <c r="F39" s="148"/>
-      <c r="G39" s="149">
+      <c r="D39" s="142"/>
+      <c r="E39" s="143"/>
+      <c r="F39" s="144"/>
+      <c r="G39" s="145">
         <v>20</v>
       </c>
-      <c r="H39" s="147">
+      <c r="H39" s="143">
         <v>80</v>
       </c>
-      <c r="I39" s="150"/>
-      <c r="J39" s="149">
+      <c r="I39" s="146"/>
+      <c r="J39" s="145">
         <v>20</v>
       </c>
-      <c r="K39" s="147">
+      <c r="K39" s="143">
         <v>80</v>
       </c>
-      <c r="L39" s="148">
+      <c r="L39" s="144">
         <v>80</v>
       </c>
       <c r="M39" s="48">
@@ -5465,20 +5514,20 @@
       <c r="B40" s="47">
         <v>36</v>
       </c>
-      <c r="C40" s="145" t="s">
-        <v>139</v>
-      </c>
-      <c r="D40" s="146"/>
-      <c r="E40" s="147"/>
-      <c r="F40" s="148"/>
-      <c r="G40" s="149"/>
-      <c r="H40" s="147"/>
-      <c r="I40" s="150"/>
-      <c r="J40" s="149">
+      <c r="C40" s="141" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="142"/>
+      <c r="E40" s="143"/>
+      <c r="F40" s="144"/>
+      <c r="G40" s="145"/>
+      <c r="H40" s="143"/>
+      <c r="I40" s="146"/>
+      <c r="J40" s="145">
         <v>200</v>
       </c>
-      <c r="K40" s="147"/>
-      <c r="L40" s="148"/>
+      <c r="K40" s="143"/>
+      <c r="L40" s="144"/>
       <c r="M40" s="48">
         <f t="shared" si="68"/>
         <v>5</v>
@@ -5539,28 +5588,28 @@
       <c r="B41" s="47">
         <v>37</v>
       </c>
-      <c r="C41" s="145" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="146">
+      <c r="C41" s="141" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="142">
         <v>160</v>
       </c>
-      <c r="E41" s="147"/>
-      <c r="F41" s="148"/>
-      <c r="G41" s="149">
+      <c r="E41" s="143"/>
+      <c r="F41" s="144"/>
+      <c r="G41" s="145">
         <v>120</v>
       </c>
-      <c r="H41" s="147">
+      <c r="H41" s="143">
         <v>120</v>
       </c>
-      <c r="I41" s="150"/>
-      <c r="J41" s="149">
+      <c r="I41" s="146"/>
+      <c r="J41" s="145">
         <v>120</v>
       </c>
-      <c r="K41" s="147">
+      <c r="K41" s="143">
         <v>120</v>
       </c>
-      <c r="L41" s="148">
+      <c r="L41" s="144">
         <v>200</v>
       </c>
       <c r="M41" s="48">
@@ -5623,24 +5672,24 @@
       <c r="B42" s="47">
         <v>38</v>
       </c>
-      <c r="C42" s="145" t="s">
-        <v>141</v>
-      </c>
-      <c r="D42" s="146">
+      <c r="C42" s="141" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="142">
         <v>80</v>
       </c>
-      <c r="E42" s="147"/>
-      <c r="F42" s="148"/>
-      <c r="G42" s="149"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="150"/>
-      <c r="J42" s="149">
+      <c r="E42" s="143"/>
+      <c r="F42" s="144"/>
+      <c r="G42" s="145"/>
+      <c r="H42" s="143"/>
+      <c r="I42" s="146"/>
+      <c r="J42" s="145">
         <v>80</v>
       </c>
-      <c r="K42" s="147">
+      <c r="K42" s="143">
         <v>80</v>
       </c>
-      <c r="L42" s="148">
+      <c r="L42" s="144">
         <v>80</v>
       </c>
       <c r="M42" s="48">
@@ -5703,22 +5752,22 @@
       <c r="B43" s="47">
         <v>39</v>
       </c>
-      <c r="C43" s="145" t="s">
+      <c r="C43" s="141" t="s">
         <v>135</v>
       </c>
-      <c r="D43" s="146"/>
-      <c r="E43" s="147"/>
-      <c r="F43" s="148"/>
-      <c r="G43" s="149"/>
-      <c r="H43" s="147"/>
-      <c r="I43" s="150"/>
-      <c r="J43" s="149">
+      <c r="D43" s="142"/>
+      <c r="E43" s="143"/>
+      <c r="F43" s="144"/>
+      <c r="G43" s="145"/>
+      <c r="H43" s="143"/>
+      <c r="I43" s="146"/>
+      <c r="J43" s="145">
         <v>40</v>
       </c>
-      <c r="K43" s="147">
+      <c r="K43" s="143">
         <v>40</v>
       </c>
-      <c r="L43" s="148">
+      <c r="L43" s="144">
         <v>80</v>
       </c>
       <c r="M43" s="48">
@@ -5781,22 +5830,22 @@
       <c r="B44" s="47">
         <v>40</v>
       </c>
-      <c r="C44" s="145" t="s">
-        <v>145</v>
-      </c>
-      <c r="D44" s="146"/>
-      <c r="E44" s="147"/>
-      <c r="F44" s="148"/>
-      <c r="G44" s="149"/>
-      <c r="H44" s="147">
+      <c r="C44" s="141" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="142"/>
+      <c r="E44" s="143"/>
+      <c r="F44" s="144"/>
+      <c r="G44" s="145"/>
+      <c r="H44" s="143">
         <v>80</v>
       </c>
-      <c r="I44" s="150"/>
-      <c r="J44" s="149">
+      <c r="I44" s="146"/>
+      <c r="J44" s="145">
         <v>40</v>
       </c>
-      <c r="K44" s="147"/>
-      <c r="L44" s="148">
+      <c r="K44" s="143"/>
+      <c r="L44" s="144">
         <v>40</v>
       </c>
       <c r="M44" s="48">
@@ -5860,7 +5909,7 @@
         <v>41</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D45" s="74"/>
       <c r="E45" s="75"/>
@@ -6493,11 +6542,11 @@
       <c r="F57" s="75"/>
       <c r="G57" s="75"/>
       <c r="H57" s="75"/>
-      <c r="I57" s="135"/>
+      <c r="I57" s="132"/>
       <c r="J57" s="75"/>
       <c r="K57" s="75"/>
       <c r="L57" s="75"/>
-      <c r="M57" s="138">
+      <c r="M57" s="135">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
@@ -6543,11 +6592,11 @@
       <c r="F58" s="75"/>
       <c r="G58" s="75"/>
       <c r="H58" s="75"/>
-      <c r="I58" s="135"/>
+      <c r="I58" s="132"/>
       <c r="J58" s="75"/>
       <c r="K58" s="75"/>
       <c r="L58" s="75"/>
-      <c r="M58" s="138">
+      <c r="M58" s="135">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
@@ -6593,11 +6642,11 @@
       <c r="F59" s="75"/>
       <c r="G59" s="75"/>
       <c r="H59" s="75"/>
-      <c r="I59" s="135"/>
+      <c r="I59" s="132"/>
       <c r="J59" s="75"/>
       <c r="K59" s="75"/>
       <c r="L59" s="75"/>
-      <c r="M59" s="138">
+      <c r="M59" s="135">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
@@ -6643,11 +6692,11 @@
       <c r="F60" s="75"/>
       <c r="G60" s="75"/>
       <c r="H60" s="75"/>
-      <c r="I60" s="135"/>
+      <c r="I60" s="132"/>
       <c r="J60" s="75"/>
       <c r="K60" s="75"/>
       <c r="L60" s="75"/>
-      <c r="M60" s="138">
+      <c r="M60" s="135">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
@@ -6705,17 +6754,17 @@
       <c r="B61" s="47">
         <v>57</v>
       </c>
-      <c r="C61" s="136"/>
+      <c r="C61" s="133"/>
       <c r="D61" s="75"/>
       <c r="E61" s="75"/>
       <c r="F61" s="75"/>
       <c r="G61" s="75"/>
       <c r="H61" s="75"/>
-      <c r="I61" s="135"/>
+      <c r="I61" s="132"/>
       <c r="J61" s="75"/>
       <c r="K61" s="75"/>
       <c r="L61" s="75"/>
-      <c r="M61" s="138">
+      <c r="M61" s="135">
         <f t="shared" ref="M61:M83" si="81">SUM(D61:L61)/40</f>
         <v>0</v>
       </c>
@@ -6773,17 +6822,17 @@
       <c r="B62" s="47">
         <v>58</v>
       </c>
-      <c r="C62" s="136"/>
+      <c r="C62" s="133"/>
       <c r="D62" s="75"/>
       <c r="E62" s="75"/>
       <c r="F62" s="75"/>
       <c r="G62" s="75"/>
       <c r="H62" s="75"/>
-      <c r="I62" s="135"/>
+      <c r="I62" s="132"/>
       <c r="J62" s="75"/>
       <c r="K62" s="75"/>
       <c r="L62" s="75"/>
-      <c r="M62" s="138">
+      <c r="M62" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6841,17 +6890,17 @@
       <c r="B63" s="47">
         <v>59</v>
       </c>
-      <c r="C63" s="136"/>
+      <c r="C63" s="133"/>
       <c r="D63" s="75"/>
       <c r="E63" s="75"/>
       <c r="F63" s="75"/>
       <c r="G63" s="75"/>
       <c r="H63" s="75"/>
-      <c r="I63" s="135"/>
+      <c r="I63" s="132"/>
       <c r="J63" s="75"/>
       <c r="K63" s="75"/>
       <c r="L63" s="75"/>
-      <c r="M63" s="138">
+      <c r="M63" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6909,17 +6958,17 @@
       <c r="B64" s="47">
         <v>60</v>
       </c>
-      <c r="C64" s="136"/>
+      <c r="C64" s="133"/>
       <c r="D64" s="75"/>
       <c r="E64" s="75"/>
       <c r="F64" s="75"/>
       <c r="G64" s="75"/>
       <c r="H64" s="75"/>
-      <c r="I64" s="135"/>
+      <c r="I64" s="132"/>
       <c r="J64" s="75"/>
       <c r="K64" s="75"/>
       <c r="L64" s="75"/>
-      <c r="M64" s="138">
+      <c r="M64" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -6977,17 +7026,17 @@
       <c r="B65" s="47">
         <v>61</v>
       </c>
-      <c r="C65" s="136"/>
+      <c r="C65" s="133"/>
       <c r="D65" s="75"/>
       <c r="E65" s="75"/>
       <c r="F65" s="75"/>
       <c r="G65" s="75"/>
       <c r="H65" s="75"/>
-      <c r="I65" s="135"/>
+      <c r="I65" s="132"/>
       <c r="J65" s="75"/>
       <c r="K65" s="75"/>
       <c r="L65" s="75"/>
-      <c r="M65" s="138">
+      <c r="M65" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7045,17 +7094,17 @@
       <c r="B66" s="47">
         <v>62</v>
       </c>
-      <c r="C66" s="136"/>
+      <c r="C66" s="133"/>
       <c r="D66" s="75"/>
       <c r="E66" s="75"/>
       <c r="F66" s="75"/>
       <c r="G66" s="75"/>
       <c r="H66" s="75"/>
-      <c r="I66" s="135"/>
+      <c r="I66" s="132"/>
       <c r="J66" s="75"/>
       <c r="K66" s="75"/>
       <c r="L66" s="75"/>
-      <c r="M66" s="138">
+      <c r="M66" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7113,17 +7162,17 @@
       <c r="B67" s="47">
         <v>63</v>
       </c>
-      <c r="C67" s="136"/>
+      <c r="C67" s="133"/>
       <c r="D67" s="75"/>
       <c r="E67" s="75"/>
       <c r="F67" s="75"/>
       <c r="G67" s="75"/>
       <c r="H67" s="75"/>
-      <c r="I67" s="135"/>
+      <c r="I67" s="132"/>
       <c r="J67" s="75"/>
       <c r="K67" s="75"/>
       <c r="L67" s="75"/>
-      <c r="M67" s="138">
+      <c r="M67" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7181,17 +7230,17 @@
       <c r="B68" s="47">
         <v>64</v>
       </c>
-      <c r="C68" s="136"/>
+      <c r="C68" s="133"/>
       <c r="D68" s="75"/>
       <c r="E68" s="75"/>
       <c r="F68" s="75"/>
       <c r="G68" s="75"/>
       <c r="H68" s="75"/>
-      <c r="I68" s="135"/>
+      <c r="I68" s="132"/>
       <c r="J68" s="75"/>
       <c r="K68" s="75"/>
       <c r="L68" s="75"/>
-      <c r="M68" s="138">
+      <c r="M68" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7249,17 +7298,17 @@
       <c r="B69" s="47">
         <v>65</v>
       </c>
-      <c r="C69" s="136"/>
+      <c r="C69" s="133"/>
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
       <c r="G69" s="75"/>
       <c r="H69" s="75"/>
-      <c r="I69" s="135"/>
+      <c r="I69" s="132"/>
       <c r="J69" s="75"/>
       <c r="K69" s="75"/>
       <c r="L69" s="75"/>
-      <c r="M69" s="138">
+      <c r="M69" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7317,17 +7366,17 @@
       <c r="B70" s="47">
         <v>66</v>
       </c>
-      <c r="C70" s="136"/>
+      <c r="C70" s="133"/>
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
       <c r="G70" s="75"/>
       <c r="H70" s="75"/>
-      <c r="I70" s="135"/>
+      <c r="I70" s="132"/>
       <c r="J70" s="75"/>
       <c r="K70" s="75"/>
       <c r="L70" s="75"/>
-      <c r="M70" s="138">
+      <c r="M70" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7385,17 +7434,17 @@
       <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="136"/>
+      <c r="C71" s="133"/>
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
       <c r="G71" s="75"/>
       <c r="H71" s="75"/>
-      <c r="I71" s="135"/>
+      <c r="I71" s="132"/>
       <c r="J71" s="75"/>
       <c r="K71" s="75"/>
       <c r="L71" s="75"/>
-      <c r="M71" s="138">
+      <c r="M71" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7453,17 +7502,17 @@
       <c r="B72" s="47">
         <v>68</v>
       </c>
-      <c r="C72" s="136"/>
+      <c r="C72" s="133"/>
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
       <c r="G72" s="75"/>
       <c r="H72" s="75"/>
-      <c r="I72" s="135"/>
+      <c r="I72" s="132"/>
       <c r="J72" s="75"/>
       <c r="K72" s="75"/>
       <c r="L72" s="75"/>
-      <c r="M72" s="138">
+      <c r="M72" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7521,17 +7570,17 @@
       <c r="B73" s="47">
         <v>69</v>
       </c>
-      <c r="C73" s="136"/>
+      <c r="C73" s="133"/>
       <c r="D73" s="75"/>
       <c r="E73" s="75"/>
       <c r="F73" s="75"/>
       <c r="G73" s="75"/>
       <c r="H73" s="75"/>
-      <c r="I73" s="135"/>
+      <c r="I73" s="132"/>
       <c r="J73" s="75"/>
       <c r="K73" s="75"/>
       <c r="L73" s="75"/>
-      <c r="M73" s="138">
+      <c r="M73" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7589,17 +7638,17 @@
       <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="137"/>
+      <c r="C74" s="134"/>
       <c r="D74" s="75"/>
       <c r="E74" s="75"/>
       <c r="F74" s="50"/>
       <c r="G74" s="75"/>
       <c r="H74" s="75"/>
-      <c r="I74" s="135"/>
+      <c r="I74" s="132"/>
       <c r="J74" s="75"/>
       <c r="K74" s="75"/>
       <c r="L74" s="75"/>
-      <c r="M74" s="138">
+      <c r="M74" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7657,17 +7706,17 @@
       <c r="B75" s="47">
         <v>71</v>
       </c>
-      <c r="C75" s="137"/>
+      <c r="C75" s="134"/>
       <c r="D75" s="75"/>
       <c r="E75" s="50"/>
       <c r="F75" s="50"/>
       <c r="G75" s="75"/>
       <c r="H75" s="75"/>
-      <c r="I75" s="135"/>
+      <c r="I75" s="132"/>
       <c r="J75" s="75"/>
       <c r="K75" s="75"/>
       <c r="L75" s="75"/>
-      <c r="M75" s="138">
+      <c r="M75" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7725,17 +7774,17 @@
       <c r="B76" s="47">
         <v>72</v>
       </c>
-      <c r="C76" s="137"/>
+      <c r="C76" s="134"/>
       <c r="D76" s="75"/>
       <c r="E76" s="50"/>
       <c r="F76" s="50"/>
       <c r="G76" s="75"/>
       <c r="H76" s="75"/>
-      <c r="I76" s="135"/>
+      <c r="I76" s="132"/>
       <c r="J76" s="75"/>
       <c r="K76" s="75"/>
       <c r="L76" s="75"/>
-      <c r="M76" s="138">
+      <c r="M76" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7793,17 +7842,17 @@
       <c r="B77" s="47">
         <v>73</v>
       </c>
-      <c r="C77" s="137"/>
+      <c r="C77" s="134"/>
       <c r="D77" s="75"/>
       <c r="E77" s="50"/>
       <c r="F77" s="50"/>
       <c r="G77" s="50"/>
       <c r="H77" s="50"/>
-      <c r="I77" s="138"/>
+      <c r="I77" s="135"/>
       <c r="J77" s="50"/>
       <c r="K77" s="50"/>
       <c r="L77" s="50"/>
-      <c r="M77" s="138">
+      <c r="M77" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7861,17 +7910,17 @@
       <c r="B78" s="47">
         <v>74</v>
       </c>
-      <c r="C78" s="137"/>
+      <c r="C78" s="134"/>
       <c r="D78" s="75"/>
       <c r="E78" s="50"/>
       <c r="F78" s="50"/>
       <c r="G78" s="50"/>
       <c r="H78" s="50"/>
-      <c r="I78" s="138"/>
+      <c r="I78" s="135"/>
       <c r="J78" s="50"/>
       <c r="K78" s="50"/>
       <c r="L78" s="50"/>
-      <c r="M78" s="138">
+      <c r="M78" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7929,17 +7978,17 @@
       <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="136"/>
+      <c r="C79" s="133"/>
       <c r="D79" s="50"/>
       <c r="E79" s="50"/>
       <c r="F79" s="50"/>
       <c r="G79" s="50"/>
       <c r="H79" s="50"/>
-      <c r="I79" s="138"/>
+      <c r="I79" s="135"/>
       <c r="J79" s="50"/>
       <c r="K79" s="50"/>
       <c r="L79" s="50"/>
-      <c r="M79" s="138">
+      <c r="M79" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7997,17 +8046,17 @@
       <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="136"/>
+      <c r="C80" s="133"/>
       <c r="D80" s="50"/>
       <c r="E80" s="50"/>
       <c r="F80" s="50"/>
       <c r="G80" s="50"/>
       <c r="H80" s="50"/>
-      <c r="I80" s="138"/>
+      <c r="I80" s="135"/>
       <c r="J80" s="50"/>
       <c r="K80" s="50"/>
       <c r="L80" s="50"/>
-      <c r="M80" s="138">
+      <c r="M80" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8065,17 +8114,17 @@
       <c r="B81" s="47">
         <v>77</v>
       </c>
-      <c r="C81" s="136"/>
+      <c r="C81" s="133"/>
       <c r="D81" s="50"/>
       <c r="E81" s="50"/>
       <c r="F81" s="50"/>
       <c r="G81" s="50"/>
       <c r="H81" s="50"/>
-      <c r="I81" s="138"/>
+      <c r="I81" s="135"/>
       <c r="J81" s="50"/>
       <c r="K81" s="50"/>
       <c r="L81" s="50"/>
-      <c r="M81" s="138">
+      <c r="M81" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8133,17 +8182,17 @@
       <c r="B82" s="47">
         <v>78</v>
       </c>
-      <c r="C82" s="136"/>
+      <c r="C82" s="133"/>
       <c r="D82" s="50"/>
       <c r="E82" s="50"/>
       <c r="F82" s="50"/>
       <c r="G82" s="50"/>
       <c r="H82" s="50"/>
-      <c r="I82" s="138"/>
+      <c r="I82" s="135"/>
       <c r="J82" s="50"/>
       <c r="K82" s="50"/>
       <c r="L82" s="50"/>
-      <c r="M82" s="138">
+      <c r="M82" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8201,17 +8250,17 @@
       <c r="B83" s="47">
         <v>79</v>
       </c>
-      <c r="C83" s="136"/>
+      <c r="C83" s="133"/>
       <c r="D83" s="50"/>
       <c r="E83" s="50"/>
       <c r="F83" s="50"/>
       <c r="G83" s="50"/>
       <c r="H83" s="50"/>
-      <c r="I83" s="138"/>
+      <c r="I83" s="135"/>
       <c r="J83" s="50"/>
       <c r="K83" s="50"/>
       <c r="L83" s="50"/>
-      <c r="M83" s="138">
+      <c r="M83" s="135">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8269,17 +8318,17 @@
       <c r="B84" s="47">
         <v>80</v>
       </c>
-      <c r="C84" s="136"/>
+      <c r="C84" s="133"/>
       <c r="D84" s="50"/>
       <c r="E84" s="50"/>
       <c r="F84" s="50"/>
       <c r="G84" s="50"/>
       <c r="H84" s="50"/>
-      <c r="I84" s="138"/>
+      <c r="I84" s="135"/>
       <c r="J84" s="50"/>
       <c r="K84" s="50"/>
       <c r="L84" s="50"/>
-      <c r="M84" s="138">
+      <c r="M84" s="135">
         <f t="shared" ref="M84:M131" si="96">SUM(D84:L84)/40</f>
         <v>0</v>
       </c>
@@ -8337,17 +8386,17 @@
       <c r="B85" s="47">
         <v>81</v>
       </c>
-      <c r="C85" s="136"/>
+      <c r="C85" s="133"/>
       <c r="D85" s="50"/>
       <c r="E85" s="50"/>
       <c r="F85" s="50"/>
       <c r="G85" s="50"/>
       <c r="H85" s="50"/>
-      <c r="I85" s="138"/>
+      <c r="I85" s="135"/>
       <c r="J85" s="50"/>
       <c r="K85" s="50"/>
       <c r="L85" s="50"/>
-      <c r="M85" s="138">
+      <c r="M85" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8405,17 +8454,17 @@
       <c r="B86" s="47">
         <v>82</v>
       </c>
-      <c r="C86" s="136"/>
+      <c r="C86" s="133"/>
       <c r="D86" s="50"/>
       <c r="E86" s="50"/>
       <c r="F86" s="50"/>
       <c r="G86" s="50"/>
       <c r="H86" s="50"/>
-      <c r="I86" s="138"/>
+      <c r="I86" s="135"/>
       <c r="J86" s="50"/>
       <c r="K86" s="50"/>
       <c r="L86" s="50"/>
-      <c r="M86" s="138">
+      <c r="M86" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8473,17 +8522,17 @@
       <c r="B87" s="47">
         <v>83</v>
       </c>
-      <c r="C87" s="136"/>
+      <c r="C87" s="133"/>
       <c r="D87" s="50"/>
       <c r="E87" s="50"/>
       <c r="F87" s="50"/>
       <c r="G87" s="50"/>
       <c r="H87" s="50"/>
-      <c r="I87" s="138"/>
+      <c r="I87" s="135"/>
       <c r="J87" s="50"/>
       <c r="K87" s="50"/>
       <c r="L87" s="50"/>
-      <c r="M87" s="138">
+      <c r="M87" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8541,17 +8590,17 @@
       <c r="B88" s="47">
         <v>84</v>
       </c>
-      <c r="C88" s="136"/>
+      <c r="C88" s="133"/>
       <c r="D88" s="50"/>
       <c r="E88" s="50"/>
       <c r="F88" s="50"/>
       <c r="G88" s="50"/>
       <c r="H88" s="50"/>
-      <c r="I88" s="138"/>
+      <c r="I88" s="135"/>
       <c r="J88" s="50"/>
       <c r="K88" s="50"/>
       <c r="L88" s="50"/>
-      <c r="M88" s="138">
+      <c r="M88" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8609,17 +8658,17 @@
       <c r="B89" s="47">
         <v>85</v>
       </c>
-      <c r="C89" s="136"/>
+      <c r="C89" s="133"/>
       <c r="D89" s="50"/>
       <c r="E89" s="50"/>
       <c r="F89" s="50"/>
       <c r="G89" s="50"/>
       <c r="H89" s="50"/>
-      <c r="I89" s="138"/>
+      <c r="I89" s="135"/>
       <c r="J89" s="50"/>
       <c r="K89" s="50"/>
       <c r="L89" s="50"/>
-      <c r="M89" s="138">
+      <c r="M89" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8677,17 +8726,17 @@
       <c r="B90" s="47">
         <v>86</v>
       </c>
-      <c r="C90" s="136"/>
+      <c r="C90" s="133"/>
       <c r="D90" s="50"/>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
       <c r="G90" s="50"/>
       <c r="H90" s="50"/>
-      <c r="I90" s="138"/>
+      <c r="I90" s="135"/>
       <c r="J90" s="50"/>
       <c r="K90" s="50"/>
       <c r="L90" s="50"/>
-      <c r="M90" s="138">
+      <c r="M90" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8745,17 +8794,17 @@
       <c r="B91" s="47">
         <v>87</v>
       </c>
-      <c r="C91" s="136"/>
+      <c r="C91" s="133"/>
       <c r="D91" s="50"/>
       <c r="E91" s="50"/>
       <c r="F91" s="50"/>
       <c r="G91" s="50"/>
       <c r="H91" s="50"/>
-      <c r="I91" s="138"/>
+      <c r="I91" s="135"/>
       <c r="J91" s="50"/>
       <c r="K91" s="50"/>
       <c r="L91" s="50"/>
-      <c r="M91" s="138">
+      <c r="M91" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8813,17 +8862,17 @@
       <c r="B92" s="47">
         <v>88</v>
       </c>
-      <c r="C92" s="136"/>
+      <c r="C92" s="133"/>
       <c r="D92" s="50"/>
       <c r="E92" s="50"/>
       <c r="F92" s="50"/>
       <c r="G92" s="50"/>
       <c r="H92" s="50"/>
-      <c r="I92" s="138"/>
+      <c r="I92" s="135"/>
       <c r="J92" s="50"/>
       <c r="K92" s="50"/>
       <c r="L92" s="50"/>
-      <c r="M92" s="138">
+      <c r="M92" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8881,17 +8930,17 @@
       <c r="B93" s="47">
         <v>89</v>
       </c>
-      <c r="C93" s="136"/>
+      <c r="C93" s="133"/>
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
       <c r="F93" s="50"/>
       <c r="G93" s="50"/>
       <c r="H93" s="50"/>
-      <c r="I93" s="138"/>
+      <c r="I93" s="135"/>
       <c r="J93" s="50"/>
       <c r="K93" s="50"/>
       <c r="L93" s="50"/>
-      <c r="M93" s="138">
+      <c r="M93" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -8949,17 +8998,17 @@
       <c r="B94" s="47">
         <v>90</v>
       </c>
-      <c r="C94" s="136"/>
+      <c r="C94" s="133"/>
       <c r="D94" s="50"/>
       <c r="E94" s="50"/>
       <c r="F94" s="50"/>
       <c r="G94" s="50"/>
       <c r="H94" s="50"/>
-      <c r="I94" s="138"/>
+      <c r="I94" s="135"/>
       <c r="J94" s="50"/>
       <c r="K94" s="50"/>
       <c r="L94" s="50"/>
-      <c r="M94" s="138">
+      <c r="M94" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9017,17 +9066,17 @@
       <c r="B95" s="47">
         <v>91</v>
       </c>
-      <c r="C95" s="136"/>
+      <c r="C95" s="133"/>
       <c r="D95" s="50"/>
       <c r="E95" s="50"/>
       <c r="F95" s="50"/>
       <c r="G95" s="50"/>
       <c r="H95" s="50"/>
-      <c r="I95" s="138"/>
+      <c r="I95" s="135"/>
       <c r="J95" s="50"/>
       <c r="K95" s="50"/>
       <c r="L95" s="50"/>
-      <c r="M95" s="138">
+      <c r="M95" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9085,17 +9134,17 @@
       <c r="B96" s="47">
         <v>92</v>
       </c>
-      <c r="C96" s="136"/>
+      <c r="C96" s="133"/>
       <c r="D96" s="50"/>
       <c r="E96" s="50"/>
       <c r="F96" s="50"/>
       <c r="G96" s="50"/>
       <c r="H96" s="50"/>
-      <c r="I96" s="138"/>
+      <c r="I96" s="135"/>
       <c r="J96" s="50"/>
       <c r="K96" s="50"/>
       <c r="L96" s="50"/>
-      <c r="M96" s="138">
+      <c r="M96" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9153,17 +9202,17 @@
       <c r="B97" s="47">
         <v>93</v>
       </c>
-      <c r="C97" s="136"/>
+      <c r="C97" s="133"/>
       <c r="D97" s="50"/>
       <c r="E97" s="50"/>
       <c r="F97" s="50"/>
       <c r="G97" s="50"/>
       <c r="H97" s="50"/>
-      <c r="I97" s="138"/>
+      <c r="I97" s="135"/>
       <c r="J97" s="50"/>
       <c r="K97" s="50"/>
       <c r="L97" s="50"/>
-      <c r="M97" s="138">
+      <c r="M97" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9221,17 +9270,17 @@
       <c r="B98" s="47">
         <v>94</v>
       </c>
-      <c r="C98" s="136"/>
+      <c r="C98" s="133"/>
       <c r="D98" s="50"/>
       <c r="E98" s="50"/>
       <c r="F98" s="50"/>
       <c r="G98" s="50"/>
       <c r="H98" s="50"/>
-      <c r="I98" s="138"/>
+      <c r="I98" s="135"/>
       <c r="J98" s="50"/>
       <c r="K98" s="50"/>
       <c r="L98" s="50"/>
-      <c r="M98" s="138">
+      <c r="M98" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9289,17 +9338,17 @@
       <c r="B99" s="47">
         <v>95</v>
       </c>
-      <c r="C99" s="136"/>
+      <c r="C99" s="133"/>
       <c r="D99" s="50"/>
       <c r="E99" s="50"/>
       <c r="F99" s="50"/>
       <c r="G99" s="50"/>
       <c r="H99" s="50"/>
-      <c r="I99" s="138"/>
+      <c r="I99" s="135"/>
       <c r="J99" s="50"/>
       <c r="K99" s="50"/>
       <c r="L99" s="50"/>
-      <c r="M99" s="138">
+      <c r="M99" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9357,17 +9406,17 @@
       <c r="B100" s="47">
         <v>96</v>
       </c>
-      <c r="C100" s="136"/>
+      <c r="C100" s="133"/>
       <c r="D100" s="50"/>
       <c r="E100" s="50"/>
       <c r="F100" s="50"/>
       <c r="G100" s="50"/>
       <c r="H100" s="50"/>
-      <c r="I100" s="138"/>
+      <c r="I100" s="135"/>
       <c r="J100" s="50"/>
       <c r="K100" s="50"/>
       <c r="L100" s="50"/>
-      <c r="M100" s="138">
+      <c r="M100" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9425,17 +9474,17 @@
       <c r="B101" s="47">
         <v>97</v>
       </c>
-      <c r="C101" s="136"/>
+      <c r="C101" s="133"/>
       <c r="D101" s="50"/>
       <c r="E101" s="50"/>
       <c r="F101" s="50"/>
       <c r="G101" s="50"/>
       <c r="H101" s="50"/>
-      <c r="I101" s="138"/>
+      <c r="I101" s="135"/>
       <c r="J101" s="50"/>
       <c r="K101" s="50"/>
       <c r="L101" s="50"/>
-      <c r="M101" s="138">
+      <c r="M101" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9493,17 +9542,17 @@
       <c r="B102" s="47">
         <v>98</v>
       </c>
-      <c r="C102" s="136"/>
+      <c r="C102" s="133"/>
       <c r="D102" s="50"/>
       <c r="E102" s="50"/>
       <c r="F102" s="50"/>
       <c r="G102" s="50"/>
       <c r="H102" s="50"/>
-      <c r="I102" s="138"/>
+      <c r="I102" s="135"/>
       <c r="J102" s="50"/>
       <c r="K102" s="50"/>
       <c r="L102" s="50"/>
-      <c r="M102" s="138">
+      <c r="M102" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9561,17 +9610,17 @@
       <c r="B103" s="47">
         <v>99</v>
       </c>
-      <c r="C103" s="136"/>
+      <c r="C103" s="133"/>
       <c r="D103" s="50"/>
       <c r="E103" s="50"/>
       <c r="F103" s="50"/>
       <c r="G103" s="50"/>
       <c r="H103" s="50"/>
-      <c r="I103" s="138"/>
+      <c r="I103" s="135"/>
       <c r="J103" s="50"/>
       <c r="K103" s="50"/>
       <c r="L103" s="50"/>
-      <c r="M103" s="138">
+      <c r="M103" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9629,17 +9678,17 @@
       <c r="B104" s="47">
         <v>100</v>
       </c>
-      <c r="C104" s="136"/>
+      <c r="C104" s="133"/>
       <c r="D104" s="50"/>
       <c r="E104" s="50"/>
       <c r="F104" s="50"/>
       <c r="G104" s="50"/>
       <c r="H104" s="50"/>
-      <c r="I104" s="138"/>
+      <c r="I104" s="135"/>
       <c r="J104" s="50"/>
       <c r="K104" s="50"/>
       <c r="L104" s="50"/>
-      <c r="M104" s="138">
+      <c r="M104" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9697,17 +9746,17 @@
       <c r="B105" s="47">
         <v>101</v>
       </c>
-      <c r="C105" s="136"/>
+      <c r="C105" s="133"/>
       <c r="D105" s="50"/>
       <c r="E105" s="50"/>
       <c r="F105" s="50"/>
       <c r="G105" s="50"/>
       <c r="H105" s="50"/>
-      <c r="I105" s="138"/>
+      <c r="I105" s="135"/>
       <c r="J105" s="50"/>
       <c r="K105" s="50"/>
       <c r="L105" s="50"/>
-      <c r="M105" s="138">
+      <c r="M105" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9765,17 +9814,17 @@
       <c r="B106" s="47">
         <v>102</v>
       </c>
-      <c r="C106" s="136"/>
+      <c r="C106" s="133"/>
       <c r="D106" s="50"/>
       <c r="E106" s="50"/>
       <c r="F106" s="50"/>
       <c r="G106" s="50"/>
       <c r="H106" s="50"/>
-      <c r="I106" s="138"/>
+      <c r="I106" s="135"/>
       <c r="J106" s="50"/>
       <c r="K106" s="50"/>
       <c r="L106" s="50"/>
-      <c r="M106" s="138">
+      <c r="M106" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9833,17 +9882,17 @@
       <c r="B107" s="47">
         <v>103</v>
       </c>
-      <c r="C107" s="136"/>
+      <c r="C107" s="133"/>
       <c r="D107" s="50"/>
       <c r="E107" s="50"/>
       <c r="F107" s="50"/>
       <c r="G107" s="50"/>
       <c r="H107" s="50"/>
-      <c r="I107" s="138"/>
+      <c r="I107" s="135"/>
       <c r="J107" s="50"/>
       <c r="K107" s="50"/>
       <c r="L107" s="50"/>
-      <c r="M107" s="138">
+      <c r="M107" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9901,17 +9950,17 @@
       <c r="B108" s="47">
         <v>104</v>
       </c>
-      <c r="C108" s="136"/>
+      <c r="C108" s="133"/>
       <c r="D108" s="50"/>
       <c r="E108" s="50"/>
       <c r="F108" s="50"/>
       <c r="G108" s="50"/>
       <c r="H108" s="50"/>
-      <c r="I108" s="138"/>
+      <c r="I108" s="135"/>
       <c r="J108" s="50"/>
       <c r="K108" s="50"/>
       <c r="L108" s="50"/>
-      <c r="M108" s="138">
+      <c r="M108" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -9969,17 +10018,17 @@
       <c r="B109" s="47">
         <v>105</v>
       </c>
-      <c r="C109" s="136"/>
+      <c r="C109" s="133"/>
       <c r="D109" s="50"/>
       <c r="E109" s="50"/>
       <c r="F109" s="50"/>
       <c r="G109" s="50"/>
       <c r="H109" s="50"/>
-      <c r="I109" s="138"/>
+      <c r="I109" s="135"/>
       <c r="J109" s="50"/>
       <c r="K109" s="50"/>
       <c r="L109" s="50"/>
-      <c r="M109" s="138">
+      <c r="M109" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10037,17 +10086,17 @@
       <c r="B110" s="47">
         <v>106</v>
       </c>
-      <c r="C110" s="136"/>
+      <c r="C110" s="133"/>
       <c r="D110" s="50"/>
       <c r="E110" s="50"/>
       <c r="F110" s="50"/>
       <c r="G110" s="50"/>
       <c r="H110" s="50"/>
-      <c r="I110" s="138"/>
+      <c r="I110" s="135"/>
       <c r="J110" s="50"/>
       <c r="K110" s="50"/>
       <c r="L110" s="50"/>
-      <c r="M110" s="138">
+      <c r="M110" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10105,17 +10154,17 @@
       <c r="B111" s="47">
         <v>107</v>
       </c>
-      <c r="C111" s="136"/>
+      <c r="C111" s="133"/>
       <c r="D111" s="50"/>
       <c r="E111" s="50"/>
       <c r="F111" s="50"/>
       <c r="G111" s="50"/>
       <c r="H111" s="50"/>
-      <c r="I111" s="138"/>
+      <c r="I111" s="135"/>
       <c r="J111" s="50"/>
       <c r="K111" s="50"/>
       <c r="L111" s="50"/>
-      <c r="M111" s="138">
+      <c r="M111" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10173,17 +10222,17 @@
       <c r="B112" s="47">
         <v>108</v>
       </c>
-      <c r="C112" s="136"/>
+      <c r="C112" s="133"/>
       <c r="D112" s="50"/>
       <c r="E112" s="50"/>
       <c r="F112" s="50"/>
       <c r="G112" s="50"/>
       <c r="H112" s="50"/>
-      <c r="I112" s="138"/>
+      <c r="I112" s="135"/>
       <c r="J112" s="50"/>
       <c r="K112" s="50"/>
       <c r="L112" s="50"/>
-      <c r="M112" s="138">
+      <c r="M112" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10241,17 +10290,17 @@
       <c r="B113" s="47">
         <v>109</v>
       </c>
-      <c r="C113" s="136"/>
+      <c r="C113" s="133"/>
       <c r="D113" s="50"/>
       <c r="E113" s="50"/>
       <c r="F113" s="50"/>
       <c r="G113" s="50"/>
       <c r="H113" s="50"/>
-      <c r="I113" s="138"/>
+      <c r="I113" s="135"/>
       <c r="J113" s="50"/>
       <c r="K113" s="50"/>
       <c r="L113" s="50"/>
-      <c r="M113" s="138">
+      <c r="M113" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10309,17 +10358,17 @@
       <c r="B114" s="47">
         <v>110</v>
       </c>
-      <c r="C114" s="136"/>
+      <c r="C114" s="133"/>
       <c r="D114" s="50"/>
       <c r="E114" s="50"/>
       <c r="F114" s="50"/>
       <c r="G114" s="50"/>
       <c r="H114" s="50"/>
-      <c r="I114" s="138"/>
+      <c r="I114" s="135"/>
       <c r="J114" s="50"/>
       <c r="K114" s="50"/>
       <c r="L114" s="50"/>
-      <c r="M114" s="138">
+      <c r="M114" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10377,17 +10426,17 @@
       <c r="B115" s="47">
         <v>111</v>
       </c>
-      <c r="C115" s="136"/>
+      <c r="C115" s="133"/>
       <c r="D115" s="50"/>
       <c r="E115" s="50"/>
       <c r="F115" s="50"/>
       <c r="G115" s="50"/>
       <c r="H115" s="50"/>
-      <c r="I115" s="138"/>
+      <c r="I115" s="135"/>
       <c r="J115" s="50"/>
       <c r="K115" s="50"/>
       <c r="L115" s="50"/>
-      <c r="M115" s="138">
+      <c r="M115" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10445,17 +10494,17 @@
       <c r="B116" s="47">
         <v>112</v>
       </c>
-      <c r="C116" s="136"/>
+      <c r="C116" s="133"/>
       <c r="D116" s="50"/>
       <c r="E116" s="50"/>
       <c r="F116" s="50"/>
       <c r="G116" s="50"/>
       <c r="H116" s="50"/>
-      <c r="I116" s="138"/>
+      <c r="I116" s="135"/>
       <c r="J116" s="50"/>
       <c r="K116" s="50"/>
       <c r="L116" s="50"/>
-      <c r="M116" s="138">
+      <c r="M116" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10513,17 +10562,17 @@
       <c r="B117" s="47">
         <v>113</v>
       </c>
-      <c r="C117" s="136"/>
+      <c r="C117" s="133"/>
       <c r="D117" s="50"/>
       <c r="E117" s="50"/>
       <c r="F117" s="50"/>
       <c r="G117" s="50"/>
       <c r="H117" s="50"/>
-      <c r="I117" s="138"/>
+      <c r="I117" s="135"/>
       <c r="J117" s="50"/>
       <c r="K117" s="50"/>
       <c r="L117" s="50"/>
-      <c r="M117" s="138">
+      <c r="M117" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10581,17 +10630,17 @@
       <c r="B118" s="47">
         <v>114</v>
       </c>
-      <c r="C118" s="136"/>
+      <c r="C118" s="133"/>
       <c r="D118" s="50"/>
       <c r="E118" s="50"/>
       <c r="F118" s="50"/>
       <c r="G118" s="50"/>
       <c r="H118" s="50"/>
-      <c r="I118" s="138"/>
+      <c r="I118" s="135"/>
       <c r="J118" s="50"/>
       <c r="K118" s="50"/>
       <c r="L118" s="50"/>
-      <c r="M118" s="138">
+      <c r="M118" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10649,17 +10698,17 @@
       <c r="B119" s="47">
         <v>115</v>
       </c>
-      <c r="C119" s="136"/>
+      <c r="C119" s="133"/>
       <c r="D119" s="50"/>
       <c r="E119" s="50"/>
       <c r="F119" s="50"/>
       <c r="G119" s="50"/>
       <c r="H119" s="50"/>
-      <c r="I119" s="138"/>
+      <c r="I119" s="135"/>
       <c r="J119" s="50"/>
       <c r="K119" s="50"/>
       <c r="L119" s="50"/>
-      <c r="M119" s="138">
+      <c r="M119" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10717,17 +10766,17 @@
       <c r="B120" s="47">
         <v>116</v>
       </c>
-      <c r="C120" s="136"/>
+      <c r="C120" s="133"/>
       <c r="D120" s="50"/>
       <c r="E120" s="50"/>
       <c r="F120" s="50"/>
       <c r="G120" s="50"/>
       <c r="H120" s="50"/>
-      <c r="I120" s="138"/>
+      <c r="I120" s="135"/>
       <c r="J120" s="50"/>
       <c r="K120" s="50"/>
       <c r="L120" s="50"/>
-      <c r="M120" s="138">
+      <c r="M120" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10785,17 +10834,17 @@
       <c r="B121" s="47">
         <v>117</v>
       </c>
-      <c r="C121" s="136"/>
+      <c r="C121" s="133"/>
       <c r="D121" s="50"/>
       <c r="E121" s="50"/>
       <c r="F121" s="50"/>
       <c r="G121" s="50"/>
       <c r="H121" s="50"/>
-      <c r="I121" s="138"/>
+      <c r="I121" s="135"/>
       <c r="J121" s="50"/>
       <c r="K121" s="50"/>
       <c r="L121" s="50"/>
-      <c r="M121" s="138">
+      <c r="M121" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10853,17 +10902,17 @@
       <c r="B122" s="47">
         <v>118</v>
       </c>
-      <c r="C122" s="136"/>
+      <c r="C122" s="133"/>
       <c r="D122" s="50"/>
       <c r="E122" s="50"/>
       <c r="F122" s="50"/>
       <c r="G122" s="50"/>
       <c r="H122" s="50"/>
-      <c r="I122" s="138"/>
+      <c r="I122" s="135"/>
       <c r="J122" s="50"/>
       <c r="K122" s="50"/>
       <c r="L122" s="50"/>
-      <c r="M122" s="138">
+      <c r="M122" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10921,17 +10970,17 @@
       <c r="B123" s="47">
         <v>119</v>
       </c>
-      <c r="C123" s="136"/>
+      <c r="C123" s="133"/>
       <c r="D123" s="50"/>
       <c r="E123" s="50"/>
       <c r="F123" s="50"/>
       <c r="G123" s="50"/>
       <c r="H123" s="50"/>
-      <c r="I123" s="138"/>
+      <c r="I123" s="135"/>
       <c r="J123" s="50"/>
       <c r="K123" s="50"/>
       <c r="L123" s="50"/>
-      <c r="M123" s="138">
+      <c r="M123" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -10987,17 +11036,17 @@
     <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" s="78"/>
       <c r="B124" s="112"/>
-      <c r="C124" s="136"/>
+      <c r="C124" s="133"/>
       <c r="D124" s="50"/>
       <c r="E124" s="50"/>
       <c r="F124" s="50"/>
       <c r="G124" s="50"/>
       <c r="H124" s="50"/>
-      <c r="I124" s="138"/>
+      <c r="I124" s="135"/>
       <c r="J124" s="50"/>
       <c r="K124" s="50"/>
       <c r="L124" s="50"/>
-      <c r="M124" s="138">
+      <c r="M124" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11053,17 +11102,17 @@
     <row r="125" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A125" s="78"/>
       <c r="B125" s="112"/>
-      <c r="C125" s="136"/>
+      <c r="C125" s="133"/>
       <c r="D125" s="50"/>
       <c r="E125" s="50"/>
       <c r="F125" s="50"/>
       <c r="G125" s="50"/>
       <c r="H125" s="50"/>
-      <c r="I125" s="138"/>
+      <c r="I125" s="135"/>
       <c r="J125" s="50"/>
       <c r="K125" s="50"/>
       <c r="L125" s="50"/>
-      <c r="M125" s="138">
+      <c r="M125" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11119,17 +11168,17 @@
     <row r="126" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A126" s="78"/>
       <c r="B126" s="112"/>
-      <c r="C126" s="136"/>
+      <c r="C126" s="133"/>
       <c r="D126" s="50"/>
       <c r="E126" s="50"/>
       <c r="F126" s="50"/>
       <c r="G126" s="50"/>
       <c r="H126" s="50"/>
-      <c r="I126" s="138"/>
+      <c r="I126" s="135"/>
       <c r="J126" s="50"/>
       <c r="K126" s="50"/>
       <c r="L126" s="50"/>
-      <c r="M126" s="138">
+      <c r="M126" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11185,17 +11234,17 @@
     <row r="127" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A127" s="78"/>
       <c r="B127" s="112"/>
-      <c r="C127" s="136"/>
+      <c r="C127" s="133"/>
       <c r="D127" s="50"/>
       <c r="E127" s="50"/>
       <c r="F127" s="50"/>
       <c r="G127" s="50"/>
       <c r="H127" s="50"/>
-      <c r="I127" s="138"/>
+      <c r="I127" s="135"/>
       <c r="J127" s="50"/>
       <c r="K127" s="50"/>
       <c r="L127" s="50"/>
-      <c r="M127" s="138">
+      <c r="M127" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11251,17 +11300,17 @@
     <row r="128" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A128" s="78"/>
       <c r="B128" s="112"/>
-      <c r="C128" s="136"/>
+      <c r="C128" s="133"/>
       <c r="D128" s="50"/>
       <c r="E128" s="50"/>
       <c r="F128" s="50"/>
       <c r="G128" s="50"/>
       <c r="H128" s="50"/>
-      <c r="I128" s="138"/>
+      <c r="I128" s="135"/>
       <c r="J128" s="50"/>
       <c r="K128" s="50"/>
       <c r="L128" s="50"/>
-      <c r="M128" s="138">
+      <c r="M128" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11317,17 +11366,17 @@
     <row r="129" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A129" s="78"/>
       <c r="B129" s="112"/>
-      <c r="C129" s="136"/>
+      <c r="C129" s="133"/>
       <c r="D129" s="50"/>
       <c r="E129" s="50"/>
       <c r="F129" s="50"/>
       <c r="G129" s="50"/>
       <c r="H129" s="50"/>
-      <c r="I129" s="138"/>
+      <c r="I129" s="135"/>
       <c r="J129" s="50"/>
       <c r="K129" s="50"/>
       <c r="L129" s="50"/>
-      <c r="M129" s="138">
+      <c r="M129" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11383,17 +11432,17 @@
     <row r="130" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A130" s="78"/>
       <c r="B130" s="112"/>
-      <c r="C130" s="136"/>
+      <c r="C130" s="133"/>
       <c r="D130" s="50"/>
       <c r="E130" s="50"/>
       <c r="F130" s="50"/>
       <c r="G130" s="50"/>
       <c r="H130" s="50"/>
-      <c r="I130" s="138"/>
+      <c r="I130" s="135"/>
       <c r="J130" s="50"/>
       <c r="K130" s="50"/>
       <c r="L130" s="50"/>
-      <c r="M130" s="138">
+      <c r="M130" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11449,17 +11498,17 @@
     <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131" s="78"/>
       <c r="B131" s="112"/>
-      <c r="C131" s="136"/>
+      <c r="C131" s="133"/>
       <c r="D131" s="50"/>
       <c r="E131" s="50"/>
       <c r="F131" s="50"/>
       <c r="G131" s="50"/>
       <c r="H131" s="50"/>
-      <c r="I131" s="138"/>
+      <c r="I131" s="135"/>
       <c r="J131" s="50"/>
       <c r="K131" s="50"/>
       <c r="L131" s="50"/>
-      <c r="M131" s="138">
+      <c r="M131" s="135">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
@@ -11514,10 +11563,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="179" t="s">
+      <c r="B132" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="180"/>
+      <c r="C132" s="161"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11781,10 +11830,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="167" t="s">
+      <c r="B136" s="173" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="168"/>
+      <c r="C136" s="174"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11875,10 +11924,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="156" t="s">
+      <c r="B137" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="157"/>
+      <c r="C137" s="163"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -11970,17 +12019,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12015,24 +12064,24 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="183" t="s">
+      <c r="C3" s="177" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="187" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="188"/>
-      <c r="K3" s="182" t="s">
+      <c r="I3" s="182"/>
+      <c r="K3" s="176" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
+      <c r="L3" s="176"/>
+      <c r="M3" s="176"/>
+      <c r="N3" s="176"/>
+      <c r="O3" s="176"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12153,21 +12202,21 @@
       <c r="O6" s="81">
         <v>129</v>
       </c>
-      <c r="S6" s="130"/>
-      <c r="T6" s="130"/>
-      <c r="U6" s="155">
+      <c r="S6" s="129"/>
+      <c r="T6" s="129"/>
+      <c r="U6" s="149">
         <v>46180</v>
       </c>
-      <c r="V6" s="155">
+      <c r="V6" s="149">
         <v>46180</v>
       </c>
-      <c r="W6" s="155">
+      <c r="W6" s="149">
         <v>46333</v>
       </c>
-      <c r="X6" s="155">
+      <c r="X6" s="149">
         <v>46210</v>
       </c>
-      <c r="Y6" s="155">
+      <c r="Y6" s="149">
         <v>46210</v>
       </c>
     </row>
@@ -12187,29 +12236,29 @@
       <c r="O7" s="81">
         <v>35</v>
       </c>
-      <c r="S7" s="154" t="s">
-        <v>156</v>
-      </c>
-      <c r="T7" s="154" t="s">
+      <c r="S7" s="148" t="s">
         <v>155</v>
       </c>
+      <c r="T7" s="148" t="s">
+        <v>154</v>
+      </c>
       <c r="U7" s="77" t="s">
-        <v>149</v>
-      </c>
-      <c r="V7" s="154" t="s">
+        <v>148</v>
+      </c>
+      <c r="V7" s="148" t="s">
+        <v>152</v>
+      </c>
+      <c r="W7" s="148" t="s">
+        <v>151</v>
+      </c>
+      <c r="X7" s="148" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y7" s="148" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z7" s="148" t="s">
         <v>153</v>
-      </c>
-      <c r="W7" s="154" t="s">
-        <v>152</v>
-      </c>
-      <c r="X7" s="154" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y7" s="154" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z7" s="154" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="8" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12236,9 +12285,9 @@
         <v>120</v>
       </c>
       <c r="T8" s="79" t="s">
-        <v>148</v>
-      </c>
-      <c r="U8" s="153">
+        <v>147</v>
+      </c>
+      <c r="U8" s="147">
         <v>50</v>
       </c>
       <c r="V8" s="79">
@@ -12290,7 +12339,7 @@
       <c r="T9" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="153">
+      <c r="U9" s="147">
         <v>50</v>
       </c>
       <c r="V9" s="79">
@@ -12331,9 +12380,9 @@
         <v>120</v>
       </c>
       <c r="T10" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="U10" s="153"/>
+        <v>149</v>
+      </c>
+      <c r="U10" s="147"/>
       <c r="V10" s="79">
         <v>3</v>
       </c>
@@ -12350,14 +12399,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="186" t="s">
+      <c r="C11" s="180" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="186"/>
-      <c r="F11" s="186" t="s">
+      <c r="D11" s="180"/>
+      <c r="F11" s="180" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="186"/>
+      <c r="G11" s="180"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12378,9 +12427,9 @@
         <v>70</v>
       </c>
       <c r="T11" s="79" t="s">
-        <v>148</v>
-      </c>
-      <c r="U11" s="153"/>
+        <v>147</v>
+      </c>
+      <c r="U11" s="147"/>
       <c r="V11" s="79"/>
       <c r="W11" s="79"/>
       <c r="X11" s="79">
@@ -12428,9 +12477,9 @@
         <v>70</v>
       </c>
       <c r="T12" s="79" t="s">
-        <v>151</v>
-      </c>
-      <c r="U12" s="153"/>
+        <v>150</v>
+      </c>
+      <c r="U12" s="147"/>
       <c r="V12" s="79"/>
       <c r="W12" s="79"/>
       <c r="X12" s="79">
@@ -12459,11 +12508,11 @@
         <f>G12*40</f>
         <v>200920</v>
       </c>
-      <c r="S13" s="181" t="s">
-        <v>154</v>
-      </c>
-      <c r="T13" s="181"/>
-      <c r="U13" s="153">
+      <c r="S13" s="175" t="s">
+        <v>153</v>
+      </c>
+      <c r="T13" s="175"/>
+      <c r="U13" s="147">
         <f>SUM(U8:U12)</f>
         <v>100</v>
       </c>
@@ -12578,13 +12627,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="182" t="s">
+      <c r="D20" s="176" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="182"/>
-      <c r="F20" s="182"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="182"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
+      <c r="G20" s="176"/>
+      <c r="H20" s="176"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -12894,7 +12943,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -12905,6 +12954,7 @@
     <col min="9" max="9" width="23.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.81640625" customWidth="1"/>
     <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -12920,14 +12970,24 @@
       <c r="D1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="128" t="s">
+      <c r="G1" s="190"/>
+      <c r="H1" s="186" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="186" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="128" t="s">
+      <c r="J1" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="128" t="s">
+      <c r="K1" s="186" t="s">
         <v>79</v>
+      </c>
+      <c r="L1" s="187" t="s">
+        <v>159</v>
+      </c>
+      <c r="M1" s="187" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -12935,17 +12995,22 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="I2" s="81" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="184" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="81">
+      <c r="J2" s="184">
         <v>70</v>
       </c>
-      <c r="K2" s="81" t="s">
+      <c r="K2" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L2" t="s">
-        <v>104</v>
+      <c r="L2" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M2" s="79">
+        <f>J2*40</f>
+        <v>2800</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -12953,14 +13018,22 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="I3" s="139" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="184" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="139">
+      <c r="J3" s="184">
         <v>10</v>
       </c>
-      <c r="K3" s="139" t="s">
+      <c r="K3" s="147" t="s">
         <v>99</v>
+      </c>
+      <c r="L3" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M3" s="79">
+        <f t="shared" ref="M3:M35" si="0">J3*40</f>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -12968,14 +13041,22 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="I4" s="139" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="J4" s="139">
+      <c r="J4" s="184">
         <v>9</v>
       </c>
-      <c r="K4" s="139" t="s">
+      <c r="K4" s="147" t="s">
         <v>99</v>
+      </c>
+      <c r="L4" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M4" s="79">
+        <f t="shared" si="0"/>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -12983,14 +13064,22 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="I5" s="139" t="s">
+      <c r="H5" s="2"/>
+      <c r="I5" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="J5" s="139">
+      <c r="J5" s="184">
         <v>18</v>
       </c>
-      <c r="K5" s="139" t="s">
+      <c r="K5" s="147" t="s">
         <v>99</v>
+      </c>
+      <c r="L5" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M5" s="79">
+        <f t="shared" si="0"/>
+        <v>720</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -12998,14 +13087,22 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="I6" s="139" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="184" t="s">
         <v>103</v>
       </c>
-      <c r="J6" s="139">
+      <c r="J6" s="184">
         <v>5</v>
       </c>
-      <c r="K6" s="139" t="s">
+      <c r="K6" s="147" t="s">
         <v>99</v>
+      </c>
+      <c r="L6" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M6" s="79">
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -13013,14 +13110,22 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="I7" s="81" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="184" t="s">
         <v>105</v>
       </c>
-      <c r="J7" s="81">
+      <c r="J7" s="184">
         <v>14</v>
       </c>
-      <c r="K7" s="81" t="s">
+      <c r="K7" s="147" t="s">
         <v>99</v>
+      </c>
+      <c r="L7" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M7" s="79">
+        <f t="shared" si="0"/>
+        <v>560</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -13029,106 +13134,140 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
+      <c r="G8" s="188"/>
       <c r="H8" s="81"/>
-      <c r="I8" s="81" t="s">
+      <c r="I8" s="184" t="s">
         <v>106</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="184">
         <v>13</v>
       </c>
-      <c r="K8" s="81" t="s">
+      <c r="K8" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L8" s="133"/>
+      <c r="L8" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M8" s="79">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="I9" s="81" t="s">
+      <c r="H9" s="2"/>
+      <c r="I9" s="184" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="81">
+      <c r="J9" s="184">
         <v>4</v>
       </c>
-      <c r="K9" s="81" t="s">
+      <c r="K9" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L9" s="133"/>
+      <c r="L9" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M9" s="79">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="152" t="s">
+      <c r="I10" s="184" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="152">
+      <c r="J10" s="184">
         <v>12</v>
       </c>
-      <c r="K10" s="152" t="s">
+      <c r="K10" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="L10" s="133"/>
+      <c r="L10" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="M10" s="79">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="H11" t="s">
+      <c r="H11" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="152" t="s">
+      <c r="I11" s="184" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="152">
+      <c r="J11" s="184">
         <v>19</v>
       </c>
-      <c r="K11" s="152" t="s">
+      <c r="K11" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="L11" s="133"/>
+      <c r="L11" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="M11" s="79">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="I12" s="151" t="s">
+      <c r="H12" s="2"/>
+      <c r="I12" s="183" t="s">
         <v>114</v>
       </c>
-      <c r="J12" s="151">
+      <c r="J12" s="183">
         <v>13</v>
       </c>
-      <c r="K12" s="151" t="s">
+      <c r="K12" s="183" t="s">
         <v>115</v>
       </c>
-      <c r="L12" s="133"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="I13" s="81" t="s">
+      <c r="H13" s="2"/>
+      <c r="I13" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="J13" s="81">
+      <c r="J13" s="79">
         <v>5</v>
       </c>
-      <c r="K13" s="139" t="s">
+      <c r="K13" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L13" s="133"/>
-      <c r="M13">
-        <v>174</v>
+      <c r="L13" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M13" s="79">
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -13136,18 +13275,22 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="I14" s="81" t="s">
+      <c r="H14" s="2"/>
+      <c r="I14" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="81">
+      <c r="J14" s="79">
         <v>8</v>
       </c>
-      <c r="K14" s="139" t="s">
+      <c r="K14" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L14" s="133"/>
-      <c r="M14">
-        <v>99</v>
+      <c r="L14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M14" s="79">
+        <f t="shared" si="0"/>
+        <v>320</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -13155,18 +13298,22 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="I15" s="81" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="81">
+      <c r="J15" s="79">
         <v>10</v>
       </c>
-      <c r="K15" s="139" t="s">
+      <c r="K15" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="M15">
-        <f>M13+M14</f>
-        <v>273</v>
+      <c r="L15" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M15" s="79">
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -13174,259 +13321,545 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="I16" s="81" t="s">
+      <c r="H16" s="2"/>
+      <c r="I16" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="J16" s="81">
+      <c r="J16" s="79">
         <v>5</v>
       </c>
-      <c r="K16" s="139" t="s">
+      <c r="K16" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L16" s="134"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L16" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M16" s="79">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="I17" s="81" t="s">
+      <c r="H17" s="2"/>
+      <c r="I17" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="J17" s="81">
+      <c r="J17" s="79">
         <v>4</v>
       </c>
-      <c r="K17" s="139" t="s">
+      <c r="K17" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L17" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M17" s="79">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="I18" s="81" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="81">
+      <c r="J18" s="79">
         <v>9</v>
       </c>
-      <c r="K18" s="139" t="s">
+      <c r="K18" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L18" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M18" s="79">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="83"/>
       <c r="C19" s="83"/>
       <c r="D19" s="83"/>
-      <c r="I19" s="81" t="s">
+      <c r="H19" s="2"/>
+      <c r="I19" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="81">
+      <c r="J19" s="79">
         <v>6</v>
       </c>
-      <c r="K19" s="139" t="s">
+      <c r="K19" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L19" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M19" s="79">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="84"/>
       <c r="B20" s="85"/>
       <c r="C20" s="85"/>
       <c r="D20" s="86"/>
-      <c r="I20" s="81" t="s">
+      <c r="H20" s="2"/>
+      <c r="I20" s="79" t="s">
         <v>124</v>
       </c>
-      <c r="J20" s="81">
+      <c r="J20" s="79">
         <v>30</v>
       </c>
-      <c r="K20" s="139" t="s">
+      <c r="K20" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="I21" s="81" t="s">
+      <c r="L20" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M20" s="79">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H21" s="2"/>
+      <c r="I21" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="J21" s="81">
+      <c r="J21" s="79">
         <v>22</v>
       </c>
-      <c r="K21" s="139" t="s">
+      <c r="K21" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L21" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M21" s="79">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H22" s="189">
+        <v>46333</v>
+      </c>
       <c r="I22" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="J22" s="81">
+      <c r="J22" s="79">
         <v>15</v>
       </c>
-      <c r="K22" s="81" t="s">
+      <c r="K22" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L22">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L22" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M22" s="79">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H23" s="189">
+        <v>46333</v>
+      </c>
       <c r="I23" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="J23" s="81">
+      <c r="J23" s="79">
         <v>4</v>
       </c>
-      <c r="K23" s="81" t="s">
+      <c r="K23" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L23">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L23" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M23" s="79">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H24" s="189">
+        <v>46333</v>
+      </c>
       <c r="I24" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="J24" s="81">
+      <c r="J24" s="79">
         <v>50</v>
       </c>
-      <c r="K24" s="81" t="s">
+      <c r="K24" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L24">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L24" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M24" s="79">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H25" s="189">
+        <v>46333</v>
+      </c>
       <c r="I25" s="79" t="s">
         <v>130</v>
       </c>
-      <c r="J25" s="81">
+      <c r="J25" s="79">
         <v>5</v>
       </c>
-      <c r="K25" s="81" t="s">
+      <c r="K25" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="L25">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L25" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M25" s="79">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H26" s="189">
+        <v>46333</v>
+      </c>
       <c r="I26" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="J26" s="81">
+        <v>162</v>
+      </c>
+      <c r="J26" s="79">
         <v>50</v>
       </c>
-      <c r="K26" s="81" t="s">
+      <c r="K26" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L26" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M26" s="79">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H27" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I27" s="79" t="s">
         <v>131</v>
       </c>
       <c r="J27" s="79">
         <v>5</v>
       </c>
-      <c r="K27" s="152" t="s">
+      <c r="K27" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L27" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M27" s="79">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H28" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I28" s="79" t="s">
         <v>132</v>
       </c>
       <c r="J28" s="79">
         <v>7</v>
       </c>
-      <c r="K28" s="152" t="s">
+      <c r="K28" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L28" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M28" s="79">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H29" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I29" s="79" t="s">
         <v>133</v>
       </c>
       <c r="J29" s="79">
         <v>21</v>
       </c>
-      <c r="K29" s="152" t="s">
+      <c r="K29" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L29" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M29" s="79">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I30" s="79" t="s">
         <v>134</v>
       </c>
       <c r="J30" s="79">
         <v>8</v>
       </c>
-      <c r="K30" s="152" t="s">
+      <c r="K30" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L30" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M30" s="79">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H31" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I31" s="79" t="s">
         <v>135</v>
       </c>
       <c r="J31" s="79">
         <v>4</v>
       </c>
-      <c r="K31" s="152" t="s">
+      <c r="K31" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L31" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M31" s="79">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H32" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I32" s="79" t="s">
         <v>136</v>
       </c>
       <c r="J32" s="79">
         <v>4</v>
       </c>
-      <c r="K32" s="152" t="s">
+      <c r="K32" s="147" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H33">
+      <c r="L32" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M32" s="79">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H33" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I33" s="183" t="s">
+        <v>143</v>
+      </c>
+      <c r="J33" s="183">
+        <v>305</v>
+      </c>
+      <c r="K33" s="183" t="s">
+        <v>115</v>
+      </c>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79">
+        <f t="shared" si="0"/>
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="34" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H34" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I34" s="79" t="s">
+        <v>141</v>
+      </c>
+      <c r="J34" s="79">
+        <v>35</v>
+      </c>
+      <c r="K34" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="L34" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M34" s="79">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="35" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H35" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I35" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="J35" s="79">
+        <v>122</v>
+      </c>
+      <c r="K35" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="L35" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M35" s="79">
+        <f t="shared" si="0"/>
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="36" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I36" s="184" t="s">
+        <v>108</v>
+      </c>
+      <c r="J36" s="184">
+        <f>M36/40</f>
+        <v>10</v>
+      </c>
+      <c r="K36" s="184" t="s">
+        <v>142</v>
+      </c>
+      <c r="L36" s="79"/>
+      <c r="M36" s="79">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H37" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I37" s="184" t="s">
+        <v>156</v>
+      </c>
+      <c r="J37" s="184">
+        <f>M37/40</f>
         <v>14</v>
       </c>
-      <c r="I33" s="79" t="s">
+      <c r="K37" s="184" t="s">
         <v>142</v>
       </c>
-      <c r="J33" s="79">
-        <v>35</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="I34" s="79" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="79">
-        <v>305</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="I35" s="79" t="s">
-        <v>147</v>
-      </c>
-      <c r="J35" s="2">
-        <v>125</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>143</v>
+      <c r="L37" s="79"/>
+      <c r="M37" s="79">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="38" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I38" s="184" t="s">
+        <v>157</v>
+      </c>
+      <c r="J38" s="184">
+        <f>M38/40</f>
+        <v>17</v>
+      </c>
+      <c r="K38" s="184" t="s">
+        <v>142</v>
+      </c>
+      <c r="L38" s="79"/>
+      <c r="M38" s="79">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="39" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H39" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I39" s="184" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" s="184">
+        <f>M39/40</f>
+        <v>18</v>
+      </c>
+      <c r="K39" s="184" t="s">
+        <v>142</v>
+      </c>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="40" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H40" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I40" s="184" t="s">
+        <v>128</v>
+      </c>
+      <c r="J40" s="184">
+        <f>M40/40</f>
+        <v>4</v>
+      </c>
+      <c r="K40" s="184" t="s">
+        <v>142</v>
+      </c>
+      <c r="L40" s="79"/>
+      <c r="M40" s="79">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H41" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I41" s="184" t="s">
+        <v>167</v>
+      </c>
+      <c r="J41" s="184">
+        <v>12</v>
+      </c>
+      <c r="K41" s="184" t="s">
+        <v>142</v>
+      </c>
+      <c r="L41" s="79"/>
+      <c r="M41" s="81">
+        <f>J41*40</f>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="H1:M40" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FA2408-9757-4C0A-90F5-6C6B251B00A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66C3BC2-8AC2-42AB-9524-71092C77CB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="170">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -529,7 +529,13 @@
     <t>17/07/2026</t>
   </si>
   <si>
-    <t>Rainbow Shadbagh</t>
+    <t xml:space="preserve">Raibow Gujranwala </t>
+  </si>
+  <si>
+    <t>Rainbow Shaikhupura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Shahbagh </t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1814,6 +1820,66 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1850,45 +1916,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1912,30 +1939,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2472,14 +2475,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="150">
+      <c r="B1" s="170">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
-      </c>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
+        <v>46221</v>
+      </c>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2501,10 +2504,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="167" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="171" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2537,13 +2540,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="164"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="166"/>
-      <c r="P2" s="167" t="s">
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="168"/>
+      <c r="Q2" s="163"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2562,8 +2565,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="172"/>
-      <c r="B3" s="152"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="172"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2594,29 +2597,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="169" t="s">
+      <c r="M3" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="170"/>
-      <c r="O3" s="171"/>
+      <c r="N3" s="165"/>
+      <c r="O3" s="166"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="154" t="s">
+      <c r="R3" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="155"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="156"/>
-      <c r="V3" s="157" t="s">
+      <c r="S3" s="175"/>
+      <c r="T3" s="175"/>
+      <c r="U3" s="176"/>
+      <c r="V3" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="158"/>
-      <c r="X3" s="158"/>
-      <c r="Y3" s="159"/>
+      <c r="W3" s="178"/>
+      <c r="X3" s="178"/>
+      <c r="Y3" s="179"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="172"/>
-      <c r="B4" s="153"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="173"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -5432,26 +5435,26 @@
       <c r="B39" s="47">
         <v>35</v>
       </c>
-      <c r="C39" s="141" t="s">
+      <c r="C39" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="142"/>
-      <c r="E39" s="143"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="145">
+      <c r="D39" s="74"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="50">
         <v>20</v>
       </c>
-      <c r="H39" s="143">
+      <c r="H39" s="75">
         <v>80</v>
       </c>
-      <c r="I39" s="146"/>
-      <c r="J39" s="145">
+      <c r="I39" s="49"/>
+      <c r="J39" s="50">
         <v>20</v>
       </c>
-      <c r="K39" s="143">
+      <c r="K39" s="75">
         <v>80</v>
       </c>
-      <c r="L39" s="144">
+      <c r="L39" s="76">
         <v>80</v>
       </c>
       <c r="M39" s="48">
@@ -5514,20 +5517,20 @@
       <c r="B40" s="47">
         <v>36</v>
       </c>
-      <c r="C40" s="141" t="s">
+      <c r="C40" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="142"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="144"/>
-      <c r="G40" s="145"/>
-      <c r="H40" s="143"/>
-      <c r="I40" s="146"/>
-      <c r="J40" s="145">
+      <c r="D40" s="74"/>
+      <c r="E40" s="75"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="75"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="50">
         <v>200</v>
       </c>
-      <c r="K40" s="143"/>
-      <c r="L40" s="144"/>
+      <c r="K40" s="75"/>
+      <c r="L40" s="76"/>
       <c r="M40" s="48">
         <f t="shared" si="68"/>
         <v>5</v>
@@ -5588,28 +5591,28 @@
       <c r="B41" s="47">
         <v>37</v>
       </c>
-      <c r="C41" s="141" t="s">
+      <c r="C41" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="D41" s="142">
+      <c r="D41" s="74">
         <v>160</v>
       </c>
-      <c r="E41" s="143"/>
-      <c r="F41" s="144"/>
-      <c r="G41" s="145">
+      <c r="E41" s="75"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="50">
         <v>120</v>
       </c>
-      <c r="H41" s="143">
+      <c r="H41" s="75">
         <v>120</v>
       </c>
-      <c r="I41" s="146"/>
-      <c r="J41" s="145">
+      <c r="I41" s="49"/>
+      <c r="J41" s="50">
         <v>120</v>
       </c>
-      <c r="K41" s="143">
+      <c r="K41" s="75">
         <v>120</v>
       </c>
-      <c r="L41" s="144">
+      <c r="L41" s="76">
         <v>200</v>
       </c>
       <c r="M41" s="48">
@@ -5672,24 +5675,24 @@
       <c r="B42" s="47">
         <v>38</v>
       </c>
-      <c r="C42" s="141" t="s">
+      <c r="C42" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="142">
+      <c r="D42" s="74">
         <v>80</v>
       </c>
-      <c r="E42" s="143"/>
-      <c r="F42" s="144"/>
-      <c r="G42" s="145"/>
-      <c r="H42" s="143"/>
-      <c r="I42" s="146"/>
-      <c r="J42" s="145">
+      <c r="E42" s="75"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="50">
         <v>80</v>
       </c>
-      <c r="K42" s="143">
+      <c r="K42" s="75">
         <v>80</v>
       </c>
-      <c r="L42" s="144">
+      <c r="L42" s="76">
         <v>80</v>
       </c>
       <c r="M42" s="48">
@@ -5752,22 +5755,22 @@
       <c r="B43" s="47">
         <v>39</v>
       </c>
-      <c r="C43" s="141" t="s">
+      <c r="C43" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="D43" s="142"/>
-      <c r="E43" s="143"/>
-      <c r="F43" s="144"/>
-      <c r="G43" s="145"/>
-      <c r="H43" s="143"/>
-      <c r="I43" s="146"/>
-      <c r="J43" s="145">
+      <c r="D43" s="74"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="50">
         <v>40</v>
       </c>
-      <c r="K43" s="143">
+      <c r="K43" s="75">
         <v>40</v>
       </c>
-      <c r="L43" s="144">
+      <c r="L43" s="76">
         <v>80</v>
       </c>
       <c r="M43" s="48">
@@ -5830,22 +5833,22 @@
       <c r="B44" s="47">
         <v>40</v>
       </c>
-      <c r="C44" s="141" t="s">
+      <c r="C44" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="142"/>
-      <c r="E44" s="143"/>
-      <c r="F44" s="144"/>
-      <c r="G44" s="145"/>
-      <c r="H44" s="143">
+      <c r="D44" s="74"/>
+      <c r="E44" s="75"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="75">
         <v>80</v>
       </c>
-      <c r="I44" s="146"/>
-      <c r="J44" s="145">
+      <c r="I44" s="49"/>
+      <c r="J44" s="50">
         <v>40</v>
       </c>
-      <c r="K44" s="143"/>
-      <c r="L44" s="144">
+      <c r="K44" s="75"/>
+      <c r="L44" s="76">
         <v>40</v>
       </c>
       <c r="M44" s="48">
@@ -5982,23 +5985,35 @@
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A46" s="78"/>
+      <c r="A46" s="78">
+        <v>17</v>
+      </c>
       <c r="B46" s="47">
         <v>42</v>
       </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="75"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="50"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="50"/>
-      <c r="K46" s="75"/>
-      <c r="L46" s="76"/>
+      <c r="C46" s="141" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="142"/>
+      <c r="E46" s="143"/>
+      <c r="F46" s="144"/>
+      <c r="G46" s="145">
+        <v>160</v>
+      </c>
+      <c r="H46" s="143">
+        <v>120</v>
+      </c>
+      <c r="I46" s="146"/>
+      <c r="J46" s="145">
+        <v>160</v>
+      </c>
+      <c r="K46" s="143"/>
+      <c r="L46" s="144">
+        <v>280</v>
+      </c>
       <c r="M46" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N46" s="39">
         <f t="shared" si="18"/>
@@ -6010,11 +6025,11 @@
       </c>
       <c r="P46" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q46" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R46" s="51"/>
       <c r="S46" s="52"/>
@@ -6032,23 +6047,35 @@
       <c r="Y46" s="56"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A47" s="78"/>
+      <c r="A47" s="78">
+        <v>17</v>
+      </c>
       <c r="B47" s="47">
         <v>43</v>
       </c>
-      <c r="C47" s="57"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="50"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="75"/>
-      <c r="L47" s="76"/>
+      <c r="C47" s="141" t="s">
+        <v>167</v>
+      </c>
+      <c r="D47" s="142"/>
+      <c r="E47" s="143"/>
+      <c r="F47" s="144"/>
+      <c r="G47" s="145">
+        <v>80</v>
+      </c>
+      <c r="H47" s="143">
+        <v>80</v>
+      </c>
+      <c r="I47" s="146"/>
+      <c r="J47" s="145">
+        <v>80</v>
+      </c>
+      <c r="K47" s="143"/>
+      <c r="L47" s="144">
+        <v>160</v>
+      </c>
       <c r="M47" s="48">
         <f t="shared" ref="M47:M59" si="76">SUM(D47:L47)/40</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N47" s="39">
         <f t="shared" si="18"/>
@@ -6060,11 +6087,11 @@
       </c>
       <c r="P47" s="73">
         <f t="shared" ref="P47:P59" si="77">SUM(G47:I47)/20</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q47" s="40">
         <f t="shared" ref="Q47:Q59" si="78">SUM(J47:L47)/20</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="52"/>
@@ -6082,23 +6109,35 @@
       <c r="Y47" s="56"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A48" s="78"/>
+      <c r="A48" s="78">
+        <v>17</v>
+      </c>
       <c r="B48" s="47">
         <v>44</v>
       </c>
-      <c r="C48" s="57"/>
-      <c r="D48" s="74"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="75"/>
-      <c r="L48" s="76"/>
+      <c r="C48" s="141" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="142"/>
+      <c r="E48" s="143"/>
+      <c r="F48" s="144"/>
+      <c r="G48" s="145">
+        <v>80</v>
+      </c>
+      <c r="H48" s="143">
+        <v>120</v>
+      </c>
+      <c r="I48" s="146"/>
+      <c r="J48" s="145">
+        <v>160</v>
+      </c>
+      <c r="K48" s="143"/>
+      <c r="L48" s="144">
+        <v>320</v>
+      </c>
       <c r="M48" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N48" s="39">
         <f t="shared" si="18"/>
@@ -6110,11 +6149,11 @@
       </c>
       <c r="P48" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q48" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R48" s="51"/>
       <c r="S48" s="52"/>
@@ -6132,23 +6171,35 @@
       <c r="Y48" s="56"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="78">
+        <v>17</v>
+      </c>
       <c r="B49" s="47">
         <v>45</v>
       </c>
-      <c r="C49" s="57"/>
-      <c r="D49" s="74"/>
-      <c r="E49" s="75"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="50"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="75"/>
-      <c r="L49" s="76"/>
+      <c r="C49" s="141" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="142"/>
+      <c r="E49" s="143"/>
+      <c r="F49" s="144"/>
+      <c r="G49" s="145">
+        <v>160</v>
+      </c>
+      <c r="H49" s="143">
+        <v>160</v>
+      </c>
+      <c r="I49" s="146"/>
+      <c r="J49" s="145">
+        <v>120</v>
+      </c>
+      <c r="K49" s="143"/>
+      <c r="L49" s="144">
+        <v>120</v>
+      </c>
       <c r="M49" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N49" s="39">
         <f t="shared" si="18"/>
@@ -6160,11 +6211,11 @@
       </c>
       <c r="P49" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q49" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R49" s="51"/>
       <c r="S49" s="52"/>
@@ -6182,23 +6233,35 @@
       <c r="Y49" s="56"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A50" s="78"/>
+      <c r="A50" s="78">
+        <v>17</v>
+      </c>
       <c r="B50" s="47">
         <v>46</v>
       </c>
-      <c r="C50" s="57"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="75"/>
-      <c r="L50" s="76"/>
+      <c r="C50" s="141" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50" s="142"/>
+      <c r="E50" s="143"/>
+      <c r="F50" s="144"/>
+      <c r="G50" s="145">
+        <v>120</v>
+      </c>
+      <c r="H50" s="143">
+        <v>120</v>
+      </c>
+      <c r="I50" s="146"/>
+      <c r="J50" s="145">
+        <v>120</v>
+      </c>
+      <c r="K50" s="143"/>
+      <c r="L50" s="144">
+        <v>120</v>
+      </c>
       <c r="M50" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N50" s="39">
         <f t="shared" si="18"/>
@@ -6210,11 +6273,11 @@
       </c>
       <c r="P50" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q50" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R50" s="51"/>
       <c r="S50" s="52"/>
@@ -11563,10 +11626,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="160" t="s">
+      <c r="B132" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="161"/>
+      <c r="C132" s="181"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11581,11 +11644,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>2058</v>
+        <v>2658</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>2157</v>
+        <v>2757</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11593,7 +11656,7 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>3539</v>
+        <v>4179</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
@@ -11601,11 +11664,11 @@
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>4078</v>
+        <v>5078</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>442.75</v>
+        <v>513.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11617,11 +11680,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>210.75</v>
+        <v>270.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>552.75</v>
+        <v>634.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11830,10 +11893,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="173" t="s">
+      <c r="B136" s="168" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="174"/>
+      <c r="C136" s="169"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11924,10 +11987,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="162" t="s">
+      <c r="B137" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="163"/>
+      <c r="C137" s="158"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -11942,11 +12005,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>2058</v>
+        <v>2658</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>2157</v>
+        <v>2757</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -11954,7 +12017,7 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>3539</v>
+        <v>4179</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
@@ -11962,11 +12025,11 @@
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>4078</v>
+        <v>5078</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>442.75</v>
+        <v>513.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11978,11 +12041,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>425.5</v>
+        <v>545.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>1111.5</v>
+        <v>1275.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12019,17 +12082,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12064,24 +12127,24 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="177" t="s">
+      <c r="C3" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="181" t="s">
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="186"/>
+      <c r="H3" s="188" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="182"/>
-      <c r="K3" s="176" t="s">
+      <c r="I3" s="189"/>
+      <c r="K3" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="176"/>
-      <c r="M3" s="176"/>
-      <c r="N3" s="176"/>
-      <c r="O3" s="176"/>
+      <c r="L3" s="183"/>
+      <c r="M3" s="183"/>
+      <c r="N3" s="183"/>
+      <c r="O3" s="183"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12124,22 +12187,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>625</v>
+        <v>670</v>
       </c>
       <c r="E5" s="79">
-        <v>664</v>
+        <v>735</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>1589</v>
+        <v>1705</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>1589</v>
+        <v>1705</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12164,11 +12227,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>25000</v>
+        <v>26800</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>26560</v>
+        <v>29400</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12176,7 +12239,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>63560</v>
+        <v>68200</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12184,7 +12247,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>63560</v>
+        <v>68200</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12311,11 +12374,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-625</v>
+        <v>-670</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-664</v>
+        <v>-735</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12399,14 +12462,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="180"/>
-      <c r="F11" s="180" t="s">
+      <c r="D11" s="187"/>
+      <c r="F11" s="187" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="180"/>
+      <c r="G11" s="187"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12455,7 +12518,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>5023</v>
+        <v>5139</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12506,12 +12569,12 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>200920</v>
-      </c>
-      <c r="S13" s="175" t="s">
+        <v>205560</v>
+      </c>
+      <c r="S13" s="182" t="s">
         <v>153</v>
       </c>
-      <c r="T13" s="175"/>
+      <c r="T13" s="182"/>
       <c r="U13" s="147">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12627,13 +12690,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="176" t="s">
+      <c r="D20" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="176"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="183"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="183"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -12970,23 +13033,23 @@
       <c r="D1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="190"/>
-      <c r="H1" s="186" t="s">
+      <c r="G1" s="156"/>
+      <c r="H1" s="152" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="186" t="s">
+      <c r="I1" s="152" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="186" t="s">
+      <c r="J1" s="152" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="186" t="s">
+      <c r="K1" s="152" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="187" t="s">
+      <c r="L1" s="153" t="s">
         <v>159</v>
       </c>
-      <c r="M1" s="187" t="s">
+      <c r="M1" s="153" t="s">
         <v>161</v>
       </c>
     </row>
@@ -12996,10 +13059,10 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="184" t="s">
+      <c r="I2" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="184">
+      <c r="J2" s="79">
         <v>70</v>
       </c>
       <c r="K2" s="147" t="s">
@@ -13019,10 +13082,10 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="184" t="s">
+      <c r="I3" s="79" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="184">
+      <c r="J3" s="79">
         <v>10</v>
       </c>
       <c r="K3" s="147" t="s">
@@ -13042,10 +13105,10 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="184" t="s">
+      <c r="I4" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="J4" s="184">
+      <c r="J4" s="79">
         <v>9</v>
       </c>
       <c r="K4" s="147" t="s">
@@ -13065,10 +13128,10 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="184" t="s">
+      <c r="I5" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="J5" s="184">
+      <c r="J5" s="79">
         <v>18</v>
       </c>
       <c r="K5" s="147" t="s">
@@ -13088,10 +13151,10 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="184" t="s">
+      <c r="I6" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="J6" s="184">
+      <c r="J6" s="79">
         <v>5</v>
       </c>
       <c r="K6" s="147" t="s">
@@ -13111,10 +13174,10 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="184" t="s">
+      <c r="I7" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="J7" s="184">
+      <c r="J7" s="79">
         <v>14</v>
       </c>
       <c r="K7" s="147" t="s">
@@ -13134,12 +13197,12 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="F8" s="81"/>
-      <c r="G8" s="188"/>
+      <c r="G8" s="154"/>
       <c r="H8" s="81"/>
-      <c r="I8" s="184" t="s">
+      <c r="I8" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="J8" s="184">
+      <c r="J8" s="79">
         <v>13</v>
       </c>
       <c r="K8" s="147" t="s">
@@ -13159,10 +13222,10 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="184" t="s">
+      <c r="I9" s="79" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="184">
+      <c r="J9" s="79">
         <v>4</v>
       </c>
       <c r="K9" s="147" t="s">
@@ -13184,13 +13247,13 @@
       <c r="H10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="184" t="s">
+      <c r="I10" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="184">
+      <c r="J10" s="79">
         <v>12</v>
       </c>
-      <c r="K10" s="185" t="s">
+      <c r="K10" s="151" t="s">
         <v>99</v>
       </c>
       <c r="L10" s="79" t="s">
@@ -13209,13 +13272,13 @@
       <c r="H11" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="184" t="s">
+      <c r="I11" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="184">
+      <c r="J11" s="79">
         <v>19</v>
       </c>
-      <c r="K11" s="185" t="s">
+      <c r="K11" s="151" t="s">
         <v>99</v>
       </c>
       <c r="L11" s="79" t="s">
@@ -13232,13 +13295,13 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="183" t="s">
+      <c r="I12" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="J12" s="183">
+      <c r="J12" s="150">
         <v>13</v>
       </c>
-      <c r="K12" s="183" t="s">
+      <c r="K12" s="150" t="s">
         <v>115</v>
       </c>
       <c r="L12" s="79"/>
@@ -13451,7 +13514,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H22" s="189">
+      <c r="H22" s="155">
         <v>46333</v>
       </c>
       <c r="I22" s="79" t="s">
@@ -13472,7 +13535,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H23" s="189">
+      <c r="H23" s="155">
         <v>46333</v>
       </c>
       <c r="I23" s="79" t="s">
@@ -13493,7 +13556,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H24" s="189">
+      <c r="H24" s="155">
         <v>46333</v>
       </c>
       <c r="I24" s="79" t="s">
@@ -13514,7 +13577,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H25" s="189">
+      <c r="H25" s="155">
         <v>46333</v>
       </c>
       <c r="I25" s="79" t="s">
@@ -13535,7 +13598,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H26" s="189">
+      <c r="H26" s="155">
         <v>46333</v>
       </c>
       <c r="I26" s="79" t="s">
@@ -13685,13 +13748,13 @@
       <c r="H33" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I33" s="183" t="s">
+      <c r="I33" s="150" t="s">
         <v>143</v>
       </c>
-      <c r="J33" s="183">
+      <c r="J33" s="150">
         <v>305</v>
       </c>
-      <c r="K33" s="183" t="s">
+      <c r="K33" s="150" t="s">
         <v>115</v>
       </c>
       <c r="L33" s="79"/>
@@ -13746,17 +13809,19 @@
       <c r="H36" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I36" s="184" t="s">
+      <c r="I36" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="J36" s="184">
+      <c r="J36" s="79">
         <f>M36/40</f>
         <v>10</v>
       </c>
-      <c r="K36" s="184" t="s">
-        <v>142</v>
-      </c>
-      <c r="L36" s="79"/>
+      <c r="K36" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="L36" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M36" s="79">
         <v>400</v>
       </c>
@@ -13765,17 +13830,19 @@
       <c r="H37" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I37" s="184" t="s">
+      <c r="I37" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="J37" s="184">
+      <c r="J37" s="79">
         <f>M37/40</f>
         <v>14</v>
       </c>
-      <c r="K37" s="184" t="s">
-        <v>142</v>
-      </c>
-      <c r="L37" s="79"/>
+      <c r="K37" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="L37" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M37" s="79">
         <v>560</v>
       </c>
@@ -13784,17 +13851,19 @@
       <c r="H38" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I38" s="184" t="s">
+      <c r="I38" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="J38" s="184">
+      <c r="J38" s="79">
         <f>M38/40</f>
         <v>17</v>
       </c>
-      <c r="K38" s="184" t="s">
-        <v>142</v>
-      </c>
-      <c r="L38" s="79"/>
+      <c r="K38" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="L38" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M38" s="79">
         <v>680</v>
       </c>
@@ -13803,17 +13872,19 @@
       <c r="H39" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I39" s="184" t="s">
+      <c r="I39" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="J39" s="184">
+      <c r="J39" s="79">
         <f>M39/40</f>
         <v>18</v>
       </c>
-      <c r="K39" s="184" t="s">
-        <v>142</v>
-      </c>
-      <c r="L39" s="79"/>
+      <c r="K39" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="L39" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M39" s="79">
         <v>720</v>
       </c>
@@ -13822,14 +13893,14 @@
       <c r="H40" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I40" s="184" t="s">
+      <c r="I40" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="J40" s="184">
+      <c r="J40" s="79">
         <f>M40/40</f>
         <v>4</v>
       </c>
-      <c r="K40" s="184" t="s">
+      <c r="K40" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L40" s="79"/>
@@ -13841,14 +13912,14 @@
       <c r="H41" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="I41" s="184" t="s">
-        <v>167</v>
-      </c>
-      <c r="J41" s="184">
+      <c r="I41" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="J41" s="79">
         <v>12</v>
       </c>
-      <c r="K41" s="184" t="s">
-        <v>142</v>
+      <c r="K41" s="147" t="s">
+        <v>99</v>
       </c>
       <c r="L41" s="79"/>
       <c r="M41" s="81">

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66C3BC2-8AC2-42AB-9524-71092C77CB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC201AFF-1F68-46CC-BF4C-64F961CC658F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="180">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -536,6 +536,36 @@
   </si>
   <si>
     <t xml:space="preserve">Risen Shahbagh </t>
+  </si>
+  <si>
+    <t>Rainbow EME</t>
+  </si>
+  <si>
+    <t>Rainbow Model Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Behria Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raja Sab </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Askari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swera Punjab Society </t>
+  </si>
+  <si>
+    <t>Euro NFC</t>
+  </si>
+  <si>
+    <t>18/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubaika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Johar Town </t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1841,6 +1871,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1880,42 +1946,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1938,6 +1968,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2475,14 +2508,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="170">
+      <c r="B1" s="157">
         <f ca="1">TODAY()</f>
         <v>46221</v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2504,10 +2537,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="167" t="s">
+      <c r="A2" s="179" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="158" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2540,13 +2573,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="162" t="s">
+      <c r="M2" s="171"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="163"/>
+      <c r="Q2" s="175"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2565,8 +2598,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="167"/>
-      <c r="B3" s="172"/>
+      <c r="A3" s="179"/>
+      <c r="B3" s="159"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2597,29 +2630,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="164" t="s">
+      <c r="M3" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="165"/>
-      <c r="O3" s="166"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="178"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="174" t="s">
+      <c r="R3" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="175"/>
-      <c r="T3" s="175"/>
-      <c r="U3" s="176"/>
-      <c r="V3" s="177" t="s">
+      <c r="S3" s="162"/>
+      <c r="T3" s="162"/>
+      <c r="U3" s="163"/>
+      <c r="V3" s="164" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="178"/>
-      <c r="X3" s="178"/>
-      <c r="Y3" s="179"/>
+      <c r="W3" s="165"/>
+      <c r="X3" s="165"/>
+      <c r="Y3" s="166"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="167"/>
-      <c r="B4" s="173"/>
+      <c r="A4" s="179"/>
+      <c r="B4" s="160"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11626,10 +11659,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="180" t="s">
+      <c r="B132" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="181"/>
+      <c r="C132" s="168"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11893,10 +11926,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="168" t="s">
+      <c r="B136" s="180" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="169"/>
+      <c r="C136" s="181"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11987,10 +12020,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="157" t="s">
+      <c r="B137" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="158"/>
+      <c r="C137" s="170"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12082,17 +12115,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -13006,7 +13039,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -13894,16 +13927,17 @@
         <v>166</v>
       </c>
       <c r="I40" s="79" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="J40" s="79">
-        <f>M40/40</f>
-        <v>4</v>
-      </c>
-      <c r="K40" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L40" s="79"/>
+        <v>12</v>
+      </c>
+      <c r="K40" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M40" s="79">
         <v>160</v>
       </c>
@@ -13913,18 +13947,170 @@
         <v>166</v>
       </c>
       <c r="I41" s="79" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="J41" s="79">
-        <v>12</v>
-      </c>
-      <c r="K41" s="147" t="s">
-        <v>99</v>
+        <v>4</v>
+      </c>
+      <c r="K41" s="190" t="s">
+        <v>142</v>
       </c>
       <c r="L41" s="79"/>
       <c r="M41" s="81">
         <f>J41*40</f>
-        <v>480</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H42" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I42" s="190" t="s">
+        <v>170</v>
+      </c>
+      <c r="J42" s="79">
+        <v>8</v>
+      </c>
+      <c r="K42" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="79">
+        <f>J42*40</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="43" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H43" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I43" s="190" t="s">
+        <v>171</v>
+      </c>
+      <c r="J43" s="79">
+        <v>9</v>
+      </c>
+      <c r="K43" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="79">
+        <f t="shared" ref="M43:M49" si="1">J43*40</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H44" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I44" s="190" t="s">
+        <v>172</v>
+      </c>
+      <c r="J44" s="79">
+        <v>5</v>
+      </c>
+      <c r="K44" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="79">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H45" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I45" s="190" t="s">
+        <v>173</v>
+      </c>
+      <c r="J45" s="79">
+        <v>5</v>
+      </c>
+      <c r="K45" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="79">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H46" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I46" s="190" t="s">
+        <v>174</v>
+      </c>
+      <c r="J46" s="79">
+        <v>8</v>
+      </c>
+      <c r="K46" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" s="79">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="47" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H47" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I47" s="190" t="s">
+        <v>178</v>
+      </c>
+      <c r="J47" s="79">
+        <v>8</v>
+      </c>
+      <c r="K47" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" s="79">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="48" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H48" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I48" s="190" t="s">
+        <v>175</v>
+      </c>
+      <c r="J48" s="79">
+        <v>20</v>
+      </c>
+      <c r="K48" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="79">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="49" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H49" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I49" s="190" t="s">
+        <v>176</v>
+      </c>
+      <c r="J49" s="79">
+        <v>4</v>
+      </c>
+      <c r="K49" s="190" t="s">
+        <v>142</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="79">
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -13933,7 +14119,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80DF3CCA-0793-4D04-8BF6-1A26354907F3}">
           <x14:formula1>
             <xm:f>Sheet1!$B$10:$B$22</xm:f>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC201AFF-1F68-46CC-BF4C-64F961CC658F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8784412-C76C-43D4-96D5-277BD21D0013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -547,25 +547,25 @@
     <t xml:space="preserve">Rainbow Behria Town </t>
   </si>
   <si>
-    <t xml:space="preserve">Raja Sab </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Askari </t>
-  </si>
-  <si>
     <t xml:space="preserve">Swera Punjab Society </t>
   </si>
   <si>
-    <t>Euro NFC</t>
-  </si>
-  <si>
     <t>18/07/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Rubaika </t>
-  </si>
-  <si>
     <t xml:space="preserve">Jalal Sons Johar Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Askari  Punjab Society </t>
+  </si>
+  <si>
+    <t>Rubaika Velencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro NFC </t>
+  </si>
+  <si>
+    <t>Raja Sab Wapda Town</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1871,6 +1871,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1907,45 +1946,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1968,9 +1968,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2508,14 +2505,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="157">
+      <c r="B1" s="170">
         <f ca="1">TODAY()</f>
         <v>46221</v>
       </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2537,10 +2534,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="167" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="171" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2573,13 +2570,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="171"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="173"/>
-      <c r="P2" s="174" t="s">
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="175"/>
+      <c r="Q2" s="163"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2598,8 +2595,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="179"/>
-      <c r="B3" s="159"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="172"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2630,29 +2627,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="176" t="s">
+      <c r="M3" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="177"/>
-      <c r="O3" s="178"/>
+      <c r="N3" s="165"/>
+      <c r="O3" s="166"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="161" t="s">
+      <c r="R3" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="162"/>
-      <c r="T3" s="162"/>
-      <c r="U3" s="163"/>
-      <c r="V3" s="164" t="s">
+      <c r="S3" s="175"/>
+      <c r="T3" s="175"/>
+      <c r="U3" s="176"/>
+      <c r="V3" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="165"/>
-      <c r="X3" s="165"/>
-      <c r="Y3" s="166"/>
+      <c r="W3" s="178"/>
+      <c r="X3" s="178"/>
+      <c r="Y3" s="179"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="179"/>
-      <c r="B4" s="160"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="173"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11659,10 +11656,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="167" t="s">
+      <c r="B132" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="168"/>
+      <c r="C132" s="181"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11926,10 +11923,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="180" t="s">
+      <c r="B136" s="168" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="181"/>
+      <c r="C136" s="169"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12020,10 +12017,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="169" t="s">
+      <c r="B137" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="170"/>
+      <c r="C137" s="158"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12115,17 +12112,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -13947,12 +13944,12 @@
         <v>166</v>
       </c>
       <c r="I41" s="79" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J41" s="79">
         <v>4</v>
       </c>
-      <c r="K41" s="190" t="s">
+      <c r="K41" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L41" s="79"/>
@@ -13963,15 +13960,15 @@
     </row>
     <row r="42" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I42" s="190" t="s">
+        <v>174</v>
+      </c>
+      <c r="I42" s="79" t="s">
         <v>170</v>
       </c>
       <c r="J42" s="79">
         <v>8</v>
       </c>
-      <c r="K42" s="190" t="s">
+      <c r="K42" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L42" s="2"/>
@@ -13982,15 +13979,15 @@
     </row>
     <row r="43" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H43" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I43" s="190" t="s">
+        <v>174</v>
+      </c>
+      <c r="I43" s="79" t="s">
         <v>171</v>
       </c>
       <c r="J43" s="79">
         <v>9</v>
       </c>
-      <c r="K43" s="190" t="s">
+      <c r="K43" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L43" s="2"/>
@@ -14001,15 +13998,15 @@
     </row>
     <row r="44" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H44" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I44" s="190" t="s">
+        <v>174</v>
+      </c>
+      <c r="I44" s="79" t="s">
         <v>172</v>
       </c>
       <c r="J44" s="79">
         <v>5</v>
       </c>
-      <c r="K44" s="190" t="s">
+      <c r="K44" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L44" s="2"/>
@@ -14020,15 +14017,15 @@
     </row>
     <row r="45" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H45" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I45" s="190" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="I45" s="79" t="s">
+        <v>179</v>
       </c>
       <c r="J45" s="79">
         <v>5</v>
       </c>
-      <c r="K45" s="190" t="s">
+      <c r="K45" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L45" s="2"/>
@@ -14039,15 +14036,15 @@
     </row>
     <row r="46" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H46" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I46" s="190" t="s">
         <v>174</v>
+      </c>
+      <c r="I46" s="79" t="s">
+        <v>176</v>
       </c>
       <c r="J46" s="79">
         <v>8</v>
       </c>
-      <c r="K46" s="190" t="s">
+      <c r="K46" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L46" s="2"/>
@@ -14058,15 +14055,15 @@
     </row>
     <row r="47" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H47" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" s="79" t="s">
         <v>177</v>
-      </c>
-      <c r="I47" s="190" t="s">
-        <v>178</v>
       </c>
       <c r="J47" s="79">
         <v>8</v>
       </c>
-      <c r="K47" s="190" t="s">
+      <c r="K47" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L47" s="2"/>
@@ -14077,15 +14074,15 @@
     </row>
     <row r="48" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H48" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I48" s="190" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="I48" s="79" t="s">
+        <v>173</v>
       </c>
       <c r="J48" s="79">
         <v>20</v>
       </c>
-      <c r="K48" s="190" t="s">
+      <c r="K48" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L48" s="2"/>
@@ -14096,15 +14093,15 @@
     </row>
     <row r="49" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H49" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I49" s="190" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="I49" s="79" t="s">
+        <v>178</v>
       </c>
       <c r="J49" s="79">
         <v>4</v>
       </c>
-      <c r="K49" s="190" t="s">
+      <c r="K49" s="79" t="s">
         <v>142</v>
       </c>
       <c r="L49" s="2"/>
@@ -14114,7 +14111,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="H1:M40" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8784412-C76C-43D4-96D5-277BD21D0013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEB8157-9FA7-4D23-9C9F-A8D2AD41DA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="188">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -566,6 +566,30 @@
   </si>
   <si>
     <t>Raja Sab Wapda Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Askari X </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nabeel Traders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zubaida Traders </t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>Raja Sahb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Askari Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubaika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweera Punjab Society </t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1871,6 +1895,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1910,42 +1974,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1969,6 +1997,19 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2505,14 +2546,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="170">
+      <c r="B1" s="159">
         <f ca="1">TODAY()</f>
-        <v>46221</v>
-      </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
+        <v>46223</v>
+      </c>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2534,10 +2575,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="167" t="s">
+      <c r="A2" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="160" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2570,13 +2611,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="162" t="s">
+      <c r="M2" s="173"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="175"/>
+      <c r="P2" s="176" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="163"/>
+      <c r="Q2" s="177"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2595,8 +2636,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="167"/>
-      <c r="B3" s="172"/>
+      <c r="A3" s="181"/>
+      <c r="B3" s="161"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2627,29 +2668,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="164" t="s">
+      <c r="M3" s="178" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="165"/>
-      <c r="O3" s="166"/>
+      <c r="N3" s="179"/>
+      <c r="O3" s="180"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="174" t="s">
+      <c r="R3" s="163" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="175"/>
-      <c r="T3" s="175"/>
-      <c r="U3" s="176"/>
-      <c r="V3" s="177" t="s">
+      <c r="S3" s="164"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="165"/>
+      <c r="V3" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="178"/>
-      <c r="X3" s="178"/>
-      <c r="Y3" s="179"/>
+      <c r="W3" s="167"/>
+      <c r="X3" s="167"/>
+      <c r="Y3" s="168"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="167"/>
-      <c r="B4" s="173"/>
+      <c r="A4" s="181"/>
+      <c r="B4" s="162"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6325,23 +6366,35 @@
       <c r="Y50" s="56"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A51" s="78"/>
+      <c r="A51" s="78">
+        <v>18</v>
+      </c>
       <c r="B51" s="47">
         <v>47</v>
       </c>
-      <c r="C51" s="57"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="50"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="50"/>
-      <c r="K51" s="75"/>
-      <c r="L51" s="76"/>
+      <c r="C51" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="D51" s="194"/>
+      <c r="E51" s="195"/>
+      <c r="F51" s="196"/>
+      <c r="G51" s="197">
+        <v>40</v>
+      </c>
+      <c r="H51" s="195">
+        <v>40</v>
+      </c>
+      <c r="I51" s="56"/>
+      <c r="J51" s="197">
+        <v>40</v>
+      </c>
+      <c r="K51" s="195"/>
+      <c r="L51" s="196">
+        <v>40</v>
+      </c>
       <c r="M51" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N51" s="39">
         <f t="shared" si="18"/>
@@ -6353,11 +6406,11 @@
       </c>
       <c r="P51" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q51" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R51" s="51"/>
       <c r="S51" s="52"/>
@@ -6375,23 +6428,35 @@
       <c r="Y51" s="56"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A52" s="78"/>
+      <c r="A52" s="78">
+        <v>18</v>
+      </c>
       <c r="B52" s="47">
         <v>48</v>
       </c>
-      <c r="C52" s="57"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="50"/>
-      <c r="K52" s="75"/>
-      <c r="L52" s="76"/>
+      <c r="C52" s="193" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" s="194"/>
+      <c r="E52" s="195"/>
+      <c r="F52" s="196"/>
+      <c r="G52" s="197">
+        <v>80</v>
+      </c>
+      <c r="H52" s="195">
+        <v>40</v>
+      </c>
+      <c r="I52" s="56"/>
+      <c r="J52" s="197">
+        <v>120</v>
+      </c>
+      <c r="K52" s="195"/>
+      <c r="L52" s="196">
+        <v>120</v>
+      </c>
       <c r="M52" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N52" s="39">
         <f t="shared" si="18"/>
@@ -6403,11 +6468,11 @@
       </c>
       <c r="P52" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q52" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R52" s="51"/>
       <c r="S52" s="52"/>
@@ -6425,23 +6490,33 @@
       <c r="Y52" s="56"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A53" s="78"/>
+      <c r="A53" s="78">
+        <v>18</v>
+      </c>
       <c r="B53" s="47">
         <v>49</v>
       </c>
-      <c r="C53" s="57"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="75"/>
-      <c r="F53" s="76"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="75"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="50"/>
-      <c r="K53" s="75"/>
-      <c r="L53" s="76"/>
+      <c r="C53" s="193" t="s">
+        <v>184</v>
+      </c>
+      <c r="D53" s="194"/>
+      <c r="E53" s="195"/>
+      <c r="F53" s="196"/>
+      <c r="G53" s="197"/>
+      <c r="H53" s="195">
+        <v>40</v>
+      </c>
+      <c r="I53" s="56"/>
+      <c r="J53" s="197">
+        <v>80</v>
+      </c>
+      <c r="K53" s="195"/>
+      <c r="L53" s="196">
+        <v>80</v>
+      </c>
       <c r="M53" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N53" s="39">
         <f t="shared" si="18"/>
@@ -6453,11 +6528,11 @@
       </c>
       <c r="P53" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="52"/>
@@ -6475,23 +6550,35 @@
       <c r="Y53" s="56"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A54" s="78"/>
+      <c r="A54" s="78">
+        <v>18</v>
+      </c>
       <c r="B54" s="47">
         <v>50</v>
       </c>
-      <c r="C54" s="57"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="75"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="50"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="49"/>
-      <c r="J54" s="50"/>
-      <c r="K54" s="75"/>
-      <c r="L54" s="76"/>
+      <c r="C54" s="193" t="s">
+        <v>185</v>
+      </c>
+      <c r="D54" s="194"/>
+      <c r="E54" s="195"/>
+      <c r="F54" s="196"/>
+      <c r="G54" s="197">
+        <v>80</v>
+      </c>
+      <c r="H54" s="195">
+        <v>80</v>
+      </c>
+      <c r="I54" s="56"/>
+      <c r="J54" s="197">
+        <v>80</v>
+      </c>
+      <c r="K54" s="195"/>
+      <c r="L54" s="196">
+        <v>80</v>
+      </c>
       <c r="M54" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N54" s="39">
         <f t="shared" si="18"/>
@@ -6503,11 +6590,11 @@
       </c>
       <c r="P54" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q54" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R54" s="51"/>
       <c r="S54" s="52"/>
@@ -6525,23 +6612,35 @@
       <c r="Y54" s="56"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A55" s="78"/>
+      <c r="A55" s="78">
+        <v>18</v>
+      </c>
       <c r="B55" s="47">
         <v>51</v>
       </c>
-      <c r="C55" s="57"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="76"/>
-      <c r="G55" s="50"/>
-      <c r="H55" s="75"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="50"/>
-      <c r="K55" s="75"/>
-      <c r="L55" s="76"/>
+      <c r="C55" s="193" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" s="194"/>
+      <c r="E55" s="195"/>
+      <c r="F55" s="196"/>
+      <c r="G55" s="197">
+        <v>80</v>
+      </c>
+      <c r="H55" s="195">
+        <v>80</v>
+      </c>
+      <c r="I55" s="56"/>
+      <c r="J55" s="197">
+        <v>80</v>
+      </c>
+      <c r="K55" s="195"/>
+      <c r="L55" s="196">
+        <v>80</v>
+      </c>
       <c r="M55" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N55" s="39">
         <f t="shared" si="18"/>
@@ -6553,11 +6652,11 @@
       </c>
       <c r="P55" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q55" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R55" s="51"/>
       <c r="S55" s="52"/>
@@ -6575,23 +6674,35 @@
       <c r="Y55" s="56"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A56" s="78"/>
+      <c r="A56" s="78">
+        <v>18</v>
+      </c>
       <c r="B56" s="47">
         <v>52</v>
       </c>
-      <c r="C56" s="57"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="75"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="75"/>
-      <c r="L56" s="76"/>
+      <c r="C56" s="193" t="s">
+        <v>187</v>
+      </c>
+      <c r="D56" s="194"/>
+      <c r="E56" s="195"/>
+      <c r="F56" s="196"/>
+      <c r="G56" s="197">
+        <v>200</v>
+      </c>
+      <c r="H56" s="195">
+        <v>200</v>
+      </c>
+      <c r="I56" s="56"/>
+      <c r="J56" s="197">
+        <v>200</v>
+      </c>
+      <c r="K56" s="195"/>
+      <c r="L56" s="196">
+        <v>200</v>
+      </c>
       <c r="M56" s="48">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N56" s="39">
         <f t="shared" si="18"/>
@@ -6603,11 +6714,11 @@
       </c>
       <c r="P56" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q56" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R56" s="51"/>
       <c r="S56" s="52"/>
@@ -6625,23 +6736,35 @@
       <c r="Y56" s="56"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="78">
+        <v>18</v>
+      </c>
       <c r="B57" s="47">
         <v>53</v>
       </c>
-      <c r="C57" s="57"/>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="75"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="75"/>
-      <c r="I57" s="132"/>
-      <c r="J57" s="75"/>
-      <c r="K57" s="75"/>
-      <c r="L57" s="75"/>
+      <c r="C57" s="193" t="s">
+        <v>178</v>
+      </c>
+      <c r="D57" s="195"/>
+      <c r="E57" s="195"/>
+      <c r="F57" s="195"/>
+      <c r="G57" s="195">
+        <v>40</v>
+      </c>
+      <c r="H57" s="195">
+        <v>40</v>
+      </c>
+      <c r="I57" s="198"/>
+      <c r="J57" s="195">
+        <v>40</v>
+      </c>
+      <c r="K57" s="195"/>
+      <c r="L57" s="195">
+        <v>40</v>
+      </c>
       <c r="M57" s="135">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N57" s="39">
         <f t="shared" si="18"/>
@@ -6653,11 +6776,11 @@
       </c>
       <c r="P57" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q57" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R57" s="51"/>
       <c r="S57" s="52"/>
@@ -11656,10 +11779,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="180" t="s">
+      <c r="B132" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="181"/>
+      <c r="C132" s="170"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11674,11 +11797,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>2658</v>
+        <v>3178</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>2757</v>
+        <v>3277</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11686,7 +11809,7 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>4179</v>
+        <v>4819</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
@@ -11694,11 +11817,11 @@
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>5078</v>
+        <v>5718</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>513.75</v>
+        <v>571.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11710,11 +11833,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>270.75</v>
+        <v>322.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>634.75</v>
+        <v>698.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11923,10 +12046,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="168" t="s">
+      <c r="B136" s="182" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="169"/>
+      <c r="C136" s="183"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12017,10 +12140,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="157" t="s">
+      <c r="B137" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="158"/>
+      <c r="C137" s="172"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12035,11 +12158,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>2658</v>
+        <v>3178</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>2757</v>
+        <v>3277</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -12047,7 +12170,7 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>4179</v>
+        <v>4819</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
@@ -12055,11 +12178,11 @@
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>5078</v>
+        <v>5718</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>513.75</v>
+        <v>571.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -12071,11 +12194,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>545.5</v>
+        <v>649.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>1275.5</v>
+        <v>1403.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12112,17 +12235,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12157,24 +12280,24 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="184" t="s">
+      <c r="C3" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="188" t="s">
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="190" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="189"/>
-      <c r="K3" s="183" t="s">
+      <c r="I3" s="191"/>
+      <c r="K3" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="183"/>
-      <c r="M3" s="183"/>
-      <c r="N3" s="183"/>
-      <c r="O3" s="183"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="185"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12492,14 +12615,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="187" t="s">
+      <c r="C11" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="187"/>
-      <c r="F11" s="187" t="s">
+      <c r="D11" s="189"/>
+      <c r="F11" s="189" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="187"/>
+      <c r="G11" s="189"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12601,10 +12724,10 @@
         <f>G12*40</f>
         <v>205560</v>
       </c>
-      <c r="S13" s="182" t="s">
+      <c r="S13" s="184" t="s">
         <v>153</v>
       </c>
-      <c r="T13" s="182"/>
+      <c r="T13" s="184"/>
       <c r="U13" s="147">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12720,13 +12843,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="183" t="s">
+      <c r="D20" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="183"/>
-      <c r="F20" s="183"/>
-      <c r="G20" s="183"/>
-      <c r="H20" s="183"/>
+      <c r="E20" s="185"/>
+      <c r="F20" s="185"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="185"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -13036,7 +13159,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -13950,29 +14073,31 @@
         <v>4</v>
       </c>
       <c r="K41" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L41" s="79"/>
+        <v>99</v>
+      </c>
+      <c r="L41" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M41" s="81">
         <f>J41*40</f>
         <v>160</v>
       </c>
     </row>
     <row r="42" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="157" t="s">
         <v>174</v>
       </c>
-      <c r="I42" s="79" t="s">
+      <c r="I42" s="158" t="s">
         <v>170</v>
       </c>
-      <c r="J42" s="79">
+      <c r="J42" s="158">
         <v>8</v>
       </c>
-      <c r="K42" s="79" t="s">
+      <c r="K42" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="79">
+      <c r="L42" s="158"/>
+      <c r="M42" s="158">
         <f>J42*40</f>
         <v>320</v>
       </c>
@@ -13988,29 +14113,31 @@
         <v>9</v>
       </c>
       <c r="K43" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="L43" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M43" s="79">
+        <f t="shared" ref="M43:M52" si="1">J43*40</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H44" s="157" t="s">
+        <v>174</v>
+      </c>
+      <c r="I44" s="158" t="s">
+        <v>172</v>
+      </c>
+      <c r="J44" s="158">
+        <v>5</v>
+      </c>
+      <c r="K44" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="79">
-        <f t="shared" ref="M43:M49" si="1">J43*40</f>
-        <v>360</v>
-      </c>
-    </row>
-    <row r="44" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H44" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I44" s="79" t="s">
-        <v>172</v>
-      </c>
-      <c r="J44" s="79">
-        <v>5</v>
-      </c>
-      <c r="K44" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="79">
+      <c r="L44" s="158"/>
+      <c r="M44" s="158">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -14026,9 +14153,11 @@
         <v>5</v>
       </c>
       <c r="K45" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L45" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="L45" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M45" s="79">
         <f t="shared" si="1"/>
         <v>200</v>
@@ -14045,9 +14174,11 @@
         <v>8</v>
       </c>
       <c r="K46" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L46" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="L46" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M46" s="79">
         <f t="shared" si="1"/>
         <v>320</v>
@@ -14064,9 +14195,11 @@
         <v>8</v>
       </c>
       <c r="K47" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L47" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="L47" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M47" s="79">
         <f t="shared" si="1"/>
         <v>320</v>
@@ -14083,9 +14216,11 @@
         <v>20</v>
       </c>
       <c r="K48" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="L48" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M48" s="79">
         <f t="shared" si="1"/>
         <v>800</v>
@@ -14102,12 +14237,68 @@
         <v>4</v>
       </c>
       <c r="K49" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="L49" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="L49" s="79" t="s">
+        <v>160</v>
+      </c>
       <c r="M49" s="79">
         <f t="shared" si="1"/>
         <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H50" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I50" s="192" t="s">
+        <v>180</v>
+      </c>
+      <c r="J50" s="192">
+        <v>5</v>
+      </c>
+      <c r="K50" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="M50" s="192">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I51" s="192" t="s">
+        <v>181</v>
+      </c>
+      <c r="J51" s="192">
+        <v>300</v>
+      </c>
+      <c r="K51" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="M51" s="192">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="52" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H52" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I52" s="192" t="s">
+        <v>182</v>
+      </c>
+      <c r="J52" s="192">
+        <v>305</v>
+      </c>
+      <c r="K52" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="M52" s="192">
+        <f t="shared" si="1"/>
+        <v>12200</v>
       </c>
     </row>
   </sheetData>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEB8157-9FA7-4D23-9C9F-A8D2AD41DA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B002CF2-3AB2-48EF-91A6-4B606911BCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1497,7 +1497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1899,108 +1899,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2010,6 +1908,105 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2546,14 +2543,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="159">
+      <c r="B1" s="165">
         <f ca="1">TODAY()</f>
         <v>46223</v>
       </c>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2575,10 +2572,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="187" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="160" t="s">
+      <c r="B2" s="166" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2611,13 +2608,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="173"/>
-      <c r="N2" s="174"/>
-      <c r="O2" s="175"/>
-      <c r="P2" s="176" t="s">
+      <c r="M2" s="179"/>
+      <c r="N2" s="180"/>
+      <c r="O2" s="181"/>
+      <c r="P2" s="182" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="177"/>
+      <c r="Q2" s="183"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2636,8 +2633,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="181"/>
-      <c r="B3" s="161"/>
+      <c r="A3" s="187"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2668,29 +2665,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="178" t="s">
+      <c r="M3" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="179"/>
-      <c r="O3" s="180"/>
+      <c r="N3" s="185"/>
+      <c r="O3" s="186"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="163" t="s">
+      <c r="R3" s="169" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="164"/>
-      <c r="T3" s="164"/>
-      <c r="U3" s="165"/>
-      <c r="V3" s="166" t="s">
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="167"/>
-      <c r="X3" s="167"/>
-      <c r="Y3" s="168"/>
+      <c r="W3" s="173"/>
+      <c r="X3" s="173"/>
+      <c r="Y3" s="174"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="181"/>
-      <c r="B4" s="162"/>
+      <c r="A4" s="187"/>
+      <c r="B4" s="168"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6372,24 +6369,24 @@
       <c r="B51" s="47">
         <v>47</v>
       </c>
-      <c r="C51" s="193" t="s">
+      <c r="C51" s="159" t="s">
         <v>175</v>
       </c>
-      <c r="D51" s="194"/>
-      <c r="E51" s="195"/>
-      <c r="F51" s="196"/>
-      <c r="G51" s="197">
+      <c r="D51" s="160"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="163">
         <v>40</v>
       </c>
-      <c r="H51" s="195">
+      <c r="H51" s="161">
         <v>40</v>
       </c>
       <c r="I51" s="56"/>
-      <c r="J51" s="197">
+      <c r="J51" s="163">
         <v>40</v>
       </c>
-      <c r="K51" s="195"/>
-      <c r="L51" s="196">
+      <c r="K51" s="161"/>
+      <c r="L51" s="162">
         <v>40</v>
       </c>
       <c r="M51" s="48">
@@ -6434,24 +6431,24 @@
       <c r="B52" s="47">
         <v>48</v>
       </c>
-      <c r="C52" s="193" t="s">
+      <c r="C52" s="159" t="s">
         <v>112</v>
       </c>
-      <c r="D52" s="194"/>
-      <c r="E52" s="195"/>
-      <c r="F52" s="196"/>
-      <c r="G52" s="197">
+      <c r="D52" s="160"/>
+      <c r="E52" s="161"/>
+      <c r="F52" s="162"/>
+      <c r="G52" s="163">
         <v>80</v>
       </c>
-      <c r="H52" s="195">
+      <c r="H52" s="161">
         <v>40</v>
       </c>
       <c r="I52" s="56"/>
-      <c r="J52" s="197">
+      <c r="J52" s="163">
         <v>120</v>
       </c>
-      <c r="K52" s="195"/>
-      <c r="L52" s="196">
+      <c r="K52" s="161"/>
+      <c r="L52" s="162">
         <v>120</v>
       </c>
       <c r="M52" s="48">
@@ -6496,22 +6493,22 @@
       <c r="B53" s="47">
         <v>49</v>
       </c>
-      <c r="C53" s="193" t="s">
+      <c r="C53" s="159" t="s">
         <v>184</v>
       </c>
-      <c r="D53" s="194"/>
-      <c r="E53" s="195"/>
-      <c r="F53" s="196"/>
-      <c r="G53" s="197"/>
-      <c r="H53" s="195">
+      <c r="D53" s="160"/>
+      <c r="E53" s="161"/>
+      <c r="F53" s="162"/>
+      <c r="G53" s="163"/>
+      <c r="H53" s="161">
         <v>40</v>
       </c>
       <c r="I53" s="56"/>
-      <c r="J53" s="197">
+      <c r="J53" s="163">
         <v>80</v>
       </c>
-      <c r="K53" s="195"/>
-      <c r="L53" s="196">
+      <c r="K53" s="161"/>
+      <c r="L53" s="162">
         <v>80</v>
       </c>
       <c r="M53" s="48">
@@ -6556,24 +6553,24 @@
       <c r="B54" s="47">
         <v>50</v>
       </c>
-      <c r="C54" s="193" t="s">
+      <c r="C54" s="159" t="s">
         <v>185</v>
       </c>
-      <c r="D54" s="194"/>
-      <c r="E54" s="195"/>
-      <c r="F54" s="196"/>
-      <c r="G54" s="197">
+      <c r="D54" s="160"/>
+      <c r="E54" s="161"/>
+      <c r="F54" s="162"/>
+      <c r="G54" s="163">
         <v>80</v>
       </c>
-      <c r="H54" s="195">
+      <c r="H54" s="161">
         <v>80</v>
       </c>
       <c r="I54" s="56"/>
-      <c r="J54" s="197">
+      <c r="J54" s="163">
         <v>80</v>
       </c>
-      <c r="K54" s="195"/>
-      <c r="L54" s="196">
+      <c r="K54" s="161"/>
+      <c r="L54" s="162">
         <v>80</v>
       </c>
       <c r="M54" s="48">
@@ -6618,24 +6615,24 @@
       <c r="B55" s="47">
         <v>51</v>
       </c>
-      <c r="C55" s="193" t="s">
+      <c r="C55" s="159" t="s">
         <v>186</v>
       </c>
-      <c r="D55" s="194"/>
-      <c r="E55" s="195"/>
-      <c r="F55" s="196"/>
-      <c r="G55" s="197">
+      <c r="D55" s="160"/>
+      <c r="E55" s="161"/>
+      <c r="F55" s="162"/>
+      <c r="G55" s="163">
         <v>80</v>
       </c>
-      <c r="H55" s="195">
+      <c r="H55" s="161">
         <v>80</v>
       </c>
       <c r="I55" s="56"/>
-      <c r="J55" s="197">
+      <c r="J55" s="163">
         <v>80</v>
       </c>
-      <c r="K55" s="195"/>
-      <c r="L55" s="196">
+      <c r="K55" s="161"/>
+      <c r="L55" s="162">
         <v>80</v>
       </c>
       <c r="M55" s="48">
@@ -6680,24 +6677,24 @@
       <c r="B56" s="47">
         <v>52</v>
       </c>
-      <c r="C56" s="193" t="s">
+      <c r="C56" s="159" t="s">
         <v>187</v>
       </c>
-      <c r="D56" s="194"/>
-      <c r="E56" s="195"/>
-      <c r="F56" s="196"/>
-      <c r="G56" s="197">
+      <c r="D56" s="160"/>
+      <c r="E56" s="161"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="163">
         <v>200</v>
       </c>
-      <c r="H56" s="195">
+      <c r="H56" s="161">
         <v>200</v>
       </c>
       <c r="I56" s="56"/>
-      <c r="J56" s="197">
+      <c r="J56" s="163">
         <v>200</v>
       </c>
-      <c r="K56" s="195"/>
-      <c r="L56" s="196">
+      <c r="K56" s="161"/>
+      <c r="L56" s="162">
         <v>200</v>
       </c>
       <c r="M56" s="48">
@@ -6742,24 +6739,24 @@
       <c r="B57" s="47">
         <v>53</v>
       </c>
-      <c r="C57" s="193" t="s">
+      <c r="C57" s="159" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="195"/>
-      <c r="E57" s="195"/>
-      <c r="F57" s="195"/>
-      <c r="G57" s="195">
+      <c r="D57" s="161"/>
+      <c r="E57" s="161"/>
+      <c r="F57" s="161"/>
+      <c r="G57" s="161">
         <v>40</v>
       </c>
-      <c r="H57" s="195">
+      <c r="H57" s="161">
         <v>40</v>
       </c>
-      <c r="I57" s="198"/>
-      <c r="J57" s="195">
+      <c r="I57" s="164"/>
+      <c r="J57" s="161">
         <v>40</v>
       </c>
-      <c r="K57" s="195"/>
-      <c r="L57" s="195">
+      <c r="K57" s="161"/>
+      <c r="L57" s="161">
         <v>40</v>
       </c>
       <c r="M57" s="135">
@@ -11779,10 +11776,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="169" t="s">
+      <c r="B132" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="170"/>
+      <c r="C132" s="176"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12046,10 +12043,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="182" t="s">
+      <c r="B136" s="188" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="183"/>
+      <c r="C136" s="189"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12140,10 +12137,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="171" t="s">
+      <c r="B137" s="177" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="172"/>
+      <c r="C137" s="178"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12280,24 +12277,24 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="186" t="s">
+      <c r="C3" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="187"/>
-      <c r="G3" s="188"/>
-      <c r="H3" s="190" t="s">
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
+      <c r="G3" s="194"/>
+      <c r="H3" s="196" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="191"/>
-      <c r="K3" s="185" t="s">
+      <c r="I3" s="197"/>
+      <c r="K3" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="185"/>
-      <c r="M3" s="185"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="185"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
+      <c r="O3" s="191"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12340,22 +12337,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>670</v>
+        <v>705</v>
       </c>
       <c r="E5" s="79">
-        <v>735</v>
+        <v>793</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>1705</v>
+        <v>1798</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>1705</v>
+        <v>1798</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12380,11 +12377,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>26800</v>
+        <v>28200</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>29400</v>
+        <v>31720</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12392,7 +12389,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>68200</v>
+        <v>71920</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12400,7 +12397,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>68200</v>
+        <v>71920</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12527,11 +12524,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-670</v>
+        <v>-705</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-735</v>
+        <v>-793</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12615,14 +12612,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="189" t="s">
+      <c r="C11" s="195" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="189"/>
-      <c r="F11" s="189" t="s">
+      <c r="D11" s="195"/>
+      <c r="F11" s="195" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="189"/>
+      <c r="G11" s="195"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12671,7 +12668,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>5139</v>
+        <v>5232</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12722,12 +12719,12 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>205560</v>
-      </c>
-      <c r="S13" s="184" t="s">
+        <v>209280</v>
+      </c>
+      <c r="S13" s="190" t="s">
         <v>153</v>
       </c>
-      <c r="T13" s="184"/>
+      <c r="T13" s="190"/>
       <c r="U13" s="147">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12843,13 +12840,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="185" t="s">
+      <c r="D20" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="185"/>
-      <c r="F20" s="185"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
+      <c r="E20" s="191"/>
+      <c r="F20" s="191"/>
+      <c r="G20" s="191"/>
+      <c r="H20" s="191"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -14251,16 +14248,16 @@
       <c r="H50" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="I50" s="192" t="s">
+      <c r="I50" s="130" t="s">
         <v>180</v>
       </c>
-      <c r="J50" s="192">
+      <c r="J50" s="130">
         <v>5</v>
       </c>
-      <c r="K50" s="192" t="s">
+      <c r="K50" s="130" t="s">
         <v>142</v>
       </c>
-      <c r="M50" s="192">
+      <c r="M50" s="130">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -14269,16 +14266,16 @@
       <c r="H51" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="I51" s="192" t="s">
+      <c r="I51" s="130" t="s">
         <v>181</v>
       </c>
-      <c r="J51" s="192">
+      <c r="J51" s="130">
         <v>300</v>
       </c>
-      <c r="K51" s="192" t="s">
+      <c r="K51" s="130" t="s">
         <v>142</v>
       </c>
-      <c r="M51" s="192">
+      <c r="M51" s="130">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
@@ -14287,16 +14284,16 @@
       <c r="H52" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="I52" s="192" t="s">
+      <c r="I52" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="J52" s="192">
+      <c r="J52" s="130">
         <v>305</v>
       </c>
-      <c r="K52" s="192" t="s">
+      <c r="K52" s="130" t="s">
         <v>142</v>
       </c>
-      <c r="M52" s="192">
+      <c r="M52" s="130">
         <f t="shared" si="1"/>
         <v>12200</v>
       </c>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B002CF2-3AB2-48EF-91A6-4B606911BCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC18E0D-DD1B-4CF9-911F-DE35DDB0EBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9600" windowHeight="10200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="189">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -590,6 +590,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sweera Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zubaida Traders Al Fateh </t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1858,13 +1861,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1899,14 +1896,43 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1945,45 +1971,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2008,6 +1995,29 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2543,14 +2553,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="165">
+      <c r="B1" s="168">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
-      </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
+        <v>46224</v>
+      </c>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2572,10 +2582,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="187" t="s">
+      <c r="A2" s="165" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="169" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2608,13 +2618,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="179"/>
-      <c r="N2" s="180"/>
-      <c r="O2" s="181"/>
-      <c r="P2" s="182" t="s">
+      <c r="M2" s="157"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="160" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="183"/>
+      <c r="Q2" s="161"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2633,8 +2643,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="187"/>
-      <c r="B3" s="167"/>
+      <c r="A3" s="165"/>
+      <c r="B3" s="170"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2665,29 +2675,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="184" t="s">
+      <c r="M3" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="185"/>
-      <c r="O3" s="186"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="164"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="169" t="s">
+      <c r="R3" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="170"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="171"/>
-      <c r="V3" s="172" t="s">
+      <c r="S3" s="173"/>
+      <c r="T3" s="173"/>
+      <c r="U3" s="174"/>
+      <c r="V3" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="173"/>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="174"/>
+      <c r="W3" s="176"/>
+      <c r="X3" s="176"/>
+      <c r="Y3" s="177"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="187"/>
-      <c r="B4" s="168"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="171"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6059,24 +6069,24 @@
       <c r="B46" s="47">
         <v>42</v>
       </c>
-      <c r="C46" s="141" t="s">
+      <c r="C46" s="188" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="142"/>
-      <c r="E46" s="143"/>
-      <c r="F46" s="144"/>
-      <c r="G46" s="145">
+      <c r="D46" s="189"/>
+      <c r="E46" s="190"/>
+      <c r="F46" s="191"/>
+      <c r="G46" s="192">
         <v>160</v>
       </c>
-      <c r="H46" s="143">
+      <c r="H46" s="190">
         <v>120</v>
       </c>
-      <c r="I46" s="146"/>
-      <c r="J46" s="145">
+      <c r="I46" s="193"/>
+      <c r="J46" s="192">
         <v>160</v>
       </c>
-      <c r="K46" s="143"/>
-      <c r="L46" s="144">
+      <c r="K46" s="190"/>
+      <c r="L46" s="191">
         <v>280</v>
       </c>
       <c r="M46" s="48">
@@ -6121,24 +6131,24 @@
       <c r="B47" s="47">
         <v>43</v>
       </c>
-      <c r="C47" s="141" t="s">
+      <c r="C47" s="188" t="s">
         <v>167</v>
       </c>
-      <c r="D47" s="142"/>
-      <c r="E47" s="143"/>
-      <c r="F47" s="144"/>
-      <c r="G47" s="145">
+      <c r="D47" s="189"/>
+      <c r="E47" s="190"/>
+      <c r="F47" s="191"/>
+      <c r="G47" s="192">
         <v>80</v>
       </c>
-      <c r="H47" s="143">
+      <c r="H47" s="190">
         <v>80</v>
       </c>
-      <c r="I47" s="146"/>
-      <c r="J47" s="145">
+      <c r="I47" s="193"/>
+      <c r="J47" s="192">
         <v>80</v>
       </c>
-      <c r="K47" s="143"/>
-      <c r="L47" s="144">
+      <c r="K47" s="190"/>
+      <c r="L47" s="191">
         <v>160</v>
       </c>
       <c r="M47" s="48">
@@ -6183,24 +6193,24 @@
       <c r="B48" s="47">
         <v>44</v>
       </c>
-      <c r="C48" s="141" t="s">
+      <c r="C48" s="188" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="142"/>
-      <c r="E48" s="143"/>
-      <c r="F48" s="144"/>
-      <c r="G48" s="145">
+      <c r="D48" s="189"/>
+      <c r="E48" s="190"/>
+      <c r="F48" s="191"/>
+      <c r="G48" s="192">
         <v>80</v>
       </c>
-      <c r="H48" s="143">
+      <c r="H48" s="190">
         <v>120</v>
       </c>
-      <c r="I48" s="146"/>
-      <c r="J48" s="145">
+      <c r="I48" s="193"/>
+      <c r="J48" s="192">
         <v>160</v>
       </c>
-      <c r="K48" s="143"/>
-      <c r="L48" s="144">
+      <c r="K48" s="190"/>
+      <c r="L48" s="191">
         <v>320</v>
       </c>
       <c r="M48" s="48">
@@ -6245,24 +6255,24 @@
       <c r="B49" s="47">
         <v>45</v>
       </c>
-      <c r="C49" s="141" t="s">
+      <c r="C49" s="188" t="s">
         <v>168</v>
       </c>
-      <c r="D49" s="142"/>
-      <c r="E49" s="143"/>
-      <c r="F49" s="144"/>
-      <c r="G49" s="145">
+      <c r="D49" s="189"/>
+      <c r="E49" s="190"/>
+      <c r="F49" s="191"/>
+      <c r="G49" s="192">
         <v>160</v>
       </c>
-      <c r="H49" s="143">
+      <c r="H49" s="190">
         <v>160</v>
       </c>
-      <c r="I49" s="146"/>
-      <c r="J49" s="145">
+      <c r="I49" s="193"/>
+      <c r="J49" s="192">
         <v>120</v>
       </c>
-      <c r="K49" s="143"/>
-      <c r="L49" s="144">
+      <c r="K49" s="190"/>
+      <c r="L49" s="191">
         <v>120</v>
       </c>
       <c r="M49" s="48">
@@ -6307,24 +6317,24 @@
       <c r="B50" s="47">
         <v>46</v>
       </c>
-      <c r="C50" s="141" t="s">
+      <c r="C50" s="188" t="s">
         <v>169</v>
       </c>
-      <c r="D50" s="142"/>
-      <c r="E50" s="143"/>
-      <c r="F50" s="144"/>
-      <c r="G50" s="145">
+      <c r="D50" s="189"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="191"/>
+      <c r="G50" s="192">
         <v>120</v>
       </c>
-      <c r="H50" s="143">
+      <c r="H50" s="190">
         <v>120</v>
       </c>
-      <c r="I50" s="146"/>
-      <c r="J50" s="145">
+      <c r="I50" s="193"/>
+      <c r="J50" s="192">
         <v>120</v>
       </c>
-      <c r="K50" s="143"/>
-      <c r="L50" s="144">
+      <c r="K50" s="190"/>
+      <c r="L50" s="191">
         <v>120</v>
       </c>
       <c r="M50" s="48">
@@ -6369,24 +6379,24 @@
       <c r="B51" s="47">
         <v>47</v>
       </c>
-      <c r="C51" s="159" t="s">
+      <c r="C51" s="188" t="s">
         <v>175</v>
       </c>
-      <c r="D51" s="160"/>
-      <c r="E51" s="161"/>
-      <c r="F51" s="162"/>
-      <c r="G51" s="163">
+      <c r="D51" s="189"/>
+      <c r="E51" s="190"/>
+      <c r="F51" s="191"/>
+      <c r="G51" s="192">
         <v>40</v>
       </c>
-      <c r="H51" s="161">
+      <c r="H51" s="190">
         <v>40</v>
       </c>
-      <c r="I51" s="56"/>
-      <c r="J51" s="163">
+      <c r="I51" s="193"/>
+      <c r="J51" s="192">
         <v>40</v>
       </c>
-      <c r="K51" s="161"/>
-      <c r="L51" s="162">
+      <c r="K51" s="190"/>
+      <c r="L51" s="191">
         <v>40</v>
       </c>
       <c r="M51" s="48">
@@ -6431,24 +6441,24 @@
       <c r="B52" s="47">
         <v>48</v>
       </c>
-      <c r="C52" s="159" t="s">
+      <c r="C52" s="188" t="s">
         <v>112</v>
       </c>
-      <c r="D52" s="160"/>
-      <c r="E52" s="161"/>
-      <c r="F52" s="162"/>
-      <c r="G52" s="163">
+      <c r="D52" s="189"/>
+      <c r="E52" s="190"/>
+      <c r="F52" s="191"/>
+      <c r="G52" s="192">
         <v>80</v>
       </c>
-      <c r="H52" s="161">
+      <c r="H52" s="190">
         <v>40</v>
       </c>
-      <c r="I52" s="56"/>
-      <c r="J52" s="163">
+      <c r="I52" s="193"/>
+      <c r="J52" s="192">
         <v>120</v>
       </c>
-      <c r="K52" s="161"/>
-      <c r="L52" s="162">
+      <c r="K52" s="190"/>
+      <c r="L52" s="191">
         <v>120</v>
       </c>
       <c r="M52" s="48">
@@ -6493,22 +6503,22 @@
       <c r="B53" s="47">
         <v>49</v>
       </c>
-      <c r="C53" s="159" t="s">
+      <c r="C53" s="188" t="s">
         <v>184</v>
       </c>
-      <c r="D53" s="160"/>
-      <c r="E53" s="161"/>
-      <c r="F53" s="162"/>
-      <c r="G53" s="163"/>
-      <c r="H53" s="161">
+      <c r="D53" s="189"/>
+      <c r="E53" s="190"/>
+      <c r="F53" s="191"/>
+      <c r="G53" s="192"/>
+      <c r="H53" s="190">
         <v>40</v>
       </c>
-      <c r="I53" s="56"/>
-      <c r="J53" s="163">
+      <c r="I53" s="193"/>
+      <c r="J53" s="192">
         <v>80</v>
       </c>
-      <c r="K53" s="161"/>
-      <c r="L53" s="162">
+      <c r="K53" s="190"/>
+      <c r="L53" s="191">
         <v>80</v>
       </c>
       <c r="M53" s="48">
@@ -6553,24 +6563,24 @@
       <c r="B54" s="47">
         <v>50</v>
       </c>
-      <c r="C54" s="159" t="s">
+      <c r="C54" s="188" t="s">
         <v>185</v>
       </c>
-      <c r="D54" s="160"/>
-      <c r="E54" s="161"/>
-      <c r="F54" s="162"/>
-      <c r="G54" s="163">
+      <c r="D54" s="189"/>
+      <c r="E54" s="190"/>
+      <c r="F54" s="191"/>
+      <c r="G54" s="192">
         <v>80</v>
       </c>
-      <c r="H54" s="161">
+      <c r="H54" s="190">
         <v>80</v>
       </c>
-      <c r="I54" s="56"/>
-      <c r="J54" s="163">
+      <c r="I54" s="193"/>
+      <c r="J54" s="192">
         <v>80</v>
       </c>
-      <c r="K54" s="161"/>
-      <c r="L54" s="162">
+      <c r="K54" s="190"/>
+      <c r="L54" s="191">
         <v>80</v>
       </c>
       <c r="M54" s="48">
@@ -6615,24 +6625,24 @@
       <c r="B55" s="47">
         <v>51</v>
       </c>
-      <c r="C55" s="159" t="s">
+      <c r="C55" s="188" t="s">
         <v>186</v>
       </c>
-      <c r="D55" s="160"/>
-      <c r="E55" s="161"/>
-      <c r="F55" s="162"/>
-      <c r="G55" s="163">
+      <c r="D55" s="189"/>
+      <c r="E55" s="190"/>
+      <c r="F55" s="191"/>
+      <c r="G55" s="192">
         <v>80</v>
       </c>
-      <c r="H55" s="161">
+      <c r="H55" s="190">
         <v>80</v>
       </c>
-      <c r="I55" s="56"/>
-      <c r="J55" s="163">
+      <c r="I55" s="193"/>
+      <c r="J55" s="192">
         <v>80</v>
       </c>
-      <c r="K55" s="161"/>
-      <c r="L55" s="162">
+      <c r="K55" s="190"/>
+      <c r="L55" s="191">
         <v>80</v>
       </c>
       <c r="M55" s="48">
@@ -6677,24 +6687,24 @@
       <c r="B56" s="47">
         <v>52</v>
       </c>
-      <c r="C56" s="159" t="s">
+      <c r="C56" s="188" t="s">
         <v>187</v>
       </c>
-      <c r="D56" s="160"/>
-      <c r="E56" s="161"/>
-      <c r="F56" s="162"/>
-      <c r="G56" s="163">
+      <c r="D56" s="189"/>
+      <c r="E56" s="190"/>
+      <c r="F56" s="191"/>
+      <c r="G56" s="192">
         <v>200</v>
       </c>
-      <c r="H56" s="161">
+      <c r="H56" s="190">
         <v>200</v>
       </c>
-      <c r="I56" s="56"/>
-      <c r="J56" s="163">
+      <c r="I56" s="193"/>
+      <c r="J56" s="192">
         <v>200</v>
       </c>
-      <c r="K56" s="161"/>
-      <c r="L56" s="162">
+      <c r="K56" s="190"/>
+      <c r="L56" s="191">
         <v>200</v>
       </c>
       <c r="M56" s="48">
@@ -6739,24 +6749,24 @@
       <c r="B57" s="47">
         <v>53</v>
       </c>
-      <c r="C57" s="159" t="s">
+      <c r="C57" s="188" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="161"/>
-      <c r="E57" s="161"/>
-      <c r="F57" s="161"/>
-      <c r="G57" s="161">
+      <c r="D57" s="190"/>
+      <c r="E57" s="190"/>
+      <c r="F57" s="190"/>
+      <c r="G57" s="190">
         <v>40</v>
       </c>
-      <c r="H57" s="161">
+      <c r="H57" s="190">
         <v>40</v>
       </c>
-      <c r="I57" s="164"/>
-      <c r="J57" s="161">
+      <c r="I57" s="194"/>
+      <c r="J57" s="190">
         <v>40</v>
       </c>
-      <c r="K57" s="161"/>
-      <c r="L57" s="161">
+      <c r="K57" s="190"/>
+      <c r="L57" s="190">
         <v>40</v>
       </c>
       <c r="M57" s="135">
@@ -6795,23 +6805,37 @@
       <c r="Y57" s="56"/>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A58" s="78"/>
+      <c r="A58" s="78">
+        <v>20</v>
+      </c>
       <c r="B58" s="47">
         <v>54</v>
       </c>
-      <c r="C58" s="57"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="75"/>
-      <c r="F58" s="75"/>
-      <c r="G58" s="75"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="132"/>
-      <c r="J58" s="75"/>
-      <c r="K58" s="75"/>
-      <c r="L58" s="75"/>
+      <c r="C58" s="141" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" s="142"/>
+      <c r="E58" s="142"/>
+      <c r="F58" s="142"/>
+      <c r="G58" s="142">
+        <v>1189</v>
+      </c>
+      <c r="H58" s="142">
+        <v>1395</v>
+      </c>
+      <c r="I58" s="195"/>
+      <c r="J58" s="142">
+        <v>2398</v>
+      </c>
+      <c r="K58" s="142">
+        <v>2397</v>
+      </c>
+      <c r="L58" s="142">
+        <v>4800</v>
+      </c>
       <c r="M58" s="135">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>304.47500000000002</v>
       </c>
       <c r="N58" s="39">
         <f t="shared" si="18"/>
@@ -6823,11 +6847,11 @@
       </c>
       <c r="P58" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="Q58" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>479.75</v>
       </c>
       <c r="R58" s="51"/>
       <c r="S58" s="52"/>
@@ -6845,23 +6869,37 @@
       <c r="Y58" s="56"/>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A59" s="78"/>
+      <c r="A59" s="78">
+        <v>20</v>
+      </c>
       <c r="B59" s="47">
         <v>55</v>
       </c>
-      <c r="C59" s="57"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
-      <c r="F59" s="75"/>
-      <c r="G59" s="75"/>
-      <c r="H59" s="75"/>
-      <c r="I59" s="132"/>
-      <c r="J59" s="75"/>
-      <c r="K59" s="75"/>
-      <c r="L59" s="75"/>
+      <c r="C59" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" s="142"/>
+      <c r="E59" s="142"/>
+      <c r="F59" s="142"/>
+      <c r="G59" s="142">
+        <v>40</v>
+      </c>
+      <c r="H59" s="142">
+        <v>40</v>
+      </c>
+      <c r="I59" s="195"/>
+      <c r="J59" s="142">
+        <v>40</v>
+      </c>
+      <c r="K59" s="142">
+        <v>40</v>
+      </c>
+      <c r="L59" s="142">
+        <v>40</v>
+      </c>
       <c r="M59" s="135">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N59" s="39">
         <f t="shared" si="18"/>
@@ -6873,11 +6911,11 @@
       </c>
       <c r="P59" s="73">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q59" s="40">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R59" s="51"/>
       <c r="S59" s="52"/>
@@ -11776,10 +11814,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="175" t="s">
+      <c r="B132" s="178" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="176"/>
+      <c r="C132" s="179"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11794,11 +11832,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>3178</v>
+        <v>4407</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>3277</v>
+        <v>4712</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11806,19 +11844,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>4819</v>
+        <v>7257</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>3438</v>
+        <v>5875</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>5718</v>
+        <v>10558</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>571.75</v>
+        <v>881.22500000000002</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11830,11 +11868,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>322.75</v>
+        <v>455.95</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>698.75</v>
+        <v>1184.5</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12043,10 +12081,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="188" t="s">
+      <c r="B136" s="166" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="189"/>
+      <c r="C136" s="167"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12137,10 +12175,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="177" t="s">
+      <c r="B137" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="178"/>
+      <c r="C137" s="156"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12155,11 +12193,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>3178</v>
+        <v>4407</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>3277</v>
+        <v>4712</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -12167,19 +12205,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>4819</v>
+        <v>7257</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>3438</v>
+        <v>5875</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>5718</v>
+        <v>10558</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>571.75</v>
+        <v>881.22500000000002</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -12191,11 +12229,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>649.5</v>
+        <v>915.9</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>1403.5</v>
+        <v>2375</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12232,17 +12270,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12277,24 +12315,24 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="192" t="s">
+      <c r="C3" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="193"/>
-      <c r="E3" s="193"/>
-      <c r="F3" s="193"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="196" t="s">
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="186" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="197"/>
-      <c r="K3" s="191" t="s">
+      <c r="I3" s="187"/>
+      <c r="K3" s="181" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
-      <c r="N3" s="191"/>
-      <c r="O3" s="191"/>
+      <c r="L3" s="181"/>
+      <c r="M3" s="181"/>
+      <c r="N3" s="181"/>
+      <c r="O3" s="181"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12337,22 +12375,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>705</v>
+        <v>744</v>
       </c>
       <c r="E5" s="79">
-        <v>793</v>
+        <v>1103</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>1798</v>
+        <v>2147</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>1798</v>
+        <v>2147</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12377,11 +12415,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>28200</v>
+        <v>29760</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>31720</v>
+        <v>44120</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12389,7 +12427,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>71920</v>
+        <v>85880</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12397,7 +12435,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>71920</v>
+        <v>85880</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12417,19 +12455,19 @@
       </c>
       <c r="S6" s="129"/>
       <c r="T6" s="129"/>
-      <c r="U6" s="149">
+      <c r="U6" s="145">
         <v>46180</v>
       </c>
-      <c r="V6" s="149">
+      <c r="V6" s="145">
         <v>46180</v>
       </c>
-      <c r="W6" s="149">
+      <c r="W6" s="145">
         <v>46333</v>
       </c>
-      <c r="X6" s="149">
+      <c r="X6" s="145">
         <v>46210</v>
       </c>
-      <c r="Y6" s="149">
+      <c r="Y6" s="145">
         <v>46210</v>
       </c>
     </row>
@@ -12449,28 +12487,28 @@
       <c r="O7" s="81">
         <v>35</v>
       </c>
-      <c r="S7" s="148" t="s">
+      <c r="S7" s="144" t="s">
         <v>155</v>
       </c>
-      <c r="T7" s="148" t="s">
+      <c r="T7" s="144" t="s">
         <v>154</v>
       </c>
       <c r="U7" s="77" t="s">
         <v>148</v>
       </c>
-      <c r="V7" s="148" t="s">
+      <c r="V7" s="144" t="s">
         <v>152</v>
       </c>
-      <c r="W7" s="148" t="s">
+      <c r="W7" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="X7" s="148" t="s">
+      <c r="X7" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="Y7" s="148" t="s">
+      <c r="Y7" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="Z7" s="148" t="s">
+      <c r="Z7" s="144" t="s">
         <v>153</v>
       </c>
     </row>
@@ -12500,7 +12538,7 @@
       <c r="T8" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="U8" s="147">
+      <c r="U8" s="143">
         <v>50</v>
       </c>
       <c r="V8" s="79">
@@ -12524,11 +12562,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-705</v>
+        <v>-744</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-793</v>
+        <v>-1103</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12552,7 +12590,7 @@
       <c r="T9" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="147">
+      <c r="U9" s="143">
         <v>50</v>
       </c>
       <c r="V9" s="79">
@@ -12595,7 +12633,7 @@
       <c r="T10" s="79" t="s">
         <v>149</v>
       </c>
-      <c r="U10" s="147"/>
+      <c r="U10" s="143"/>
       <c r="V10" s="79">
         <v>3</v>
       </c>
@@ -12612,14 +12650,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="195" t="s">
+      <c r="C11" s="185" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="195"/>
-      <c r="F11" s="195" t="s">
+      <c r="D11" s="185"/>
+      <c r="F11" s="185" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="195"/>
+      <c r="G11" s="185"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12642,7 +12680,7 @@
       <c r="T11" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="U11" s="147"/>
+      <c r="U11" s="143"/>
       <c r="V11" s="79"/>
       <c r="W11" s="79"/>
       <c r="X11" s="79">
@@ -12668,7 +12706,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>5232</v>
+        <v>5581</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12692,7 +12730,7 @@
       <c r="T12" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="U12" s="147"/>
+      <c r="U12" s="143"/>
       <c r="V12" s="79"/>
       <c r="W12" s="79"/>
       <c r="X12" s="79">
@@ -12719,13 +12757,13 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>209280</v>
-      </c>
-      <c r="S13" s="190" t="s">
+        <v>223240</v>
+      </c>
+      <c r="S13" s="180" t="s">
         <v>153</v>
       </c>
-      <c r="T13" s="190"/>
-      <c r="U13" s="147">
+      <c r="T13" s="180"/>
+      <c r="U13" s="143">
         <f>SUM(U8:U12)</f>
         <v>100</v>
       </c>
@@ -12840,13 +12878,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="191" t="s">
+      <c r="D20" s="181" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="191"/>
-      <c r="F20" s="191"/>
-      <c r="G20" s="191"/>
-      <c r="H20" s="191"/>
+      <c r="E20" s="181"/>
+      <c r="F20" s="181"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="181"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -13156,7 +13194,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -13183,23 +13221,23 @@
       <c r="D1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="152" t="s">
+      <c r="G1" s="152"/>
+      <c r="H1" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="148" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="152" t="s">
+      <c r="J1" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="152" t="s">
+      <c r="K1" s="148" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="153" t="s">
+      <c r="L1" s="149" t="s">
         <v>159</v>
       </c>
-      <c r="M1" s="153" t="s">
+      <c r="M1" s="149" t="s">
         <v>161</v>
       </c>
     </row>
@@ -13215,7 +13253,7 @@
       <c r="J2" s="79">
         <v>70</v>
       </c>
-      <c r="K2" s="147" t="s">
+      <c r="K2" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L2" s="79" t="s">
@@ -13238,7 +13276,7 @@
       <c r="J3" s="79">
         <v>10</v>
       </c>
-      <c r="K3" s="147" t="s">
+      <c r="K3" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L3" s="79" t="s">
@@ -13261,7 +13299,7 @@
       <c r="J4" s="79">
         <v>9</v>
       </c>
-      <c r="K4" s="147" t="s">
+      <c r="K4" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L4" s="79" t="s">
@@ -13284,7 +13322,7 @@
       <c r="J5" s="79">
         <v>18</v>
       </c>
-      <c r="K5" s="147" t="s">
+      <c r="K5" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L5" s="79" t="s">
@@ -13307,7 +13345,7 @@
       <c r="J6" s="79">
         <v>5</v>
       </c>
-      <c r="K6" s="147" t="s">
+      <c r="K6" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L6" s="79" t="s">
@@ -13330,7 +13368,7 @@
       <c r="J7" s="79">
         <v>14</v>
       </c>
-      <c r="K7" s="147" t="s">
+      <c r="K7" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L7" s="79" t="s">
@@ -13347,7 +13385,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="F8" s="81"/>
-      <c r="G8" s="154"/>
+      <c r="G8" s="150"/>
       <c r="H8" s="81"/>
       <c r="I8" s="79" t="s">
         <v>106</v>
@@ -13355,7 +13393,7 @@
       <c r="J8" s="79">
         <v>13</v>
       </c>
-      <c r="K8" s="147" t="s">
+      <c r="K8" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L8" s="79" t="s">
@@ -13378,7 +13416,7 @@
       <c r="J9" s="79">
         <v>4</v>
       </c>
-      <c r="K9" s="147" t="s">
+      <c r="K9" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L9" s="79" t="s">
@@ -13403,7 +13441,7 @@
       <c r="J10" s="79">
         <v>12</v>
       </c>
-      <c r="K10" s="151" t="s">
+      <c r="K10" s="147" t="s">
         <v>99</v>
       </c>
       <c r="L10" s="79" t="s">
@@ -13428,7 +13466,7 @@
       <c r="J11" s="79">
         <v>19</v>
       </c>
-      <c r="K11" s="151" t="s">
+      <c r="K11" s="147" t="s">
         <v>99</v>
       </c>
       <c r="L11" s="79" t="s">
@@ -13445,13 +13483,13 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="150" t="s">
+      <c r="I12" s="146" t="s">
         <v>114</v>
       </c>
-      <c r="J12" s="150">
+      <c r="J12" s="146">
         <v>13</v>
       </c>
-      <c r="K12" s="150" t="s">
+      <c r="K12" s="146" t="s">
         <v>115</v>
       </c>
       <c r="L12" s="79"/>
@@ -13472,7 +13510,7 @@
       <c r="J13" s="79">
         <v>5</v>
       </c>
-      <c r="K13" s="147" t="s">
+      <c r="K13" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L13" s="79" t="s">
@@ -13495,7 +13533,7 @@
       <c r="J14" s="79">
         <v>8</v>
       </c>
-      <c r="K14" s="147" t="s">
+      <c r="K14" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L14" s="79" t="s">
@@ -13518,7 +13556,7 @@
       <c r="J15" s="79">
         <v>10</v>
       </c>
-      <c r="K15" s="147" t="s">
+      <c r="K15" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L15" s="79" t="s">
@@ -13541,7 +13579,7 @@
       <c r="J16" s="79">
         <v>5</v>
       </c>
-      <c r="K16" s="147" t="s">
+      <c r="K16" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L16" s="79" t="s">
@@ -13564,7 +13602,7 @@
       <c r="J17" s="79">
         <v>4</v>
       </c>
-      <c r="K17" s="147" t="s">
+      <c r="K17" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L17" s="79" t="s">
@@ -13587,7 +13625,7 @@
       <c r="J18" s="79">
         <v>9</v>
       </c>
-      <c r="K18" s="147" t="s">
+      <c r="K18" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L18" s="79" t="s">
@@ -13610,7 +13648,7 @@
       <c r="J19" s="79">
         <v>6</v>
       </c>
-      <c r="K19" s="147" t="s">
+      <c r="K19" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L19" s="79" t="s">
@@ -13633,7 +13671,7 @@
       <c r="J20" s="79">
         <v>30</v>
       </c>
-      <c r="K20" s="147" t="s">
+      <c r="K20" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L20" s="79" t="s">
@@ -13652,7 +13690,7 @@
       <c r="J21" s="79">
         <v>22</v>
       </c>
-      <c r="K21" s="147" t="s">
+      <c r="K21" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L21" s="79" t="s">
@@ -13664,7 +13702,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H22" s="155">
+      <c r="H22" s="151">
         <v>46333</v>
       </c>
       <c r="I22" s="79" t="s">
@@ -13673,7 +13711,7 @@
       <c r="J22" s="79">
         <v>15</v>
       </c>
-      <c r="K22" s="147" t="s">
+      <c r="K22" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L22" s="79" t="s">
@@ -13685,7 +13723,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H23" s="155">
+      <c r="H23" s="151">
         <v>46333</v>
       </c>
       <c r="I23" s="79" t="s">
@@ -13694,7 +13732,7 @@
       <c r="J23" s="79">
         <v>4</v>
       </c>
-      <c r="K23" s="147" t="s">
+      <c r="K23" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L23" s="79" t="s">
@@ -13706,7 +13744,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H24" s="155">
+      <c r="H24" s="151">
         <v>46333</v>
       </c>
       <c r="I24" s="79" t="s">
@@ -13715,7 +13753,7 @@
       <c r="J24" s="79">
         <v>50</v>
       </c>
-      <c r="K24" s="147" t="s">
+      <c r="K24" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L24" s="79" t="s">
@@ -13727,7 +13765,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H25" s="155">
+      <c r="H25" s="151">
         <v>46333</v>
       </c>
       <c r="I25" s="79" t="s">
@@ -13736,7 +13774,7 @@
       <c r="J25" s="79">
         <v>5</v>
       </c>
-      <c r="K25" s="147" t="s">
+      <c r="K25" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L25" s="79" t="s">
@@ -13748,7 +13786,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H26" s="155">
+      <c r="H26" s="151">
         <v>46333</v>
       </c>
       <c r="I26" s="79" t="s">
@@ -13757,7 +13795,7 @@
       <c r="J26" s="79">
         <v>50</v>
       </c>
-      <c r="K26" s="147" t="s">
+      <c r="K26" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L26" s="79" t="s">
@@ -13778,7 +13816,7 @@
       <c r="J27" s="79">
         <v>5</v>
       </c>
-      <c r="K27" s="147" t="s">
+      <c r="K27" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L27" s="79" t="s">
@@ -13799,7 +13837,7 @@
       <c r="J28" s="79">
         <v>7</v>
       </c>
-      <c r="K28" s="147" t="s">
+      <c r="K28" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L28" s="79" t="s">
@@ -13820,7 +13858,7 @@
       <c r="J29" s="79">
         <v>21</v>
       </c>
-      <c r="K29" s="147" t="s">
+      <c r="K29" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L29" s="79" t="s">
@@ -13841,7 +13879,7 @@
       <c r="J30" s="79">
         <v>8</v>
       </c>
-      <c r="K30" s="147" t="s">
+      <c r="K30" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L30" s="79" t="s">
@@ -13862,7 +13900,7 @@
       <c r="J31" s="79">
         <v>4</v>
       </c>
-      <c r="K31" s="147" t="s">
+      <c r="K31" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L31" s="79" t="s">
@@ -13883,7 +13921,7 @@
       <c r="J32" s="79">
         <v>4</v>
       </c>
-      <c r="K32" s="147" t="s">
+      <c r="K32" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L32" s="79" t="s">
@@ -13898,13 +13936,13 @@
       <c r="H33" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I33" s="150" t="s">
+      <c r="I33" s="146" t="s">
         <v>143</v>
       </c>
-      <c r="J33" s="150">
+      <c r="J33" s="146">
         <v>305</v>
       </c>
-      <c r="K33" s="150" t="s">
+      <c r="K33" s="146" t="s">
         <v>115</v>
       </c>
       <c r="L33" s="79"/>
@@ -13923,7 +13961,7 @@
       <c r="J34" s="79">
         <v>35</v>
       </c>
-      <c r="K34" s="147" t="s">
+      <c r="K34" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L34" s="79" t="s">
@@ -13944,7 +13982,7 @@
       <c r="J35" s="79">
         <v>122</v>
       </c>
-      <c r="K35" s="147" t="s">
+      <c r="K35" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L35" s="79" t="s">
@@ -13966,7 +14004,7 @@
         <f>M36/40</f>
         <v>10</v>
       </c>
-      <c r="K36" s="147" t="s">
+      <c r="K36" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L36" s="79" t="s">
@@ -13987,7 +14025,7 @@
         <f>M37/40</f>
         <v>14</v>
       </c>
-      <c r="K37" s="147" t="s">
+      <c r="K37" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L37" s="79" t="s">
@@ -14008,7 +14046,7 @@
         <f>M38/40</f>
         <v>17</v>
       </c>
-      <c r="K38" s="147" t="s">
+      <c r="K38" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L38" s="79" t="s">
@@ -14029,7 +14067,7 @@
         <f>M39/40</f>
         <v>18</v>
       </c>
-      <c r="K39" s="147" t="s">
+      <c r="K39" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L39" s="79" t="s">
@@ -14049,7 +14087,7 @@
       <c r="J40" s="79">
         <v>12</v>
       </c>
-      <c r="K40" s="147" t="s">
+      <c r="K40" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L40" s="79" t="s">
@@ -14081,20 +14119,20 @@
       </c>
     </row>
     <row r="42" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H42" s="157" t="s">
+      <c r="H42" s="153" t="s">
         <v>174</v>
       </c>
-      <c r="I42" s="158" t="s">
+      <c r="I42" s="154" t="s">
         <v>170</v>
       </c>
-      <c r="J42" s="158">
+      <c r="J42" s="154">
         <v>8</v>
       </c>
-      <c r="K42" s="158" t="s">
+      <c r="K42" s="154" t="s">
         <v>142</v>
       </c>
-      <c r="L42" s="158"/>
-      <c r="M42" s="158">
+      <c r="L42" s="154"/>
+      <c r="M42" s="154">
         <f>J42*40</f>
         <v>320</v>
       </c>
@@ -14116,25 +14154,25 @@
         <v>160</v>
       </c>
       <c r="M43" s="79">
-        <f t="shared" ref="M43:M52" si="1">J43*40</f>
+        <f t="shared" ref="M43:M53" si="1">J43*40</f>
         <v>360</v>
       </c>
     </row>
     <row r="44" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H44" s="157" t="s">
+      <c r="H44" s="153" t="s">
         <v>174</v>
       </c>
-      <c r="I44" s="158" t="s">
+      <c r="I44" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="J44" s="158">
+      <c r="J44" s="154">
         <v>5</v>
       </c>
-      <c r="K44" s="158" t="s">
+      <c r="K44" s="154" t="s">
         <v>142</v>
       </c>
-      <c r="L44" s="158"/>
-      <c r="M44" s="158">
+      <c r="L44" s="154"/>
+      <c r="M44" s="154">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -14255,7 +14293,10 @@
         <v>5</v>
       </c>
       <c r="K50" s="130" t="s">
-        <v>142</v>
+        <v>99</v>
+      </c>
+      <c r="L50" s="196" t="s">
+        <v>160</v>
       </c>
       <c r="M50" s="130">
         <f t="shared" si="1"/>
@@ -14267,35 +14308,48 @@
         <v>183</v>
       </c>
       <c r="I51" s="130" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J51" s="130">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K51" s="130" t="s">
-        <v>142</v>
+        <v>99</v>
+      </c>
+      <c r="L51" s="196" t="s">
+        <v>160</v>
       </c>
       <c r="M51" s="130">
         <f t="shared" si="1"/>
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="52" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H52" s="153" t="s">
+        <v>183</v>
+      </c>
+      <c r="I52" s="197" t="s">
+        <v>181</v>
+      </c>
+      <c r="J52" s="197">
+        <v>300</v>
+      </c>
+      <c r="K52" s="197" t="s">
+        <v>142</v>
+      </c>
+      <c r="L52" s="198"/>
+      <c r="M52" s="197">
+        <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
-    <row r="52" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H52" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I52" s="130" t="s">
-        <v>182</v>
-      </c>
-      <c r="J52" s="130">
-        <v>305</v>
-      </c>
-      <c r="K52" s="130" t="s">
-        <v>142</v>
-      </c>
-      <c r="M52" s="130">
+    <row r="53" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="I53" s="196"/>
+      <c r="J53" s="196"/>
+      <c r="K53" s="196"/>
+      <c r="M53" s="196">
         <f t="shared" si="1"/>
-        <v>12200</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14303,7 +14357,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80DF3CCA-0793-4D04-8BF6-1A26354907F3}">
           <x14:formula1>
             <xm:f>Sheet1!$B$10:$B$22</xm:f>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC18E0D-DD1B-4CF9-911F-DE35DDB0EBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBF0201-7F17-4EE2-94AF-ABD1862027D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9600" windowHeight="10200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="196">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -593,6 +593,27 @@
   </si>
   <si>
     <t xml:space="preserve">Zubaida Traders Al Fateh </t>
+  </si>
+  <si>
+    <t>21/07/26</t>
+  </si>
+  <si>
+    <t>Rainbow Barki Road</t>
+  </si>
+  <si>
+    <t>Risen Askari 11</t>
+  </si>
+  <si>
+    <t>Rainbow Defence Road</t>
+  </si>
+  <si>
+    <t>Euro K-2</t>
+  </si>
+  <si>
+    <t>Euro D-2</t>
+  </si>
+  <si>
+    <t>Not Deliver</t>
   </si>
 </sst>
 </file>
@@ -704,7 +725,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -777,6 +798,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="58">
     <border>
@@ -1500,7 +1527,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1883,9 +1910,6 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1896,6 +1920,61 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1935,42 +2014,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1995,29 +2038,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2553,14 +2573,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="168">
+      <c r="B1" s="163">
         <f ca="1">TODAY()</f>
         <v>46224</v>
       </c>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2582,10 +2602,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="169" t="s">
+      <c r="B2" s="164" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2618,13 +2638,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="157"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="160" t="s">
+      <c r="M2" s="177"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="179"/>
+      <c r="P2" s="180" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="161"/>
+      <c r="Q2" s="181"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2643,8 +2663,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="165"/>
-      <c r="B3" s="170"/>
+      <c r="A3" s="185"/>
+      <c r="B3" s="165"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2675,29 +2695,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="162" t="s">
+      <c r="M3" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="163"/>
-      <c r="O3" s="164"/>
+      <c r="N3" s="183"/>
+      <c r="O3" s="184"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="172" t="s">
+      <c r="R3" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="173"/>
-      <c r="T3" s="173"/>
-      <c r="U3" s="174"/>
-      <c r="V3" s="175" t="s">
+      <c r="S3" s="168"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169"/>
+      <c r="V3" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="176"/>
-      <c r="X3" s="176"/>
-      <c r="Y3" s="177"/>
+      <c r="W3" s="171"/>
+      <c r="X3" s="171"/>
+      <c r="Y3" s="172"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="165"/>
-      <c r="B4" s="171"/>
+      <c r="A4" s="185"/>
+      <c r="B4" s="166"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6069,24 +6089,24 @@
       <c r="B46" s="47">
         <v>42</v>
       </c>
-      <c r="C46" s="188" t="s">
+      <c r="C46" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="189"/>
-      <c r="E46" s="190"/>
-      <c r="F46" s="191"/>
-      <c r="G46" s="192">
+      <c r="D46" s="74"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="50">
         <v>160</v>
       </c>
-      <c r="H46" s="190">
+      <c r="H46" s="75">
         <v>120</v>
       </c>
-      <c r="I46" s="193"/>
-      <c r="J46" s="192">
+      <c r="I46" s="49"/>
+      <c r="J46" s="50">
         <v>160</v>
       </c>
-      <c r="K46" s="190"/>
-      <c r="L46" s="191">
+      <c r="K46" s="75"/>
+      <c r="L46" s="76">
         <v>280</v>
       </c>
       <c r="M46" s="48">
@@ -6131,24 +6151,24 @@
       <c r="B47" s="47">
         <v>43</v>
       </c>
-      <c r="C47" s="188" t="s">
+      <c r="C47" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="D47" s="189"/>
-      <c r="E47" s="190"/>
-      <c r="F47" s="191"/>
-      <c r="G47" s="192">
+      <c r="D47" s="74"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="50">
         <v>80</v>
       </c>
-      <c r="H47" s="190">
+      <c r="H47" s="75">
         <v>80</v>
       </c>
-      <c r="I47" s="193"/>
-      <c r="J47" s="192">
+      <c r="I47" s="49"/>
+      <c r="J47" s="50">
         <v>80</v>
       </c>
-      <c r="K47" s="190"/>
-      <c r="L47" s="191">
+      <c r="K47" s="75"/>
+      <c r="L47" s="76">
         <v>160</v>
       </c>
       <c r="M47" s="48">
@@ -6193,24 +6213,24 @@
       <c r="B48" s="47">
         <v>44</v>
       </c>
-      <c r="C48" s="188" t="s">
+      <c r="C48" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="189"/>
-      <c r="E48" s="190"/>
-      <c r="F48" s="191"/>
-      <c r="G48" s="192">
+      <c r="D48" s="74"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="50">
         <v>80</v>
       </c>
-      <c r="H48" s="190">
+      <c r="H48" s="75">
         <v>120</v>
       </c>
-      <c r="I48" s="193"/>
-      <c r="J48" s="192">
+      <c r="I48" s="49"/>
+      <c r="J48" s="50">
         <v>160</v>
       </c>
-      <c r="K48" s="190"/>
-      <c r="L48" s="191">
+      <c r="K48" s="75"/>
+      <c r="L48" s="76">
         <v>320</v>
       </c>
       <c r="M48" s="48">
@@ -6255,24 +6275,24 @@
       <c r="B49" s="47">
         <v>45</v>
       </c>
-      <c r="C49" s="188" t="s">
+      <c r="C49" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="D49" s="189"/>
-      <c r="E49" s="190"/>
-      <c r="F49" s="191"/>
-      <c r="G49" s="192">
+      <c r="D49" s="74"/>
+      <c r="E49" s="75"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="50">
         <v>160</v>
       </c>
-      <c r="H49" s="190">
+      <c r="H49" s="75">
         <v>160</v>
       </c>
-      <c r="I49" s="193"/>
-      <c r="J49" s="192">
+      <c r="I49" s="49"/>
+      <c r="J49" s="50">
         <v>120</v>
       </c>
-      <c r="K49" s="190"/>
-      <c r="L49" s="191">
+      <c r="K49" s="75"/>
+      <c r="L49" s="76">
         <v>120</v>
       </c>
       <c r="M49" s="48">
@@ -6317,24 +6337,24 @@
       <c r="B50" s="47">
         <v>46</v>
       </c>
-      <c r="C50" s="188" t="s">
+      <c r="C50" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="D50" s="189"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="191"/>
-      <c r="G50" s="192">
+      <c r="D50" s="74"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="50">
         <v>120</v>
       </c>
-      <c r="H50" s="190">
+      <c r="H50" s="75">
         <v>120</v>
       </c>
-      <c r="I50" s="193"/>
-      <c r="J50" s="192">
+      <c r="I50" s="49"/>
+      <c r="J50" s="50">
         <v>120</v>
       </c>
-      <c r="K50" s="190"/>
-      <c r="L50" s="191">
+      <c r="K50" s="75"/>
+      <c r="L50" s="76">
         <v>120</v>
       </c>
       <c r="M50" s="48">
@@ -6379,24 +6399,24 @@
       <c r="B51" s="47">
         <v>47</v>
       </c>
-      <c r="C51" s="188" t="s">
+      <c r="C51" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D51" s="189"/>
-      <c r="E51" s="190"/>
-      <c r="F51" s="191"/>
-      <c r="G51" s="192">
+      <c r="D51" s="74"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="50">
         <v>40</v>
       </c>
-      <c r="H51" s="190">
+      <c r="H51" s="75">
         <v>40</v>
       </c>
-      <c r="I51" s="193"/>
-      <c r="J51" s="192">
+      <c r="I51" s="49"/>
+      <c r="J51" s="50">
         <v>40</v>
       </c>
-      <c r="K51" s="190"/>
-      <c r="L51" s="191">
+      <c r="K51" s="75"/>
+      <c r="L51" s="76">
         <v>40</v>
       </c>
       <c r="M51" s="48">
@@ -6441,24 +6461,24 @@
       <c r="B52" s="47">
         <v>48</v>
       </c>
-      <c r="C52" s="188" t="s">
+      <c r="C52" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="D52" s="189"/>
-      <c r="E52" s="190"/>
-      <c r="F52" s="191"/>
-      <c r="G52" s="192">
+      <c r="D52" s="74"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="76"/>
+      <c r="G52" s="50">
         <v>80</v>
       </c>
-      <c r="H52" s="190">
+      <c r="H52" s="75">
         <v>40</v>
       </c>
-      <c r="I52" s="193"/>
-      <c r="J52" s="192">
+      <c r="I52" s="49"/>
+      <c r="J52" s="50">
         <v>120</v>
       </c>
-      <c r="K52" s="190"/>
-      <c r="L52" s="191">
+      <c r="K52" s="75"/>
+      <c r="L52" s="76">
         <v>120</v>
       </c>
       <c r="M52" s="48">
@@ -6503,22 +6523,22 @@
       <c r="B53" s="47">
         <v>49</v>
       </c>
-      <c r="C53" s="188" t="s">
+      <c r="C53" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="D53" s="189"/>
-      <c r="E53" s="190"/>
-      <c r="F53" s="191"/>
-      <c r="G53" s="192"/>
-      <c r="H53" s="190">
+      <c r="D53" s="74"/>
+      <c r="E53" s="75"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="50"/>
+      <c r="H53" s="75">
         <v>40</v>
       </c>
-      <c r="I53" s="193"/>
-      <c r="J53" s="192">
+      <c r="I53" s="49"/>
+      <c r="J53" s="50">
         <v>80</v>
       </c>
-      <c r="K53" s="190"/>
-      <c r="L53" s="191">
+      <c r="K53" s="75"/>
+      <c r="L53" s="76">
         <v>80</v>
       </c>
       <c r="M53" s="48">
@@ -6563,24 +6583,24 @@
       <c r="B54" s="47">
         <v>50</v>
       </c>
-      <c r="C54" s="188" t="s">
+      <c r="C54" s="57" t="s">
         <v>185</v>
       </c>
-      <c r="D54" s="189"/>
-      <c r="E54" s="190"/>
-      <c r="F54" s="191"/>
-      <c r="G54" s="192">
+      <c r="D54" s="74"/>
+      <c r="E54" s="75"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="50">
         <v>80</v>
       </c>
-      <c r="H54" s="190">
+      <c r="H54" s="75">
         <v>80</v>
       </c>
-      <c r="I54" s="193"/>
-      <c r="J54" s="192">
+      <c r="I54" s="49"/>
+      <c r="J54" s="50">
         <v>80</v>
       </c>
-      <c r="K54" s="190"/>
-      <c r="L54" s="191">
+      <c r="K54" s="75"/>
+      <c r="L54" s="76">
         <v>80</v>
       </c>
       <c r="M54" s="48">
@@ -6625,24 +6645,24 @@
       <c r="B55" s="47">
         <v>51</v>
       </c>
-      <c r="C55" s="188" t="s">
+      <c r="C55" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="D55" s="189"/>
-      <c r="E55" s="190"/>
-      <c r="F55" s="191"/>
-      <c r="G55" s="192">
+      <c r="D55" s="74"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="76"/>
+      <c r="G55" s="50">
         <v>80</v>
       </c>
-      <c r="H55" s="190">
+      <c r="H55" s="75">
         <v>80</v>
       </c>
-      <c r="I55" s="193"/>
-      <c r="J55" s="192">
+      <c r="I55" s="49"/>
+      <c r="J55" s="50">
         <v>80</v>
       </c>
-      <c r="K55" s="190"/>
-      <c r="L55" s="191">
+      <c r="K55" s="75"/>
+      <c r="L55" s="76">
         <v>80</v>
       </c>
       <c r="M55" s="48">
@@ -6687,24 +6707,24 @@
       <c r="B56" s="47">
         <v>52</v>
       </c>
-      <c r="C56" s="188" t="s">
+      <c r="C56" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="D56" s="189"/>
-      <c r="E56" s="190"/>
-      <c r="F56" s="191"/>
-      <c r="G56" s="192">
+      <c r="D56" s="74"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="76"/>
+      <c r="G56" s="50">
         <v>200</v>
       </c>
-      <c r="H56" s="190">
+      <c r="H56" s="75">
         <v>200</v>
       </c>
-      <c r="I56" s="193"/>
-      <c r="J56" s="192">
+      <c r="I56" s="49"/>
+      <c r="J56" s="50">
         <v>200</v>
       </c>
-      <c r="K56" s="190"/>
-      <c r="L56" s="191">
+      <c r="K56" s="75"/>
+      <c r="L56" s="76">
         <v>200</v>
       </c>
       <c r="M56" s="48">
@@ -6749,24 +6769,24 @@
       <c r="B57" s="47">
         <v>53</v>
       </c>
-      <c r="C57" s="188" t="s">
+      <c r="C57" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="190"/>
-      <c r="E57" s="190"/>
-      <c r="F57" s="190"/>
-      <c r="G57" s="190">
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75">
         <v>40</v>
       </c>
-      <c r="H57" s="190">
+      <c r="H57" s="75">
         <v>40</v>
       </c>
-      <c r="I57" s="194"/>
-      <c r="J57" s="190">
+      <c r="I57" s="132"/>
+      <c r="J57" s="75">
         <v>40</v>
       </c>
-      <c r="K57" s="190"/>
-      <c r="L57" s="190">
+      <c r="K57" s="75"/>
+      <c r="L57" s="75">
         <v>40</v>
       </c>
       <c r="M57" s="135">
@@ -6823,7 +6843,7 @@
       <c r="H58" s="142">
         <v>1395</v>
       </c>
-      <c r="I58" s="195"/>
+      <c r="I58" s="154"/>
       <c r="J58" s="142">
         <v>2398</v>
       </c>
@@ -6887,7 +6907,7 @@
       <c r="H59" s="142">
         <v>40</v>
       </c>
-      <c r="I59" s="195"/>
+      <c r="I59" s="154"/>
       <c r="J59" s="142">
         <v>40</v>
       </c>
@@ -11814,10 +11834,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="178" t="s">
+      <c r="B132" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="179"/>
+      <c r="C132" s="174"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12081,10 +12101,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="166" t="s">
+      <c r="B136" s="186" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="167"/>
+      <c r="C136" s="187"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12175,10 +12195,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="155" t="s">
+      <c r="B137" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="156"/>
+      <c r="C137" s="176"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12270,17 +12290,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12315,24 +12335,24 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="182" t="s">
+      <c r="C3" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="186" t="s">
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="194" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="187"/>
-      <c r="K3" s="181" t="s">
+      <c r="I3" s="195"/>
+      <c r="K3" s="189" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="181"/>
-      <c r="M3" s="181"/>
-      <c r="N3" s="181"/>
-      <c r="O3" s="181"/>
+      <c r="L3" s="189"/>
+      <c r="M3" s="189"/>
+      <c r="N3" s="189"/>
+      <c r="O3" s="189"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12650,14 +12670,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="185" t="s">
+      <c r="C11" s="193" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="185"/>
-      <c r="F11" s="185" t="s">
+      <c r="D11" s="193"/>
+      <c r="F11" s="193" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="185"/>
+      <c r="G11" s="193"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12759,10 +12779,10 @@
         <f>G12*40</f>
         <v>223240</v>
       </c>
-      <c r="S13" s="180" t="s">
+      <c r="S13" s="188" t="s">
         <v>153</v>
       </c>
-      <c r="T13" s="180"/>
+      <c r="T13" s="188"/>
       <c r="U13" s="143">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12878,13 +12898,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="181" t="s">
+      <c r="D20" s="189" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="181"/>
-      <c r="F20" s="181"/>
-      <c r="G20" s="181"/>
-      <c r="H20" s="181"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="189"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="189"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -13194,7 +13214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -13221,7 +13241,7 @@
       <c r="D1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="152"/>
+      <c r="G1" s="151"/>
       <c r="H1" s="148" t="s">
         <v>37</v>
       </c>
@@ -13246,7 +13266,9 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="158">
+        <v>46029</v>
+      </c>
       <c r="I2" s="79" t="s">
         <v>98</v>
       </c>
@@ -13269,7 +13291,9 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="H3" s="158">
+        <v>46029</v>
+      </c>
       <c r="I3" s="79" t="s">
         <v>100</v>
       </c>
@@ -13292,7 +13316,9 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="H4" s="158">
+        <v>46029</v>
+      </c>
       <c r="I4" s="79" t="s">
         <v>101</v>
       </c>
@@ -13384,8 +13410,8 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="150"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
       <c r="H8" s="81"/>
       <c r="I8" s="79" t="s">
         <v>106</v>
@@ -13702,7 +13728,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H22" s="151">
+      <c r="H22" s="150">
         <v>46333</v>
       </c>
       <c r="I22" s="79" t="s">
@@ -13723,7 +13749,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H23" s="151">
+      <c r="H23" s="150">
         <v>46333</v>
       </c>
       <c r="I23" s="79" t="s">
@@ -13744,7 +13770,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H24" s="151">
+      <c r="H24" s="150">
         <v>46333</v>
       </c>
       <c r="I24" s="79" t="s">
@@ -13765,7 +13791,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H25" s="151">
+      <c r="H25" s="150">
         <v>46333</v>
       </c>
       <c r="I25" s="79" t="s">
@@ -13786,7 +13812,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H26" s="151">
+      <c r="H26" s="150">
         <v>46333</v>
       </c>
       <c r="I26" s="79" t="s">
@@ -13936,14 +13962,14 @@
       <c r="H33" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I33" s="146" t="s">
+      <c r="I33" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="J33" s="146">
+      <c r="J33" s="79">
         <v>305</v>
       </c>
-      <c r="K33" s="146" t="s">
-        <v>115</v>
+      <c r="K33" s="143" t="s">
+        <v>99</v>
       </c>
       <c r="L33" s="79"/>
       <c r="M33" s="79">
@@ -14107,7 +14133,7 @@
       <c r="J41" s="79">
         <v>4</v>
       </c>
-      <c r="K41" s="79" t="s">
+      <c r="K41" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L41" s="79" t="s">
@@ -14119,20 +14145,20 @@
       </c>
     </row>
     <row r="42" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H42" s="153" t="s">
+      <c r="H42" s="152" t="s">
         <v>174</v>
       </c>
-      <c r="I42" s="154" t="s">
+      <c r="I42" s="153" t="s">
         <v>170</v>
       </c>
-      <c r="J42" s="154">
+      <c r="J42" s="153">
         <v>8</v>
       </c>
-      <c r="K42" s="154" t="s">
+      <c r="K42" s="153" t="s">
         <v>142</v>
       </c>
-      <c r="L42" s="154"/>
-      <c r="M42" s="154">
+      <c r="L42" s="153"/>
+      <c r="M42" s="153">
         <f>J42*40</f>
         <v>320</v>
       </c>
@@ -14147,32 +14173,32 @@
       <c r="J43" s="79">
         <v>9</v>
       </c>
-      <c r="K43" s="79" t="s">
+      <c r="K43" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L43" s="79" t="s">
         <v>160</v>
       </c>
       <c r="M43" s="79">
-        <f t="shared" ref="M43:M53" si="1">J43*40</f>
+        <f t="shared" ref="M43:M59" si="1">J43*40</f>
         <v>360</v>
       </c>
     </row>
     <row r="44" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H44" s="153" t="s">
+      <c r="H44" s="152" t="s">
         <v>174</v>
       </c>
-      <c r="I44" s="154" t="s">
+      <c r="I44" s="153" t="s">
         <v>172</v>
       </c>
-      <c r="J44" s="154">
+      <c r="J44" s="153">
         <v>5</v>
       </c>
-      <c r="K44" s="154" t="s">
+      <c r="K44" s="153" t="s">
         <v>142</v>
       </c>
-      <c r="L44" s="154"/>
-      <c r="M44" s="154">
+      <c r="L44" s="153"/>
+      <c r="M44" s="153">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -14187,7 +14213,7 @@
       <c r="J45" s="79">
         <v>5</v>
       </c>
-      <c r="K45" s="79" t="s">
+      <c r="K45" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L45" s="79" t="s">
@@ -14208,7 +14234,7 @@
       <c r="J46" s="79">
         <v>8</v>
       </c>
-      <c r="K46" s="79" t="s">
+      <c r="K46" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L46" s="79" t="s">
@@ -14229,7 +14255,7 @@
       <c r="J47" s="79">
         <v>8</v>
       </c>
-      <c r="K47" s="79" t="s">
+      <c r="K47" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L47" s="79" t="s">
@@ -14250,7 +14276,7 @@
       <c r="J48" s="79">
         <v>20</v>
       </c>
-      <c r="K48" s="79" t="s">
+      <c r="K48" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L48" s="79" t="s">
@@ -14271,7 +14297,7 @@
       <c r="J49" s="79">
         <v>4</v>
       </c>
-      <c r="K49" s="79" t="s">
+      <c r="K49" s="143" t="s">
         <v>99</v>
       </c>
       <c r="L49" s="79" t="s">
@@ -14292,10 +14318,10 @@
       <c r="J50" s="130">
         <v>5</v>
       </c>
-      <c r="K50" s="130" t="s">
+      <c r="K50" s="162" t="s">
         <v>99</v>
       </c>
-      <c r="L50" s="196" t="s">
+      <c r="L50" s="130" t="s">
         <v>160</v>
       </c>
       <c r="M50" s="130">
@@ -14313,10 +14339,10 @@
       <c r="J51" s="130">
         <v>305</v>
       </c>
-      <c r="K51" s="130" t="s">
+      <c r="K51" s="162" t="s">
         <v>99</v>
       </c>
-      <c r="L51" s="196" t="s">
+      <c r="L51" s="130" t="s">
         <v>160</v>
       </c>
       <c r="M51" s="130">
@@ -14325,31 +14351,155 @@
       </c>
     </row>
     <row r="52" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H52" s="153" t="s">
+      <c r="H52" s="157" t="s">
         <v>183</v>
       </c>
-      <c r="I52" s="197" t="s">
+      <c r="I52" s="155" t="s">
         <v>181</v>
       </c>
-      <c r="J52" s="197">
+      <c r="J52" s="155">
         <v>300</v>
       </c>
-      <c r="K52" s="197" t="s">
+      <c r="K52" s="155" t="s">
         <v>142</v>
       </c>
-      <c r="L52" s="198"/>
-      <c r="M52" s="197">
+      <c r="L52" s="156"/>
+      <c r="M52" s="155">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
     <row r="53" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="I53" s="196"/>
-      <c r="J53" s="196"/>
-      <c r="K53" s="196"/>
-      <c r="M53" s="196">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="H53" s="159" t="s">
+        <v>189</v>
+      </c>
+      <c r="I53" s="160" t="s">
+        <v>190</v>
+      </c>
+      <c r="J53" s="160">
+        <v>5</v>
+      </c>
+      <c r="K53" s="160" t="s">
+        <v>195</v>
+      </c>
+      <c r="L53" s="161"/>
+      <c r="M53" s="160">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H54" s="159" t="s">
+        <v>189</v>
+      </c>
+      <c r="I54" s="161" t="s">
+        <v>191</v>
+      </c>
+      <c r="J54" s="161">
+        <v>8</v>
+      </c>
+      <c r="K54" s="160" t="s">
+        <v>195</v>
+      </c>
+      <c r="L54" s="161"/>
+      <c r="M54" s="161">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H55" s="158" t="s">
+        <v>189</v>
+      </c>
+      <c r="I55" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="J55" s="81">
+        <v>28</v>
+      </c>
+      <c r="K55" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="L55" s="81"/>
+      <c r="M55" s="81">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="56" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H56" s="158" t="s">
+        <v>189</v>
+      </c>
+      <c r="I56" s="81" t="s">
+        <v>192</v>
+      </c>
+      <c r="J56" s="81">
+        <v>44</v>
+      </c>
+      <c r="K56" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="L56" s="81"/>
+      <c r="M56" s="81">
+        <f t="shared" si="1"/>
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="57" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H57" s="158" t="s">
+        <v>189</v>
+      </c>
+      <c r="I57" s="81" t="s">
+        <v>193</v>
+      </c>
+      <c r="J57" s="81">
+        <v>30</v>
+      </c>
+      <c r="K57" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="L57" s="81"/>
+      <c r="M57" s="81">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="58" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H58" s="158" t="s">
+        <v>189</v>
+      </c>
+      <c r="I58" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="J58" s="81">
+        <v>25</v>
+      </c>
+      <c r="K58" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="L58" s="81"/>
+      <c r="M58" s="81">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="59" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H59" s="158" t="s">
+        <v>189</v>
+      </c>
+      <c r="I59" s="81" t="s">
+        <v>135</v>
+      </c>
+      <c r="J59" s="81">
+        <v>11</v>
+      </c>
+      <c r="K59" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="L59" s="81"/>
+      <c r="M59" s="81">
+        <f t="shared" si="1"/>
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBF0201-7F17-4EE2-94AF-ABD1862027D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E5A29A-6A1C-4B03-81AC-FB75C985F845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="204">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -340,9 +340,6 @@
     <t>Umaima Paragon</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
     <t>Raheem Store</t>
   </si>
   <si>
@@ -613,7 +610,34 @@
     <t>Euro D-2</t>
   </si>
   <si>
-    <t>Not Deliver</t>
+    <t xml:space="preserve">MTD Sale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow C &amp; C Barki Road </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Badami Bagh </t>
+  </si>
+  <si>
+    <t>Gourmet Food Kareem Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA Mart </t>
+  </si>
+  <si>
+    <t>Naqshbandi Indocaion free</t>
+  </si>
+  <si>
+    <t>Naqshbandi Multan Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem Store Iqbal Town </t>
+  </si>
+  <si>
+    <t>Risen Sabzazar</t>
+  </si>
+  <si>
+    <t>23/07/26</t>
   </si>
 </sst>
 </file>
@@ -725,7 +749,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,12 +822,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="58">
     <border>
@@ -1527,7 +1545,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1885,10 +1903,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1920,25 +1934,18 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2037,6 +2044,30 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2573,14 +2604,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="163">
+      <c r="B1" s="158">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
-      </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
+        <v>46227</v>
+      </c>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2602,10 +2633,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="180" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="159" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2638,13 +2669,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="177"/>
-      <c r="N2" s="178"/>
-      <c r="O2" s="179"/>
-      <c r="P2" s="180" t="s">
+      <c r="M2" s="172"/>
+      <c r="N2" s="173"/>
+      <c r="O2" s="174"/>
+      <c r="P2" s="175" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="181"/>
+      <c r="Q2" s="176"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2663,8 +2694,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="185"/>
-      <c r="B3" s="165"/>
+      <c r="A3" s="180"/>
+      <c r="B3" s="160"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2695,29 +2726,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="182" t="s">
+      <c r="M3" s="177" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="183"/>
-      <c r="O3" s="184"/>
+      <c r="N3" s="178"/>
+      <c r="O3" s="179"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="167" t="s">
+      <c r="R3" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="168"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169"/>
-      <c r="V3" s="170" t="s">
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="164"/>
+      <c r="V3" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="171"/>
-      <c r="X3" s="171"/>
-      <c r="Y3" s="172"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="166"/>
+      <c r="Y3" s="167"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="185"/>
-      <c r="B4" s="166"/>
+      <c r="A4" s="180"/>
+      <c r="B4" s="161"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3862,7 +3893,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" s="74"/>
       <c r="E18" s="75"/>
@@ -3944,7 +3975,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" s="74"/>
       <c r="E19" s="75"/>
@@ -4100,7 +4131,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" s="74"/>
       <c r="E21" s="75"/>
@@ -4180,7 +4211,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" s="74"/>
       <c r="E22" s="75"/>
@@ -4260,7 +4291,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
@@ -4338,7 +4369,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
@@ -4420,7 +4451,7 @@
         <v>21</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D25" s="74"/>
       <c r="E25" s="75"/>
@@ -4580,7 +4611,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D27" s="74"/>
       <c r="E27" s="75"/>
@@ -4658,7 +4689,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" s="74"/>
       <c r="E28" s="75"/>
@@ -4822,7 +4853,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D30" s="74"/>
       <c r="E30" s="75"/>
@@ -4900,7 +4931,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D31" s="74">
         <v>200</v>
@@ -4984,7 +5015,7 @@
         <v>28</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D32" s="74"/>
       <c r="E32" s="75"/>
@@ -5062,7 +5093,7 @@
         <v>29</v>
       </c>
       <c r="C33" s="57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D33" s="74"/>
       <c r="E33" s="75"/>
@@ -5222,7 +5253,7 @@
         <v>31</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D35" s="74"/>
       <c r="E35" s="75"/>
@@ -5300,7 +5331,7 @@
         <v>32</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D36" s="74"/>
       <c r="E36" s="75"/>
@@ -5382,7 +5413,7 @@
         <v>33</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D37" s="74"/>
       <c r="E37" s="75"/>
@@ -5460,7 +5491,7 @@
         <v>34</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D38" s="74">
         <v>2000</v>
@@ -5534,7 +5565,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D39" s="74"/>
       <c r="E39" s="75"/>
@@ -5616,7 +5647,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="74"/>
       <c r="E40" s="75"/>
@@ -5690,7 +5721,7 @@
         <v>37</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D41" s="74">
         <v>160</v>
@@ -5774,7 +5805,7 @@
         <v>38</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D42" s="74">
         <v>80</v>
@@ -5854,7 +5885,7 @@
         <v>39</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D43" s="74"/>
       <c r="E43" s="75"/>
@@ -5932,7 +5963,7 @@
         <v>40</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D44" s="74"/>
       <c r="E44" s="75"/>
@@ -6010,7 +6041,7 @@
         <v>41</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D45" s="74"/>
       <c r="E45" s="75"/>
@@ -6152,7 +6183,7 @@
         <v>43</v>
       </c>
       <c r="C47" s="57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D47" s="74"/>
       <c r="E47" s="75"/>
@@ -6214,7 +6245,7 @@
         <v>44</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D48" s="74"/>
       <c r="E48" s="75"/>
@@ -6276,7 +6307,7 @@
         <v>45</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D49" s="74"/>
       <c r="E49" s="75"/>
@@ -6338,7 +6369,7 @@
         <v>46</v>
       </c>
       <c r="C50" s="57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D50" s="74"/>
       <c r="E50" s="75"/>
@@ -6400,7 +6431,7 @@
         <v>47</v>
       </c>
       <c r="C51" s="57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D51" s="74"/>
       <c r="E51" s="75"/>
@@ -6462,7 +6493,7 @@
         <v>48</v>
       </c>
       <c r="C52" s="57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D52" s="74"/>
       <c r="E52" s="75"/>
@@ -6524,7 +6555,7 @@
         <v>49</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D53" s="74"/>
       <c r="E53" s="75"/>
@@ -6584,7 +6615,7 @@
         <v>50</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D54" s="74"/>
       <c r="E54" s="75"/>
@@ -6646,7 +6677,7 @@
         <v>51</v>
       </c>
       <c r="C55" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D55" s="74"/>
       <c r="E55" s="75"/>
@@ -6708,7 +6739,7 @@
         <v>52</v>
       </c>
       <c r="C56" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D56" s="74"/>
       <c r="E56" s="75"/>
@@ -6770,7 +6801,7 @@
         <v>53</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D57" s="75"/>
       <c r="E57" s="75"/>
@@ -6831,26 +6862,26 @@
       <c r="B58" s="47">
         <v>54</v>
       </c>
-      <c r="C58" s="141" t="s">
-        <v>188</v>
-      </c>
-      <c r="D58" s="142"/>
-      <c r="E58" s="142"/>
-      <c r="F58" s="142"/>
-      <c r="G58" s="142">
+      <c r="C58" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="75">
         <v>1189</v>
       </c>
-      <c r="H58" s="142">
+      <c r="H58" s="75">
         <v>1395</v>
       </c>
-      <c r="I58" s="154"/>
-      <c r="J58" s="142">
+      <c r="I58" s="132"/>
+      <c r="J58" s="75">
         <v>2398</v>
       </c>
-      <c r="K58" s="142">
+      <c r="K58" s="75">
         <v>2397</v>
       </c>
-      <c r="L58" s="142">
+      <c r="L58" s="75">
         <v>4800</v>
       </c>
       <c r="M58" s="135">
@@ -6895,26 +6926,26 @@
       <c r="B59" s="47">
         <v>55</v>
       </c>
-      <c r="C59" s="141" t="s">
-        <v>128</v>
-      </c>
-      <c r="D59" s="142"/>
-      <c r="E59" s="142"/>
-      <c r="F59" s="142"/>
-      <c r="G59" s="142">
+      <c r="C59" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="75">
         <v>40</v>
       </c>
-      <c r="H59" s="142">
+      <c r="H59" s="75">
         <v>40</v>
       </c>
-      <c r="I59" s="154"/>
-      <c r="J59" s="142">
+      <c r="I59" s="132"/>
+      <c r="J59" s="75">
         <v>40</v>
       </c>
-      <c r="K59" s="142">
+      <c r="K59" s="75">
         <v>40</v>
       </c>
-      <c r="L59" s="142">
+      <c r="L59" s="75">
         <v>40</v>
       </c>
       <c r="M59" s="135">
@@ -6953,23 +6984,37 @@
       <c r="Y59" s="56"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A60" s="78"/>
+      <c r="A60" s="78">
+        <v>21</v>
+      </c>
       <c r="B60" s="47">
         <v>56</v>
       </c>
-      <c r="C60" s="57"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="75"/>
-      <c r="F60" s="75"/>
-      <c r="G60" s="75"/>
-      <c r="H60" s="75"/>
-      <c r="I60" s="132"/>
-      <c r="J60" s="75"/>
-      <c r="K60" s="75"/>
-      <c r="L60" s="75"/>
+      <c r="C60" s="197" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" s="198"/>
+      <c r="E60" s="198"/>
+      <c r="F60" s="198"/>
+      <c r="G60" s="198">
+        <v>40</v>
+      </c>
+      <c r="H60" s="198">
+        <v>400</v>
+      </c>
+      <c r="I60" s="199"/>
+      <c r="J60" s="198">
+        <v>160</v>
+      </c>
+      <c r="K60" s="198">
+        <v>320</v>
+      </c>
+      <c r="L60" s="198">
+        <v>200</v>
+      </c>
       <c r="M60" s="135">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N60" s="39">
         <f t="shared" si="18"/>
@@ -6981,11 +7026,11 @@
       </c>
       <c r="P60" s="73">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q60" s="40">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R60" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7021,23 +7066,37 @@
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A61" s="78"/>
+      <c r="A61" s="78">
+        <v>21</v>
+      </c>
       <c r="B61" s="47">
         <v>57</v>
       </c>
-      <c r="C61" s="133"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
-      <c r="F61" s="75"/>
-      <c r="G61" s="75"/>
-      <c r="H61" s="75"/>
-      <c r="I61" s="132"/>
-      <c r="J61" s="75"/>
-      <c r="K61" s="75"/>
-      <c r="L61" s="75"/>
+      <c r="C61" s="200" t="s">
+        <v>191</v>
+      </c>
+      <c r="D61" s="198"/>
+      <c r="E61" s="198"/>
+      <c r="F61" s="198"/>
+      <c r="G61" s="198">
+        <v>200</v>
+      </c>
+      <c r="H61" s="198">
+        <v>320</v>
+      </c>
+      <c r="I61" s="199"/>
+      <c r="J61" s="198">
+        <v>320</v>
+      </c>
+      <c r="K61" s="198">
+        <v>400</v>
+      </c>
+      <c r="L61" s="198">
+        <v>520</v>
+      </c>
       <c r="M61" s="135">
         <f t="shared" ref="M61:M83" si="81">SUM(D61:L61)/40</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N61" s="39">
         <f t="shared" si="18"/>
@@ -7049,11 +7108,11 @@
       </c>
       <c r="P61" s="73">
         <f t="shared" ref="P61:P78" si="82">SUM(G61:I61)/20</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q61" s="40">
         <f t="shared" ref="Q61:Q78" si="83">SUM(J61:L61)/20</f>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R61" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7089,23 +7148,37 @@
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A62" s="78"/>
+      <c r="A62" s="78">
+        <v>21</v>
+      </c>
       <c r="B62" s="47">
         <v>58</v>
       </c>
-      <c r="C62" s="133"/>
-      <c r="D62" s="75"/>
-      <c r="E62" s="75"/>
-      <c r="F62" s="75"/>
-      <c r="G62" s="75"/>
-      <c r="H62" s="75"/>
-      <c r="I62" s="132"/>
-      <c r="J62" s="75"/>
-      <c r="K62" s="75"/>
-      <c r="L62" s="75"/>
+      <c r="C62" s="200" t="s">
+        <v>192</v>
+      </c>
+      <c r="D62" s="198"/>
+      <c r="E62" s="198"/>
+      <c r="F62" s="198"/>
+      <c r="G62" s="198">
+        <v>240</v>
+      </c>
+      <c r="H62" s="198">
+        <v>240</v>
+      </c>
+      <c r="I62" s="199"/>
+      <c r="J62" s="198">
+        <v>240</v>
+      </c>
+      <c r="K62" s="198">
+        <v>240</v>
+      </c>
+      <c r="L62" s="198">
+        <v>240</v>
+      </c>
       <c r="M62" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N62" s="39">
         <f t="shared" si="18"/>
@@ -7117,11 +7190,11 @@
       </c>
       <c r="P62" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q62" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R62" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7157,23 +7230,37 @@
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A63" s="78"/>
+      <c r="A63" s="78">
+        <v>21</v>
+      </c>
       <c r="B63" s="47">
         <v>59</v>
       </c>
-      <c r="C63" s="133"/>
-      <c r="D63" s="75"/>
-      <c r="E63" s="75"/>
-      <c r="F63" s="75"/>
-      <c r="G63" s="75"/>
-      <c r="H63" s="75"/>
-      <c r="I63" s="132"/>
-      <c r="J63" s="75"/>
-      <c r="K63" s="75"/>
-      <c r="L63" s="75"/>
+      <c r="C63" s="200" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" s="198"/>
+      <c r="E63" s="198"/>
+      <c r="F63" s="198"/>
+      <c r="G63" s="198">
+        <v>200</v>
+      </c>
+      <c r="H63" s="198">
+        <v>200</v>
+      </c>
+      <c r="I63" s="199"/>
+      <c r="J63" s="198">
+        <v>200</v>
+      </c>
+      <c r="K63" s="198">
+        <v>200</v>
+      </c>
+      <c r="L63" s="198">
+        <v>200</v>
+      </c>
       <c r="M63" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N63" s="39">
         <f t="shared" si="18"/>
@@ -7185,11 +7272,11 @@
       </c>
       <c r="P63" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q63" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R63" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7225,23 +7312,37 @@
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A64" s="78"/>
+      <c r="A64" s="78">
+        <v>21</v>
+      </c>
       <c r="B64" s="47">
         <v>60</v>
       </c>
-      <c r="C64" s="133"/>
-      <c r="D64" s="75"/>
-      <c r="E64" s="75"/>
-      <c r="F64" s="75"/>
-      <c r="G64" s="75"/>
-      <c r="H64" s="75"/>
-      <c r="I64" s="132"/>
-      <c r="J64" s="75"/>
-      <c r="K64" s="75"/>
-      <c r="L64" s="75"/>
+      <c r="C64" s="200" t="s">
+        <v>134</v>
+      </c>
+      <c r="D64" s="198"/>
+      <c r="E64" s="198"/>
+      <c r="F64" s="198"/>
+      <c r="G64" s="198">
+        <v>80</v>
+      </c>
+      <c r="H64" s="198">
+        <v>80</v>
+      </c>
+      <c r="I64" s="199"/>
+      <c r="J64" s="198">
+        <v>80</v>
+      </c>
+      <c r="K64" s="198">
+        <v>80</v>
+      </c>
+      <c r="L64" s="198">
+        <v>120</v>
+      </c>
       <c r="M64" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N64" s="39">
         <f t="shared" si="18"/>
@@ -7253,11 +7354,11 @@
       </c>
       <c r="P64" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q64" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R64" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7293,23 +7394,39 @@
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A65" s="78"/>
+      <c r="A65" s="78">
+        <v>21</v>
+      </c>
       <c r="B65" s="47">
         <v>61</v>
       </c>
-      <c r="C65" s="133"/>
-      <c r="D65" s="75"/>
-      <c r="E65" s="75"/>
-      <c r="F65" s="75"/>
-      <c r="G65" s="75"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="132"/>
-      <c r="J65" s="75"/>
-      <c r="K65" s="75"/>
-      <c r="L65" s="75"/>
+      <c r="C65" s="200" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="198">
+        <v>4000</v>
+      </c>
+      <c r="E65" s="198"/>
+      <c r="F65" s="198"/>
+      <c r="G65" s="198">
+        <v>600</v>
+      </c>
+      <c r="H65" s="198">
+        <v>800</v>
+      </c>
+      <c r="I65" s="199"/>
+      <c r="J65" s="198">
+        <v>2800</v>
+      </c>
+      <c r="K65" s="198">
+        <v>1200</v>
+      </c>
+      <c r="L65" s="198">
+        <v>2600</v>
+      </c>
       <c r="M65" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N65" s="39">
         <f t="shared" si="18"/>
@@ -7321,11 +7438,11 @@
       </c>
       <c r="P65" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q65" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="R65" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7361,23 +7478,37 @@
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A66" s="78"/>
+      <c r="A66" s="78">
+        <v>23</v>
+      </c>
       <c r="B66" s="47">
         <v>62</v>
       </c>
-      <c r="C66" s="133"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="75"/>
-      <c r="F66" s="75"/>
-      <c r="G66" s="75"/>
-      <c r="H66" s="75"/>
-      <c r="I66" s="132"/>
-      <c r="J66" s="75"/>
-      <c r="K66" s="75"/>
-      <c r="L66" s="75"/>
+      <c r="C66" s="192" t="s">
+        <v>190</v>
+      </c>
+      <c r="D66" s="193"/>
+      <c r="E66" s="193"/>
+      <c r="F66" s="193"/>
+      <c r="G66" s="193">
+        <v>40</v>
+      </c>
+      <c r="H66" s="193">
+        <v>40</v>
+      </c>
+      <c r="I66" s="194"/>
+      <c r="J66" s="193">
+        <v>40</v>
+      </c>
+      <c r="K66" s="193">
+        <v>80</v>
+      </c>
+      <c r="L66" s="193">
+        <v>80</v>
+      </c>
       <c r="M66" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N66" s="39">
         <f t="shared" si="18"/>
@@ -7389,11 +7520,11 @@
       </c>
       <c r="P66" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q66" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R66" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7429,23 +7560,29 @@
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A67" s="78"/>
+      <c r="A67" s="78">
+        <v>23</v>
+      </c>
       <c r="B67" s="47">
         <v>63</v>
       </c>
-      <c r="C67" s="133"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="75"/>
-      <c r="F67" s="75"/>
-      <c r="G67" s="75"/>
-      <c r="H67" s="75"/>
-      <c r="I67" s="132"/>
-      <c r="J67" s="75"/>
-      <c r="K67" s="75"/>
-      <c r="L67" s="75"/>
+      <c r="C67" s="192" t="s">
+        <v>195</v>
+      </c>
+      <c r="D67" s="193"/>
+      <c r="E67" s="193"/>
+      <c r="F67" s="193"/>
+      <c r="G67" s="193"/>
+      <c r="H67" s="193"/>
+      <c r="I67" s="194"/>
+      <c r="J67" s="193"/>
+      <c r="K67" s="193"/>
+      <c r="L67" s="193">
+        <v>200</v>
+      </c>
       <c r="M67" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N67" s="39">
         <f t="shared" si="18"/>
@@ -7461,7 +7598,7 @@
       </c>
       <c r="Q67" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R67" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7497,23 +7634,37 @@
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A68" s="78"/>
+      <c r="A68" s="78">
+        <v>23</v>
+      </c>
       <c r="B68" s="47">
         <v>64</v>
       </c>
-      <c r="C68" s="133"/>
-      <c r="D68" s="75"/>
-      <c r="E68" s="75"/>
-      <c r="F68" s="75"/>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
-      <c r="I68" s="132"/>
-      <c r="J68" s="75"/>
-      <c r="K68" s="75"/>
-      <c r="L68" s="75"/>
+      <c r="C68" s="192" t="s">
+        <v>196</v>
+      </c>
+      <c r="D68" s="193"/>
+      <c r="E68" s="193"/>
+      <c r="F68" s="193"/>
+      <c r="G68" s="193">
+        <v>10</v>
+      </c>
+      <c r="H68" s="193">
+        <v>10</v>
+      </c>
+      <c r="I68" s="194"/>
+      <c r="J68" s="193">
+        <v>10</v>
+      </c>
+      <c r="K68" s="193">
+        <v>10</v>
+      </c>
+      <c r="L68" s="193">
+        <v>20</v>
+      </c>
       <c r="M68" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N68" s="39">
         <f t="shared" si="18"/>
@@ -7525,11 +7676,11 @@
       </c>
       <c r="P68" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R68" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7565,23 +7716,37 @@
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A69" s="78"/>
+      <c r="A69" s="78">
+        <v>23</v>
+      </c>
       <c r="B69" s="47">
         <v>65</v>
       </c>
-      <c r="C69" s="133"/>
-      <c r="D69" s="75"/>
-      <c r="E69" s="75"/>
-      <c r="F69" s="75"/>
-      <c r="G69" s="75"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="132"/>
-      <c r="J69" s="75"/>
-      <c r="K69" s="75"/>
-      <c r="L69" s="75"/>
+      <c r="C69" s="192" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" s="193"/>
+      <c r="E69" s="193"/>
+      <c r="F69" s="193"/>
+      <c r="G69" s="193">
+        <v>10</v>
+      </c>
+      <c r="H69" s="193">
+        <v>10</v>
+      </c>
+      <c r="I69" s="194"/>
+      <c r="J69" s="193">
+        <v>20</v>
+      </c>
+      <c r="K69" s="193">
+        <v>20</v>
+      </c>
+      <c r="L69" s="193">
+        <v>20</v>
+      </c>
       <c r="M69" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N69" s="39">
         <f t="shared" si="18"/>
@@ -7593,11 +7758,11 @@
       </c>
       <c r="P69" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R69" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7633,23 +7798,35 @@
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A70" s="78"/>
+      <c r="A70" s="78">
+        <v>23</v>
+      </c>
       <c r="B70" s="47">
         <v>66</v>
       </c>
-      <c r="C70" s="133"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75"/>
-      <c r="F70" s="75"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="132"/>
-      <c r="J70" s="75"/>
-      <c r="K70" s="75"/>
-      <c r="L70" s="75"/>
+      <c r="C70" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="D70" s="193"/>
+      <c r="E70" s="193"/>
+      <c r="F70" s="193"/>
+      <c r="G70" s="193">
+        <v>40</v>
+      </c>
+      <c r="H70" s="193"/>
+      <c r="I70" s="194"/>
+      <c r="J70" s="193">
+        <v>40</v>
+      </c>
+      <c r="K70" s="193">
+        <v>80</v>
+      </c>
+      <c r="L70" s="193">
+        <v>80</v>
+      </c>
       <c r="M70" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N70" s="39">
         <f t="shared" si="18"/>
@@ -7661,11 +7838,11 @@
       </c>
       <c r="P70" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R70" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7701,23 +7878,35 @@
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A71" s="78"/>
+      <c r="A71" s="78">
+        <v>23</v>
+      </c>
       <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="133"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="75"/>
-      <c r="F71" s="75"/>
-      <c r="G71" s="75"/>
-      <c r="H71" s="75"/>
-      <c r="I71" s="132"/>
-      <c r="J71" s="75"/>
-      <c r="K71" s="75"/>
-      <c r="L71" s="75"/>
+      <c r="C71" s="192" t="s">
+        <v>199</v>
+      </c>
+      <c r="D71" s="193"/>
+      <c r="E71" s="193"/>
+      <c r="F71" s="193"/>
+      <c r="G71" s="193">
+        <v>40</v>
+      </c>
+      <c r="H71" s="193">
+        <v>40</v>
+      </c>
+      <c r="I71" s="194"/>
+      <c r="J71" s="193"/>
+      <c r="K71" s="193">
+        <v>40</v>
+      </c>
+      <c r="L71" s="193">
+        <v>40</v>
+      </c>
       <c r="M71" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N71" s="39">
         <f t="shared" si="18"/>
@@ -7729,11 +7918,11 @@
       </c>
       <c r="P71" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q71" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R71" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7769,23 +7958,37 @@
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A72" s="78"/>
+      <c r="A72" s="78">
+        <v>23</v>
+      </c>
       <c r="B72" s="47">
         <v>68</v>
       </c>
-      <c r="C72" s="133"/>
-      <c r="D72" s="75"/>
-      <c r="E72" s="75"/>
-      <c r="F72" s="75"/>
-      <c r="G72" s="75"/>
-      <c r="H72" s="75"/>
-      <c r="I72" s="132"/>
-      <c r="J72" s="75"/>
-      <c r="K72" s="75"/>
-      <c r="L72" s="75"/>
+      <c r="C72" s="192" t="s">
+        <v>200</v>
+      </c>
+      <c r="D72" s="193"/>
+      <c r="E72" s="193"/>
+      <c r="F72" s="193"/>
+      <c r="G72" s="193">
+        <v>80</v>
+      </c>
+      <c r="H72" s="193">
+        <v>80</v>
+      </c>
+      <c r="I72" s="194"/>
+      <c r="J72" s="193">
+        <v>80</v>
+      </c>
+      <c r="K72" s="193">
+        <v>80</v>
+      </c>
+      <c r="L72" s="193">
+        <v>80</v>
+      </c>
       <c r="M72" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N72" s="39">
         <f t="shared" si="18"/>
@@ -7797,11 +8000,11 @@
       </c>
       <c r="P72" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q72" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R72" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7837,23 +8040,33 @@
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A73" s="78"/>
+      <c r="A73" s="78">
+        <v>23</v>
+      </c>
       <c r="B73" s="47">
         <v>69</v>
       </c>
-      <c r="C73" s="133"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="75"/>
-      <c r="F73" s="75"/>
-      <c r="G73" s="75"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="132"/>
-      <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
-      <c r="L73" s="75"/>
+      <c r="C73" s="192" t="s">
+        <v>201</v>
+      </c>
+      <c r="D73" s="193"/>
+      <c r="E73" s="193"/>
+      <c r="F73" s="193"/>
+      <c r="G73" s="193">
+        <v>200</v>
+      </c>
+      <c r="H73" s="193">
+        <v>120</v>
+      </c>
+      <c r="I73" s="194"/>
+      <c r="J73" s="193"/>
+      <c r="K73" s="193"/>
+      <c r="L73" s="193">
+        <v>400</v>
+      </c>
       <c r="M73" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N73" s="39">
         <f t="shared" si="18"/>
@@ -7865,11 +8078,11 @@
       </c>
       <c r="P73" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q73" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R73" s="51" t="e">
         <f t="shared" si="4"/>
@@ -7905,23 +8118,37 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A74" s="78"/>
+      <c r="A74" s="78">
+        <v>23</v>
+      </c>
       <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="134"/>
-      <c r="D74" s="75"/>
-      <c r="E74" s="75"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="75"/>
-      <c r="H74" s="75"/>
-      <c r="I74" s="132"/>
-      <c r="J74" s="75"/>
-      <c r="K74" s="75"/>
-      <c r="L74" s="75"/>
+      <c r="C74" s="195" t="s">
+        <v>202</v>
+      </c>
+      <c r="D74" s="193"/>
+      <c r="E74" s="193"/>
+      <c r="F74" s="196"/>
+      <c r="G74" s="193">
+        <v>40</v>
+      </c>
+      <c r="H74" s="193">
+        <v>80</v>
+      </c>
+      <c r="I74" s="194"/>
+      <c r="J74" s="193">
+        <v>80</v>
+      </c>
+      <c r="K74" s="193">
+        <v>80</v>
+      </c>
+      <c r="L74" s="193">
+        <v>80</v>
+      </c>
       <c r="M74" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N74" s="39">
         <f t="shared" si="18"/>
@@ -7933,11 +8160,11 @@
       </c>
       <c r="P74" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q74" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R74" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11834,10 +12061,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="173" t="s">
+      <c r="B132" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="174"/>
+      <c r="C132" s="169"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -11852,11 +12079,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>4407</v>
+        <v>4447</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>4712</v>
+        <v>5112</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11864,19 +12091,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>7257</v>
+        <v>7417</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>5875</v>
+        <v>6195</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>10558</v>
+        <v>10758</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>881.22500000000002</v>
+        <v>909.22500000000002</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11888,11 +12115,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>455.95</v>
+        <v>477.95</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>1184.5</v>
+        <v>1218.5</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12101,10 +12328,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="186" t="s">
+      <c r="B136" s="181" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="187"/>
+      <c r="C136" s="182"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12195,10 +12422,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="175" t="s">
+      <c r="B137" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="176"/>
+      <c r="C137" s="171"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12213,11 +12440,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>4407</v>
+        <v>4447</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>4712</v>
+        <v>5112</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -12225,19 +12452,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>7257</v>
+        <v>7417</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>5875</v>
+        <v>6195</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>10558</v>
+        <v>10758</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>881.22500000000002</v>
+        <v>909.22500000000002</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -12249,11 +12476,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>915.9</v>
+        <v>1149.9000000000001</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>2375</v>
+        <v>2998</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12318,7 +12545,7 @@
     <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="4.08984375" customWidth="1"/>
     <col min="3" max="3" width="10.7265625" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="39.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.36328125" customWidth="1"/>
     <col min="7" max="7" width="11.26953125" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
@@ -12327,6 +12554,7 @@
     <col min="12" max="12" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6328125" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -12335,24 +12563,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="190" t="s">
+      <c r="C3" s="185" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="194" t="s">
+      <c r="D3" s="186"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="195"/>
-      <c r="K3" s="189" t="s">
+      <c r="I3" s="190"/>
+      <c r="K3" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="189"/>
-      <c r="M3" s="189"/>
-      <c r="N3" s="189"/>
-      <c r="O3" s="189"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
+      <c r="O3" s="191"/>
+      <c r="P3" s="191"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12389,28 +12618,33 @@
       <c r="O4" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="P4" s="157" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="5" spans="3:26" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C5" s="105" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="E5" s="79">
-        <v>1103</v>
+        <v>1241</v>
       </c>
       <c r="F5" s="79">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>2147</v>
-      </c>
-      <c r="H5" s="99"/>
+        <v>2613</v>
+      </c>
+      <c r="H5" s="99">
+        <v>10000</v>
+      </c>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>2147</v>
+        <v>-7387</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12435,27 +12669,27 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>29760</v>
+        <v>30880</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>44120</v>
+        <v>49640</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>85880</v>
+        <v>104520</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>85880</v>
+        <v>-295480</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12475,19 +12709,19 @@
       </c>
       <c r="S6" s="129"/>
       <c r="T6" s="129"/>
-      <c r="U6" s="145">
+      <c r="U6" s="143">
         <v>46180</v>
       </c>
-      <c r="V6" s="145">
+      <c r="V6" s="143">
         <v>46180</v>
       </c>
-      <c r="W6" s="145">
+      <c r="W6" s="143">
         <v>46333</v>
       </c>
-      <c r="X6" s="145">
+      <c r="X6" s="143">
         <v>46210</v>
       </c>
-      <c r="Y6" s="145">
+      <c r="Y6" s="143">
         <v>46210</v>
       </c>
     </row>
@@ -12507,29 +12741,29 @@
       <c r="O7" s="81">
         <v>35</v>
       </c>
-      <c r="S7" s="144" t="s">
-        <v>155</v>
-      </c>
-      <c r="T7" s="144" t="s">
+      <c r="S7" s="142" t="s">
         <v>154</v>
       </c>
+      <c r="T7" s="142" t="s">
+        <v>153</v>
+      </c>
       <c r="U7" s="77" t="s">
-        <v>148</v>
-      </c>
-      <c r="V7" s="144" t="s">
+        <v>147</v>
+      </c>
+      <c r="V7" s="142" t="s">
+        <v>151</v>
+      </c>
+      <c r="W7" s="142" t="s">
+        <v>150</v>
+      </c>
+      <c r="X7" s="142" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y7" s="142" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z7" s="142" t="s">
         <v>152</v>
-      </c>
-      <c r="W7" s="144" t="s">
-        <v>151</v>
-      </c>
-      <c r="X7" s="144" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y7" s="144" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z7" s="144" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="8" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12556,9 +12790,9 @@
         <v>120</v>
       </c>
       <c r="T8" s="79" t="s">
-        <v>147</v>
-      </c>
-      <c r="U8" s="143">
+        <v>146</v>
+      </c>
+      <c r="U8" s="141">
         <v>50</v>
       </c>
       <c r="V8" s="79">
@@ -12582,11 +12816,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-744</v>
+        <v>-772</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-1103</v>
+        <v>-1241</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12610,7 +12844,7 @@
       <c r="T9" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="143">
+      <c r="U9" s="141">
         <v>50</v>
       </c>
       <c r="V9" s="79">
@@ -12651,9 +12885,9 @@
         <v>120</v>
       </c>
       <c r="T10" s="79" t="s">
-        <v>149</v>
-      </c>
-      <c r="U10" s="143"/>
+        <v>148</v>
+      </c>
+      <c r="U10" s="141"/>
       <c r="V10" s="79">
         <v>3</v>
       </c>
@@ -12670,14 +12904,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="193" t="s">
+      <c r="C11" s="188" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="193"/>
-      <c r="F11" s="193" t="s">
+      <c r="D11" s="188"/>
+      <c r="F11" s="188" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="193"/>
+      <c r="G11" s="188"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12698,9 +12932,9 @@
         <v>70</v>
       </c>
       <c r="T11" s="79" t="s">
-        <v>147</v>
-      </c>
-      <c r="U11" s="143"/>
+        <v>146</v>
+      </c>
+      <c r="U11" s="141"/>
       <c r="V11" s="79"/>
       <c r="W11" s="79"/>
       <c r="X11" s="79">
@@ -12726,7 +12960,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>5581</v>
+        <v>6047</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -12748,9 +12982,9 @@
         <v>70</v>
       </c>
       <c r="T12" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="U12" s="143"/>
+        <v>149</v>
+      </c>
+      <c r="U12" s="141"/>
       <c r="V12" s="79"/>
       <c r="W12" s="79"/>
       <c r="X12" s="79">
@@ -12777,13 +13011,13 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>223240</v>
-      </c>
-      <c r="S13" s="188" t="s">
-        <v>153</v>
-      </c>
-      <c r="T13" s="188"/>
-      <c r="U13" s="143">
+        <v>241880</v>
+      </c>
+      <c r="S13" s="183" t="s">
+        <v>152</v>
+      </c>
+      <c r="T13" s="183"/>
+      <c r="U13" s="141">
         <f>SUM(U8:U12)</f>
         <v>100</v>
       </c>
@@ -12873,7 +13107,7 @@
     </row>
     <row r="19" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>3</v>
@@ -12898,13 +13132,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="189" t="s">
+      <c r="D20" s="184" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="189"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="184"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -13205,8 +13439,8 @@
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="K3:O3"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="K3:P3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13214,7 +13448,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -13241,24 +13475,24 @@
       <c r="D1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="151"/>
-      <c r="H1" s="148" t="s">
+      <c r="G1" s="149"/>
+      <c r="H1" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="148" t="s">
+      <c r="I1" s="146" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="148" t="s">
+      <c r="J1" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="148" t="s">
+      <c r="K1" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="149" t="s">
-        <v>159</v>
-      </c>
-      <c r="M1" s="149" t="s">
-        <v>161</v>
+      <c r="L1" s="147" t="s">
+        <v>158</v>
+      </c>
+      <c r="M1" s="147" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -13266,7 +13500,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="H2" s="158">
+      <c r="H2" s="155">
         <v>46029</v>
       </c>
       <c r="I2" s="79" t="s">
@@ -13275,11 +13509,11 @@
       <c r="J2" s="79">
         <v>70</v>
       </c>
-      <c r="K2" s="143" t="s">
+      <c r="K2" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L2" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M2" s="79">
         <f>J2*40</f>
@@ -13291,7 +13525,7 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="H3" s="158">
+      <c r="H3" s="155">
         <v>46029</v>
       </c>
       <c r="I3" s="79" t="s">
@@ -13300,11 +13534,11 @@
       <c r="J3" s="79">
         <v>10</v>
       </c>
-      <c r="K3" s="143" t="s">
+      <c r="K3" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L3" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M3" s="79">
         <f t="shared" ref="M3:M35" si="0">J3*40</f>
@@ -13316,7 +13550,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="H4" s="158">
+      <c r="H4" s="155">
         <v>46029</v>
       </c>
       <c r="I4" s="79" t="s">
@@ -13325,11 +13559,11 @@
       <c r="J4" s="79">
         <v>9</v>
       </c>
-      <c r="K4" s="143" t="s">
+      <c r="K4" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L4" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M4" s="79">
         <f t="shared" si="0"/>
@@ -13341,18 +13575,20 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="H5" s="155">
+        <v>46060</v>
+      </c>
       <c r="I5" s="79" t="s">
         <v>102</v>
       </c>
       <c r="J5" s="79">
         <v>18</v>
       </c>
-      <c r="K5" s="143" t="s">
+      <c r="K5" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L5" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M5" s="79">
         <f t="shared" si="0"/>
@@ -13364,18 +13600,20 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="155">
+        <v>46060</v>
+      </c>
       <c r="I6" s="79" t="s">
         <v>103</v>
       </c>
       <c r="J6" s="79">
         <v>5</v>
       </c>
-      <c r="K6" s="143" t="s">
+      <c r="K6" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L6" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M6" s="79">
         <f t="shared" si="0"/>
@@ -13387,18 +13625,20 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="155">
+        <v>46088</v>
+      </c>
       <c r="I7" s="79" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J7" s="79">
         <v>14</v>
       </c>
-      <c r="K7" s="143" t="s">
+      <c r="K7" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L7" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M7" s="79">
         <f t="shared" si="0"/>
@@ -13410,20 +13650,22 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="81"/>
+      <c r="F8" s="149"/>
+      <c r="G8" s="149"/>
+      <c r="H8" s="155">
+        <v>46088</v>
+      </c>
       <c r="I8" s="79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J8" s="79">
         <v>13</v>
       </c>
-      <c r="K8" s="143" t="s">
+      <c r="K8" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L8" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M8" s="79">
         <f t="shared" si="0"/>
@@ -13435,18 +13677,20 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="155">
+        <v>46088</v>
+      </c>
       <c r="I9" s="79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J9" s="79">
         <v>4</v>
       </c>
-      <c r="K9" s="143" t="s">
+      <c r="K9" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L9" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M9" s="79">
         <f t="shared" si="0"/>
@@ -13458,20 +13702,20 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>104</v>
+      <c r="H10" s="155">
+        <v>46088</v>
       </c>
       <c r="I10" s="79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J10" s="79">
         <v>12</v>
       </c>
-      <c r="K10" s="147" t="s">
+      <c r="K10" s="145" t="s">
         <v>99</v>
       </c>
       <c r="L10" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M10" s="79">
         <f t="shared" si="0"/>
@@ -13483,20 +13727,20 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>104</v>
+      <c r="H11" s="155">
+        <v>46088</v>
       </c>
       <c r="I11" s="79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J11" s="79">
         <v>19</v>
       </c>
-      <c r="K11" s="147" t="s">
+      <c r="K11" s="145" t="s">
         <v>99</v>
       </c>
       <c r="L11" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M11" s="79">
         <f t="shared" si="0"/>
@@ -13509,14 +13753,14 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="146" t="s">
+      <c r="I12" s="144" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="144">
+        <v>13</v>
+      </c>
+      <c r="K12" s="144" t="s">
         <v>114</v>
-      </c>
-      <c r="J12" s="146">
-        <v>13</v>
-      </c>
-      <c r="K12" s="146" t="s">
-        <v>115</v>
       </c>
       <c r="L12" s="79"/>
       <c r="M12" s="79">
@@ -13529,18 +13773,20 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="155">
+        <v>46272</v>
+      </c>
       <c r="I13" s="79" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J13" s="79">
         <v>5</v>
       </c>
-      <c r="K13" s="143" t="s">
+      <c r="K13" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L13" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M13" s="79">
         <f t="shared" si="0"/>
@@ -13552,18 +13798,20 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="155">
+        <v>46272</v>
+      </c>
       <c r="I14" s="79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J14" s="79">
         <v>8</v>
       </c>
-      <c r="K14" s="143" t="s">
+      <c r="K14" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L14" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M14" s="79">
         <f t="shared" si="0"/>
@@ -13575,18 +13823,20 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="155">
+        <v>46272</v>
+      </c>
       <c r="I15" s="79" t="s">
         <v>98</v>
       </c>
       <c r="J15" s="79">
         <v>10</v>
       </c>
-      <c r="K15" s="143" t="s">
+      <c r="K15" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L15" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M15" s="79">
         <f t="shared" si="0"/>
@@ -13598,18 +13848,20 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="155">
+        <v>46302</v>
+      </c>
       <c r="I16" s="79" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J16" s="79">
         <v>5</v>
       </c>
-      <c r="K16" s="143" t="s">
+      <c r="K16" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L16" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M16" s="79">
         <f t="shared" si="0"/>
@@ -13621,18 +13873,20 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="155">
+        <v>46302</v>
+      </c>
       <c r="I17" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J17" s="79">
         <v>4</v>
       </c>
-      <c r="K17" s="143" t="s">
+      <c r="K17" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L17" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M17" s="79">
         <f t="shared" si="0"/>
@@ -13644,18 +13898,20 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="155">
+        <v>46302</v>
+      </c>
       <c r="I18" s="79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J18" s="79">
         <v>9</v>
       </c>
-      <c r="K18" s="143" t="s">
+      <c r="K18" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L18" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M18" s="79">
         <f t="shared" si="0"/>
@@ -13667,18 +13923,20 @@
       <c r="B19" s="83"/>
       <c r="C19" s="83"/>
       <c r="D19" s="83"/>
-      <c r="H19" s="2"/>
+      <c r="H19" s="155">
+        <v>46302</v>
+      </c>
       <c r="I19" s="79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J19" s="79">
         <v>6</v>
       </c>
-      <c r="K19" s="143" t="s">
+      <c r="K19" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L19" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M19" s="79">
         <f t="shared" si="0"/>
@@ -13690,18 +13948,20 @@
       <c r="B20" s="85"/>
       <c r="C20" s="85"/>
       <c r="D20" s="86"/>
-      <c r="H20" s="2"/>
+      <c r="H20" s="155">
+        <v>46302</v>
+      </c>
       <c r="I20" s="79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J20" s="79">
         <v>30</v>
       </c>
-      <c r="K20" s="143" t="s">
+      <c r="K20" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L20" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M20" s="79">
         <f t="shared" si="0"/>
@@ -13709,18 +13969,20 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H21" s="2"/>
+      <c r="H21" s="155">
+        <v>46302</v>
+      </c>
       <c r="I21" s="79" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="79">
         <v>22</v>
       </c>
-      <c r="K21" s="143" t="s">
+      <c r="K21" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L21" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M21" s="79">
         <f t="shared" si="0"/>
@@ -13728,7 +13990,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H22" s="150">
+      <c r="H22" s="148">
         <v>46333</v>
       </c>
       <c r="I22" s="79" t="s">
@@ -13737,11 +13999,11 @@
       <c r="J22" s="79">
         <v>15</v>
       </c>
-      <c r="K22" s="143" t="s">
+      <c r="K22" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L22" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M22" s="79">
         <f t="shared" si="0"/>
@@ -13749,20 +14011,20 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H23" s="150">
+      <c r="H23" s="148">
         <v>46333</v>
       </c>
       <c r="I23" s="79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J23" s="79">
         <v>4</v>
       </c>
-      <c r="K23" s="143" t="s">
+      <c r="K23" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L23" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M23" s="79">
         <f t="shared" si="0"/>
@@ -13770,20 +14032,20 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H24" s="150">
+      <c r="H24" s="148">
         <v>46333</v>
       </c>
       <c r="I24" s="79" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J24" s="79">
         <v>50</v>
       </c>
-      <c r="K24" s="143" t="s">
+      <c r="K24" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L24" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M24" s="79">
         <f t="shared" si="0"/>
@@ -13791,20 +14053,20 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H25" s="150">
+      <c r="H25" s="148">
         <v>46333</v>
       </c>
       <c r="I25" s="79" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J25" s="79">
         <v>5</v>
       </c>
-      <c r="K25" s="143" t="s">
+      <c r="K25" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L25" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M25" s="79">
         <f t="shared" si="0"/>
@@ -13812,20 +14074,20 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="H26" s="150">
+      <c r="H26" s="148">
         <v>46333</v>
       </c>
       <c r="I26" s="79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J26" s="79">
         <v>50</v>
       </c>
-      <c r="K26" s="143" t="s">
+      <c r="K26" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L26" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M26" s="79">
         <f t="shared" si="0"/>
@@ -13834,19 +14096,19 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H27" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I27" s="79" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J27" s="79">
         <v>5</v>
       </c>
-      <c r="K27" s="143" t="s">
+      <c r="K27" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L27" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M27" s="79">
         <f t="shared" si="0"/>
@@ -13855,19 +14117,19 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H28" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I28" s="79" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J28" s="79">
         <v>7</v>
       </c>
-      <c r="K28" s="143" t="s">
+      <c r="K28" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L28" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M28" s="79">
         <f t="shared" si="0"/>
@@ -13876,19 +14138,19 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I29" s="79" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J29" s="79">
         <v>21</v>
       </c>
-      <c r="K29" s="143" t="s">
+      <c r="K29" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L29" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M29" s="79">
         <f t="shared" si="0"/>
@@ -13897,19 +14159,19 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H30" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I30" s="79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J30" s="79">
         <v>8</v>
       </c>
-      <c r="K30" s="143" t="s">
+      <c r="K30" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L30" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M30" s="79">
         <f t="shared" si="0"/>
@@ -13918,19 +14180,19 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H31" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I31" s="79" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J31" s="79">
         <v>4</v>
       </c>
-      <c r="K31" s="143" t="s">
+      <c r="K31" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L31" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M31" s="79">
         <f t="shared" si="0"/>
@@ -13939,19 +14201,19 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H32" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I32" s="79" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J32" s="79">
         <v>4</v>
       </c>
-      <c r="K32" s="143" t="s">
+      <c r="K32" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L32" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M32" s="79">
         <f t="shared" si="0"/>
@@ -13960,15 +14222,15 @@
     </row>
     <row r="33" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H33" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I33" s="79" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J33" s="79">
         <v>305</v>
       </c>
-      <c r="K33" s="143" t="s">
+      <c r="K33" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L33" s="79"/>
@@ -13979,19 +14241,19 @@
     </row>
     <row r="34" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H34" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I34" s="79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J34" s="79">
         <v>35</v>
       </c>
-      <c r="K34" s="143" t="s">
+      <c r="K34" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L34" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M34" s="79">
         <f t="shared" si="0"/>
@@ -14000,19 +14262,19 @@
     </row>
     <row r="35" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H35" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I35" s="79" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J35" s="79">
         <v>122</v>
       </c>
-      <c r="K35" s="143" t="s">
+      <c r="K35" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L35" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M35" s="79">
         <f t="shared" si="0"/>
@@ -14021,20 +14283,20 @@
     </row>
     <row r="36" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H36" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I36" s="79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J36" s="79">
         <f>M36/40</f>
         <v>10</v>
       </c>
-      <c r="K36" s="143" t="s">
+      <c r="K36" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L36" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M36" s="79">
         <v>400</v>
@@ -14042,20 +14304,20 @@
     </row>
     <row r="37" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H37" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I37" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J37" s="79">
         <f>M37/40</f>
         <v>14</v>
       </c>
-      <c r="K37" s="143" t="s">
+      <c r="K37" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L37" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M37" s="79">
         <v>560</v>
@@ -14063,20 +14325,20 @@
     </row>
     <row r="38" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H38" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I38" s="79" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J38" s="79">
         <f>M38/40</f>
         <v>17</v>
       </c>
-      <c r="K38" s="143" t="s">
+      <c r="K38" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L38" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M38" s="79">
         <v>680</v>
@@ -14084,7 +14346,7 @@
     </row>
     <row r="39" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H39" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I39" s="79" t="s">
         <v>25</v>
@@ -14093,11 +14355,11 @@
         <f>M39/40</f>
         <v>18</v>
       </c>
-      <c r="K39" s="143" t="s">
+      <c r="K39" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L39" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M39" s="79">
         <v>720</v>
@@ -14105,7 +14367,7 @@
     </row>
     <row r="40" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I40" s="79" t="s">
         <v>101</v>
@@ -14113,11 +14375,11 @@
       <c r="J40" s="79">
         <v>12</v>
       </c>
-      <c r="K40" s="143" t="s">
+      <c r="K40" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L40" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M40" s="79">
         <v>160</v>
@@ -14125,19 +14387,19 @@
     </row>
     <row r="41" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H41" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I41" s="79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J41" s="79">
         <v>4</v>
       </c>
-      <c r="K41" s="143" t="s">
+      <c r="K41" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L41" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M41" s="81">
         <f>J41*40</f>
@@ -14145,39 +14407,39 @@
       </c>
     </row>
     <row r="42" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H42" s="152" t="s">
-        <v>174</v>
-      </c>
-      <c r="I42" s="153" t="s">
-        <v>170</v>
-      </c>
-      <c r="J42" s="153">
+      <c r="H42" s="150" t="s">
+        <v>173</v>
+      </c>
+      <c r="I42" s="151" t="s">
+        <v>169</v>
+      </c>
+      <c r="J42" s="151">
         <v>8</v>
       </c>
-      <c r="K42" s="153" t="s">
-        <v>142</v>
-      </c>
-      <c r="L42" s="153"/>
-      <c r="M42" s="153">
+      <c r="K42" s="151" t="s">
+        <v>141</v>
+      </c>
+      <c r="L42" s="151"/>
+      <c r="M42" s="151">
         <f>J42*40</f>
         <v>320</v>
       </c>
     </row>
     <row r="43" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H43" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I43" s="79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J43" s="79">
         <v>9</v>
       </c>
-      <c r="K43" s="143" t="s">
+      <c r="K43" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L43" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M43" s="79">
         <f t="shared" ref="M43:M59" si="1">J43*40</f>
@@ -14185,39 +14447,39 @@
       </c>
     </row>
     <row r="44" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H44" s="152" t="s">
-        <v>174</v>
-      </c>
-      <c r="I44" s="153" t="s">
-        <v>172</v>
-      </c>
-      <c r="J44" s="153">
+      <c r="H44" s="150" t="s">
+        <v>173</v>
+      </c>
+      <c r="I44" s="151" t="s">
+        <v>171</v>
+      </c>
+      <c r="J44" s="151">
         <v>5</v>
       </c>
-      <c r="K44" s="153" t="s">
-        <v>142</v>
-      </c>
-      <c r="L44" s="153"/>
-      <c r="M44" s="153">
+      <c r="K44" s="151" t="s">
+        <v>141</v>
+      </c>
+      <c r="L44" s="151"/>
+      <c r="M44" s="151">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
     <row r="45" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H45" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I45" s="79" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J45" s="79">
         <v>5</v>
       </c>
-      <c r="K45" s="143" t="s">
+      <c r="K45" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L45" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M45" s="79">
         <f t="shared" si="1"/>
@@ -14226,19 +14488,19 @@
     </row>
     <row r="46" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H46" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I46" s="79" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J46" s="79">
         <v>8</v>
       </c>
-      <c r="K46" s="143" t="s">
+      <c r="K46" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L46" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M46" s="79">
         <f t="shared" si="1"/>
@@ -14247,19 +14509,19 @@
     </row>
     <row r="47" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H47" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I47" s="79" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J47" s="79">
         <v>8</v>
       </c>
-      <c r="K47" s="143" t="s">
+      <c r="K47" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L47" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M47" s="79">
         <f t="shared" si="1"/>
@@ -14268,19 +14530,19 @@
     </row>
     <row r="48" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H48" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I48" s="79" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J48" s="79">
         <v>20</v>
       </c>
-      <c r="K48" s="143" t="s">
+      <c r="K48" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L48" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M48" s="79">
         <f t="shared" si="1"/>
@@ -14289,19 +14551,19 @@
     </row>
     <row r="49" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H49" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I49" s="79" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J49" s="79">
         <v>4</v>
       </c>
-      <c r="K49" s="143" t="s">
+      <c r="K49" s="141" t="s">
         <v>99</v>
       </c>
       <c r="L49" s="79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M49" s="79">
         <f t="shared" si="1"/>
@@ -14310,19 +14572,19 @@
     </row>
     <row r="50" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H50" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I50" s="130" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J50" s="130">
         <v>5</v>
       </c>
-      <c r="K50" s="162" t="s">
+      <c r="K50" s="156" t="s">
         <v>99</v>
       </c>
       <c r="L50" s="130" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M50" s="130">
         <f t="shared" si="1"/>
@@ -14331,19 +14593,19 @@
     </row>
     <row r="51" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H51" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I51" s="130" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J51" s="130">
         <v>305</v>
       </c>
-      <c r="K51" s="162" t="s">
+      <c r="K51" s="156" t="s">
         <v>99</v>
       </c>
       <c r="L51" s="130" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M51" s="130">
         <f t="shared" si="1"/>
@@ -14351,155 +14613,316 @@
       </c>
     </row>
     <row r="52" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H52" s="157" t="s">
-        <v>183</v>
-      </c>
-      <c r="I52" s="155" t="s">
-        <v>181</v>
-      </c>
-      <c r="J52" s="155">
+      <c r="H52" s="154" t="s">
+        <v>182</v>
+      </c>
+      <c r="I52" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="J52" s="152">
         <v>300</v>
       </c>
-      <c r="K52" s="155" t="s">
-        <v>142</v>
-      </c>
-      <c r="L52" s="156"/>
-      <c r="M52" s="155">
+      <c r="K52" s="152" t="s">
+        <v>141</v>
+      </c>
+      <c r="L52" s="153"/>
+      <c r="M52" s="152">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
     </row>
     <row r="53" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H53" s="159" t="s">
+      <c r="H53" s="155" t="s">
+        <v>188</v>
+      </c>
+      <c r="I53" s="79" t="s">
         <v>189</v>
       </c>
-      <c r="I53" s="160" t="s">
-        <v>190</v>
-      </c>
-      <c r="J53" s="160">
+      <c r="J53" s="79">
         <v>5</v>
       </c>
-      <c r="K53" s="160" t="s">
-        <v>195</v>
-      </c>
-      <c r="L53" s="161"/>
-      <c r="M53" s="160">
+      <c r="K53" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="L53" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M53" s="79">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
     <row r="54" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H54" s="159" t="s">
-        <v>189</v>
-      </c>
-      <c r="I54" s="161" t="s">
-        <v>191</v>
-      </c>
-      <c r="J54" s="161">
-        <v>8</v>
-      </c>
-      <c r="K54" s="160" t="s">
-        <v>195</v>
-      </c>
-      <c r="L54" s="161"/>
-      <c r="M54" s="161">
+      <c r="H54" s="155" t="s">
+        <v>188</v>
+      </c>
+      <c r="I54" s="81" t="s">
+        <v>190</v>
+      </c>
+      <c r="J54" s="81">
+        <v>7</v>
+      </c>
+      <c r="K54" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="L54" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M54" s="81">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H55" s="158" t="s">
-        <v>189</v>
+      <c r="H55" s="155" t="s">
+        <v>188</v>
       </c>
       <c r="I55" s="81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J55" s="81">
         <v>28</v>
       </c>
       <c r="K55" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="L55" s="81"/>
+        <v>99</v>
+      </c>
+      <c r="L55" s="81" t="s">
+        <v>159</v>
+      </c>
       <c r="M55" s="81">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
     </row>
     <row r="56" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H56" s="158" t="s">
-        <v>189</v>
+      <c r="H56" s="155" t="s">
+        <v>188</v>
       </c>
       <c r="I56" s="81" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J56" s="81">
         <v>44</v>
       </c>
       <c r="K56" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="L56" s="81"/>
+        <v>99</v>
+      </c>
+      <c r="L56" s="81" t="s">
+        <v>159</v>
+      </c>
       <c r="M56" s="81">
         <f t="shared" si="1"/>
         <v>1760</v>
       </c>
     </row>
     <row r="57" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H57" s="158" t="s">
-        <v>189</v>
+      <c r="H57" s="155" t="s">
+        <v>188</v>
       </c>
       <c r="I57" s="81" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J57" s="81">
         <v>30</v>
       </c>
       <c r="K57" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="L57" s="81"/>
+        <v>99</v>
+      </c>
+      <c r="L57" s="81" t="s">
+        <v>159</v>
+      </c>
       <c r="M57" s="81">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
     <row r="58" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H58" s="158" t="s">
-        <v>189</v>
+      <c r="H58" s="155" t="s">
+        <v>188</v>
       </c>
       <c r="I58" s="81" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J58" s="81">
         <v>25</v>
       </c>
       <c r="K58" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="L58" s="81"/>
+        <v>99</v>
+      </c>
+      <c r="L58" s="81" t="s">
+        <v>159</v>
+      </c>
       <c r="M58" s="81">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
     </row>
     <row r="59" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H59" s="158" t="s">
-        <v>189</v>
+      <c r="H59" s="155" t="s">
+        <v>188</v>
       </c>
       <c r="I59" s="81" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J59" s="81">
         <v>11</v>
       </c>
       <c r="K59" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="L59" s="81"/>
+        <v>99</v>
+      </c>
+      <c r="L59" s="81" t="s">
+        <v>159</v>
+      </c>
       <c r="M59" s="81">
         <f t="shared" si="1"/>
         <v>440</v>
+      </c>
+    </row>
+    <row r="60" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H60" s="155" t="s">
+        <v>203</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J60" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="K60" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L60" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M60" s="81">
+        <f>J60*40</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H61" s="155" t="s">
+        <v>203</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J61" s="79">
+        <v>2</v>
+      </c>
+      <c r="K61" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L61" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M61" s="81">
+        <f t="shared" ref="M61:M66" si="2">J61*40</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H62" s="155" t="s">
+        <v>203</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J62" s="79">
+        <v>6</v>
+      </c>
+      <c r="K62" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L62" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M62" s="81">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H63" s="155" t="s">
+        <v>203</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J63" s="79">
+        <v>4</v>
+      </c>
+      <c r="K63" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L63" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M63" s="81">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H64" s="155" t="s">
+        <v>203</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J64" s="79">
+        <v>10</v>
+      </c>
+      <c r="K64" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L64" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M64" s="81">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H65" s="155" t="s">
+        <v>203</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J65" s="79">
+        <v>18</v>
+      </c>
+      <c r="K65" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L65" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M65" s="81">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="66" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H66" s="155" t="s">
+        <v>203</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J66" s="79">
+        <v>9</v>
+      </c>
+      <c r="K66" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L66" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="M66" s="81">
+        <f t="shared" si="2"/>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -14507,7 +14930,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80DF3CCA-0793-4D04-8BF6-1A26354907F3}">
           <x14:formula1>
             <xm:f>Sheet1!$B$10:$B$22</xm:f>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E5A29A-6A1C-4B03-81AC-FB75C985F845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2156C53-10F7-4BBA-B23F-E01BD26DA496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1545,7 +1545,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1946,108 +1946,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2059,15 +1957,107 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2604,14 +2594,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="158">
+      <c r="B1" s="176">
         <f ca="1">TODAY()</f>
         <v>46227</v>
       </c>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2633,10 +2623,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="180" t="s">
+      <c r="A2" s="173" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="177" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2669,13 +2659,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="172"/>
-      <c r="N2" s="173"/>
-      <c r="O2" s="174"/>
-      <c r="P2" s="175" t="s">
+      <c r="M2" s="165"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="176"/>
+      <c r="Q2" s="169"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2694,8 +2684,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="180"/>
-      <c r="B3" s="160"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="178"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2726,29 +2716,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="177" t="s">
+      <c r="M3" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="178"/>
-      <c r="O3" s="179"/>
+      <c r="N3" s="171"/>
+      <c r="O3" s="172"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="162" t="s">
+      <c r="R3" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="163"/>
-      <c r="T3" s="163"/>
-      <c r="U3" s="164"/>
-      <c r="V3" s="165" t="s">
+      <c r="S3" s="181"/>
+      <c r="T3" s="181"/>
+      <c r="U3" s="182"/>
+      <c r="V3" s="183" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="166"/>
-      <c r="X3" s="166"/>
-      <c r="Y3" s="167"/>
+      <c r="W3" s="184"/>
+      <c r="X3" s="184"/>
+      <c r="Y3" s="185"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="180"/>
-      <c r="B4" s="161"/>
+      <c r="A4" s="173"/>
+      <c r="B4" s="179"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -6990,26 +6980,26 @@
       <c r="B60" s="47">
         <v>56</v>
       </c>
-      <c r="C60" s="197" t="s">
+      <c r="C60" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="D60" s="198"/>
-      <c r="E60" s="198"/>
-      <c r="F60" s="198"/>
-      <c r="G60" s="198">
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="75">
         <v>40</v>
       </c>
-      <c r="H60" s="198">
+      <c r="H60" s="75">
         <v>400</v>
       </c>
-      <c r="I60" s="199"/>
-      <c r="J60" s="198">
+      <c r="I60" s="132"/>
+      <c r="J60" s="75">
         <v>160</v>
       </c>
-      <c r="K60" s="198">
+      <c r="K60" s="75">
         <v>320</v>
       </c>
-      <c r="L60" s="198">
+      <c r="L60" s="75">
         <v>200</v>
       </c>
       <c r="M60" s="135">
@@ -7072,26 +7062,26 @@
       <c r="B61" s="47">
         <v>57</v>
       </c>
-      <c r="C61" s="200" t="s">
+      <c r="C61" s="133" t="s">
         <v>191</v>
       </c>
-      <c r="D61" s="198"/>
-      <c r="E61" s="198"/>
-      <c r="F61" s="198"/>
-      <c r="G61" s="198">
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75">
         <v>200</v>
       </c>
-      <c r="H61" s="198">
+      <c r="H61" s="75">
         <v>320</v>
       </c>
-      <c r="I61" s="199"/>
-      <c r="J61" s="198">
+      <c r="I61" s="132"/>
+      <c r="J61" s="75">
         <v>320</v>
       </c>
-      <c r="K61" s="198">
+      <c r="K61" s="75">
         <v>400</v>
       </c>
-      <c r="L61" s="198">
+      <c r="L61" s="75">
         <v>520</v>
       </c>
       <c r="M61" s="135">
@@ -7154,26 +7144,26 @@
       <c r="B62" s="47">
         <v>58</v>
       </c>
-      <c r="C62" s="200" t="s">
+      <c r="C62" s="133" t="s">
         <v>192</v>
       </c>
-      <c r="D62" s="198"/>
-      <c r="E62" s="198"/>
-      <c r="F62" s="198"/>
-      <c r="G62" s="198">
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="75">
         <v>240</v>
       </c>
-      <c r="H62" s="198">
+      <c r="H62" s="75">
         <v>240</v>
       </c>
-      <c r="I62" s="199"/>
-      <c r="J62" s="198">
+      <c r="I62" s="132"/>
+      <c r="J62" s="75">
         <v>240</v>
       </c>
-      <c r="K62" s="198">
+      <c r="K62" s="75">
         <v>240</v>
       </c>
-      <c r="L62" s="198">
+      <c r="L62" s="75">
         <v>240</v>
       </c>
       <c r="M62" s="135">
@@ -7236,26 +7226,26 @@
       <c r="B63" s="47">
         <v>59</v>
       </c>
-      <c r="C63" s="200" t="s">
+      <c r="C63" s="133" t="s">
         <v>193</v>
       </c>
-      <c r="D63" s="198"/>
-      <c r="E63" s="198"/>
-      <c r="F63" s="198"/>
-      <c r="G63" s="198">
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="75">
         <v>200</v>
       </c>
-      <c r="H63" s="198">
+      <c r="H63" s="75">
         <v>200</v>
       </c>
-      <c r="I63" s="199"/>
-      <c r="J63" s="198">
+      <c r="I63" s="132"/>
+      <c r="J63" s="75">
         <v>200</v>
       </c>
-      <c r="K63" s="198">
+      <c r="K63" s="75">
         <v>200</v>
       </c>
-      <c r="L63" s="198">
+      <c r="L63" s="75">
         <v>200</v>
       </c>
       <c r="M63" s="135">
@@ -7318,26 +7308,26 @@
       <c r="B64" s="47">
         <v>60</v>
       </c>
-      <c r="C64" s="200" t="s">
+      <c r="C64" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="D64" s="198"/>
-      <c r="E64" s="198"/>
-      <c r="F64" s="198"/>
-      <c r="G64" s="198">
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
+      <c r="F64" s="75"/>
+      <c r="G64" s="75">
         <v>80</v>
       </c>
-      <c r="H64" s="198">
+      <c r="H64" s="75">
         <v>80</v>
       </c>
-      <c r="I64" s="199"/>
-      <c r="J64" s="198">
+      <c r="I64" s="132"/>
+      <c r="J64" s="75">
         <v>80</v>
       </c>
-      <c r="K64" s="198">
+      <c r="K64" s="75">
         <v>80</v>
       </c>
-      <c r="L64" s="198">
+      <c r="L64" s="75">
         <v>120</v>
       </c>
       <c r="M64" s="135">
@@ -7400,28 +7390,28 @@
       <c r="B65" s="47">
         <v>61</v>
       </c>
-      <c r="C65" s="200" t="s">
+      <c r="C65" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="D65" s="198">
+      <c r="D65" s="75">
         <v>4000</v>
       </c>
-      <c r="E65" s="198"/>
-      <c r="F65" s="198"/>
-      <c r="G65" s="198">
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="75">
         <v>600</v>
       </c>
-      <c r="H65" s="198">
+      <c r="H65" s="75">
         <v>800</v>
       </c>
-      <c r="I65" s="199"/>
-      <c r="J65" s="198">
+      <c r="I65" s="132"/>
+      <c r="J65" s="75">
         <v>2800</v>
       </c>
-      <c r="K65" s="198">
+      <c r="K65" s="75">
         <v>1200</v>
       </c>
-      <c r="L65" s="198">
+      <c r="L65" s="75">
         <v>2600</v>
       </c>
       <c r="M65" s="135">
@@ -7484,26 +7474,26 @@
       <c r="B66" s="47">
         <v>62</v>
       </c>
-      <c r="C66" s="192" t="s">
+      <c r="C66" s="158" t="s">
         <v>190</v>
       </c>
-      <c r="D66" s="193"/>
-      <c r="E66" s="193"/>
-      <c r="F66" s="193"/>
-      <c r="G66" s="193">
+      <c r="D66" s="159"/>
+      <c r="E66" s="159"/>
+      <c r="F66" s="159"/>
+      <c r="G66" s="159">
         <v>40</v>
       </c>
-      <c r="H66" s="193">
+      <c r="H66" s="159">
         <v>40</v>
       </c>
-      <c r="I66" s="194"/>
-      <c r="J66" s="193">
+      <c r="I66" s="160"/>
+      <c r="J66" s="159">
         <v>40</v>
       </c>
-      <c r="K66" s="193">
+      <c r="K66" s="159">
         <v>80</v>
       </c>
-      <c r="L66" s="193">
+      <c r="L66" s="159">
         <v>80</v>
       </c>
       <c r="M66" s="135">
@@ -7566,18 +7556,18 @@
       <c r="B67" s="47">
         <v>63</v>
       </c>
-      <c r="C67" s="192" t="s">
+      <c r="C67" s="158" t="s">
         <v>195</v>
       </c>
-      <c r="D67" s="193"/>
-      <c r="E67" s="193"/>
-      <c r="F67" s="193"/>
-      <c r="G67" s="193"/>
-      <c r="H67" s="193"/>
-      <c r="I67" s="194"/>
-      <c r="J67" s="193"/>
-      <c r="K67" s="193"/>
-      <c r="L67" s="193">
+      <c r="D67" s="159"/>
+      <c r="E67" s="159"/>
+      <c r="F67" s="159"/>
+      <c r="G67" s="159"/>
+      <c r="H67" s="159"/>
+      <c r="I67" s="160"/>
+      <c r="J67" s="159"/>
+      <c r="K67" s="159"/>
+      <c r="L67" s="159">
         <v>200</v>
       </c>
       <c r="M67" s="135">
@@ -7640,26 +7630,26 @@
       <c r="B68" s="47">
         <v>64</v>
       </c>
-      <c r="C68" s="192" t="s">
+      <c r="C68" s="158" t="s">
         <v>196</v>
       </c>
-      <c r="D68" s="193"/>
-      <c r="E68" s="193"/>
-      <c r="F68" s="193"/>
-      <c r="G68" s="193">
+      <c r="D68" s="159"/>
+      <c r="E68" s="159"/>
+      <c r="F68" s="159"/>
+      <c r="G68" s="159">
         <v>10</v>
       </c>
-      <c r="H68" s="193">
+      <c r="H68" s="159">
         <v>10</v>
       </c>
-      <c r="I68" s="194"/>
-      <c r="J68" s="193">
+      <c r="I68" s="160"/>
+      <c r="J68" s="159">
         <v>10</v>
       </c>
-      <c r="K68" s="193">
+      <c r="K68" s="159">
         <v>10</v>
       </c>
-      <c r="L68" s="193">
+      <c r="L68" s="159">
         <v>20</v>
       </c>
       <c r="M68" s="135">
@@ -7722,26 +7712,26 @@
       <c r="B69" s="47">
         <v>65</v>
       </c>
-      <c r="C69" s="192" t="s">
+      <c r="C69" s="158" t="s">
         <v>197</v>
       </c>
-      <c r="D69" s="193"/>
-      <c r="E69" s="193"/>
-      <c r="F69" s="193"/>
-      <c r="G69" s="193">
+      <c r="D69" s="159"/>
+      <c r="E69" s="159"/>
+      <c r="F69" s="159"/>
+      <c r="G69" s="159">
         <v>10</v>
       </c>
-      <c r="H69" s="193">
+      <c r="H69" s="159">
         <v>10</v>
       </c>
-      <c r="I69" s="194"/>
-      <c r="J69" s="193">
+      <c r="I69" s="160"/>
+      <c r="J69" s="159">
         <v>20</v>
       </c>
-      <c r="K69" s="193">
+      <c r="K69" s="159">
         <v>20</v>
       </c>
-      <c r="L69" s="193">
+      <c r="L69" s="159">
         <v>20</v>
       </c>
       <c r="M69" s="135">
@@ -7804,24 +7794,24 @@
       <c r="B70" s="47">
         <v>66</v>
       </c>
-      <c r="C70" s="192" t="s">
+      <c r="C70" s="158" t="s">
         <v>198</v>
       </c>
-      <c r="D70" s="193"/>
-      <c r="E70" s="193"/>
-      <c r="F70" s="193"/>
-      <c r="G70" s="193">
+      <c r="D70" s="159"/>
+      <c r="E70" s="159"/>
+      <c r="F70" s="159"/>
+      <c r="G70" s="159">
         <v>40</v>
       </c>
-      <c r="H70" s="193"/>
-      <c r="I70" s="194"/>
-      <c r="J70" s="193">
+      <c r="H70" s="159"/>
+      <c r="I70" s="160"/>
+      <c r="J70" s="159">
         <v>40</v>
       </c>
-      <c r="K70" s="193">
+      <c r="K70" s="159">
         <v>80</v>
       </c>
-      <c r="L70" s="193">
+      <c r="L70" s="159">
         <v>80</v>
       </c>
       <c r="M70" s="135">
@@ -7884,24 +7874,24 @@
       <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="192" t="s">
+      <c r="C71" s="158" t="s">
         <v>199</v>
       </c>
-      <c r="D71" s="193"/>
-      <c r="E71" s="193"/>
-      <c r="F71" s="193"/>
-      <c r="G71" s="193">
+      <c r="D71" s="159"/>
+      <c r="E71" s="159"/>
+      <c r="F71" s="159"/>
+      <c r="G71" s="159">
         <v>40</v>
       </c>
-      <c r="H71" s="193">
+      <c r="H71" s="159">
         <v>40</v>
       </c>
-      <c r="I71" s="194"/>
-      <c r="J71" s="193"/>
-      <c r="K71" s="193">
+      <c r="I71" s="160"/>
+      <c r="J71" s="159"/>
+      <c r="K71" s="159">
         <v>40</v>
       </c>
-      <c r="L71" s="193">
+      <c r="L71" s="159">
         <v>40</v>
       </c>
       <c r="M71" s="135">
@@ -7964,26 +7954,26 @@
       <c r="B72" s="47">
         <v>68</v>
       </c>
-      <c r="C72" s="192" t="s">
+      <c r="C72" s="158" t="s">
         <v>200</v>
       </c>
-      <c r="D72" s="193"/>
-      <c r="E72" s="193"/>
-      <c r="F72" s="193"/>
-      <c r="G72" s="193">
+      <c r="D72" s="159"/>
+      <c r="E72" s="159"/>
+      <c r="F72" s="159"/>
+      <c r="G72" s="159">
         <v>80</v>
       </c>
-      <c r="H72" s="193">
+      <c r="H72" s="159">
         <v>80</v>
       </c>
-      <c r="I72" s="194"/>
-      <c r="J72" s="193">
+      <c r="I72" s="160"/>
+      <c r="J72" s="159">
         <v>80</v>
       </c>
-      <c r="K72" s="193">
+      <c r="K72" s="159">
         <v>80</v>
       </c>
-      <c r="L72" s="193">
+      <c r="L72" s="159">
         <v>80</v>
       </c>
       <c r="M72" s="135">
@@ -8046,22 +8036,22 @@
       <c r="B73" s="47">
         <v>69</v>
       </c>
-      <c r="C73" s="192" t="s">
+      <c r="C73" s="158" t="s">
         <v>201</v>
       </c>
-      <c r="D73" s="193"/>
-      <c r="E73" s="193"/>
-      <c r="F73" s="193"/>
-      <c r="G73" s="193">
+      <c r="D73" s="159"/>
+      <c r="E73" s="159"/>
+      <c r="F73" s="159"/>
+      <c r="G73" s="159">
         <v>200</v>
       </c>
-      <c r="H73" s="193">
+      <c r="H73" s="159">
         <v>120</v>
       </c>
-      <c r="I73" s="194"/>
-      <c r="J73" s="193"/>
-      <c r="K73" s="193"/>
-      <c r="L73" s="193">
+      <c r="I73" s="160"/>
+      <c r="J73" s="159"/>
+      <c r="K73" s="159"/>
+      <c r="L73" s="159">
         <v>400</v>
       </c>
       <c r="M73" s="135">
@@ -8124,26 +8114,26 @@
       <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="195" t="s">
+      <c r="C74" s="161" t="s">
         <v>202</v>
       </c>
-      <c r="D74" s="193"/>
-      <c r="E74" s="193"/>
-      <c r="F74" s="196"/>
-      <c r="G74" s="193">
+      <c r="D74" s="159"/>
+      <c r="E74" s="159"/>
+      <c r="F74" s="162"/>
+      <c r="G74" s="159">
         <v>40</v>
       </c>
-      <c r="H74" s="193">
+      <c r="H74" s="159">
         <v>80</v>
       </c>
-      <c r="I74" s="194"/>
-      <c r="J74" s="193">
+      <c r="I74" s="160"/>
+      <c r="J74" s="159">
         <v>80</v>
       </c>
-      <c r="K74" s="193">
+      <c r="K74" s="159">
         <v>80</v>
       </c>
-      <c r="L74" s="193">
+      <c r="L74" s="159">
         <v>80</v>
       </c>
       <c r="M74" s="135">
@@ -12061,10 +12051,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="168" t="s">
+      <c r="B132" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="169"/>
+      <c r="C132" s="187"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12328,10 +12318,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="181" t="s">
+      <c r="B136" s="174" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="182"/>
+      <c r="C136" s="175"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12422,10 +12412,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="170" t="s">
+      <c r="B137" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="171"/>
+      <c r="C137" s="164"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12517,17 +12507,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12545,7 +12535,7 @@
     <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="4.08984375" customWidth="1"/>
     <col min="3" max="3" width="10.7265625" customWidth="1"/>
-    <col min="4" max="4" width="39.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" customWidth="1"/>
     <col min="5" max="6" width="12.36328125" customWidth="1"/>
     <col min="7" max="7" width="11.26953125" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
@@ -12563,25 +12553,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="185" t="s">
+      <c r="C3" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="189" t="s">
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="194" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="190"/>
-      <c r="K3" s="191" t="s">
+      <c r="I3" s="195"/>
+      <c r="K3" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
-      <c r="N3" s="191"/>
-      <c r="O3" s="191"/>
-      <c r="P3" s="191"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="196"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="196"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12627,24 +12617,24 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>772</v>
+        <v>817</v>
       </c>
       <c r="E5" s="79">
-        <v>1241</v>
+        <v>1304</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>2613</v>
+        <v>2721</v>
       </c>
       <c r="H5" s="99">
         <v>10000</v>
       </c>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>-7387</v>
+        <v>-7279</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12669,11 +12659,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>30880</v>
+        <v>32680</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>49640</v>
+        <v>52160</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12681,7 +12671,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>104520</v>
+        <v>108840</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12689,7 +12679,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>-295480</v>
+        <v>-291160</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12816,11 +12806,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-772</v>
+        <v>-817</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-1241</v>
+        <v>-1304</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -12904,14 +12894,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="188" t="s">
+      <c r="C11" s="193" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="188"/>
-      <c r="F11" s="188" t="s">
+      <c r="D11" s="193"/>
+      <c r="F11" s="193" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="188"/>
+      <c r="G11" s="193"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12960,7 +12950,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>6047</v>
+        <v>6155</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -13011,12 +13001,12 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>241880</v>
-      </c>
-      <c r="S13" s="183" t="s">
+        <v>246200</v>
+      </c>
+      <c r="S13" s="188" t="s">
         <v>152</v>
       </c>
-      <c r="T13" s="183"/>
+      <c r="T13" s="188"/>
       <c r="U13" s="141">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13132,13 +13122,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="184" t="s">
+      <c r="D20" s="189" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="184"/>
-      <c r="F20" s="184"/>
-      <c r="G20" s="184"/>
-      <c r="H20" s="184"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="189"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="189"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2156C53-10F7-4BBA-B23F-E01BD26DA496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA21E7D5-036E-4005-997F-C3655962911E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="210">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -638,6 +638,24 @@
   </si>
   <si>
     <t>23/07/26</t>
+  </si>
+  <si>
+    <t>Aster Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem Pujab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usman Canvenioun </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aster </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem Store punhab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usman Canvinain </t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1563,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1957,6 +1975,42 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1996,42 +2050,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2059,6 +2077,7 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2594,14 +2613,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="176">
+      <c r="B1" s="163">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
-      </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
+        <v>46228</v>
+      </c>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2623,10 +2642,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="164" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2659,13 +2678,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="165"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="168" t="s">
+      <c r="M2" s="177"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="179"/>
+      <c r="P2" s="180" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="169"/>
+      <c r="Q2" s="181"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2684,8 +2703,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="173"/>
-      <c r="B3" s="178"/>
+      <c r="A3" s="185"/>
+      <c r="B3" s="165"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2716,29 +2735,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="170" t="s">
+      <c r="M3" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="171"/>
-      <c r="O3" s="172"/>
+      <c r="N3" s="183"/>
+      <c r="O3" s="184"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="180" t="s">
+      <c r="R3" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="181"/>
-      <c r="T3" s="181"/>
-      <c r="U3" s="182"/>
-      <c r="V3" s="183" t="s">
+      <c r="S3" s="168"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169"/>
+      <c r="V3" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="184"/>
-      <c r="X3" s="184"/>
-      <c r="Y3" s="185"/>
+      <c r="W3" s="171"/>
+      <c r="X3" s="171"/>
+      <c r="Y3" s="172"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="173"/>
-      <c r="B4" s="179"/>
+      <c r="A4" s="185"/>
+      <c r="B4" s="166"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -8194,19 +8213,31 @@
       <c r="B75" s="47">
         <v>71</v>
       </c>
-      <c r="C75" s="134"/>
+      <c r="C75" s="134" t="s">
+        <v>207</v>
+      </c>
       <c r="D75" s="75"/>
       <c r="E75" s="50"/>
       <c r="F75" s="50"/>
-      <c r="G75" s="75"/>
-      <c r="H75" s="75"/>
+      <c r="G75" s="75">
+        <v>80</v>
+      </c>
+      <c r="H75" s="75">
+        <v>80</v>
+      </c>
       <c r="I75" s="132"/>
-      <c r="J75" s="75"/>
-      <c r="K75" s="75"/>
-      <c r="L75" s="75"/>
+      <c r="J75" s="75">
+        <v>80</v>
+      </c>
+      <c r="K75" s="75">
+        <v>80</v>
+      </c>
+      <c r="L75" s="75">
+        <v>80</v>
+      </c>
       <c r="M75" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N75" s="39">
         <f t="shared" si="18"/>
@@ -8218,11 +8249,11 @@
       </c>
       <c r="P75" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q75" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R75" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8262,19 +8293,31 @@
       <c r="B76" s="47">
         <v>72</v>
       </c>
-      <c r="C76" s="134"/>
+      <c r="C76" s="134" t="s">
+        <v>208</v>
+      </c>
       <c r="D76" s="75"/>
       <c r="E76" s="50"/>
       <c r="F76" s="50"/>
-      <c r="G76" s="75"/>
-      <c r="H76" s="75"/>
+      <c r="G76" s="75">
+        <v>200</v>
+      </c>
+      <c r="H76" s="75">
+        <v>200</v>
+      </c>
       <c r="I76" s="132"/>
-      <c r="J76" s="75"/>
-      <c r="K76" s="75"/>
-      <c r="L76" s="75"/>
+      <c r="J76" s="75">
+        <v>200</v>
+      </c>
+      <c r="K76" s="75">
+        <v>200</v>
+      </c>
+      <c r="L76" s="75">
+        <v>200</v>
+      </c>
       <c r="M76" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N76" s="39">
         <f t="shared" si="18"/>
@@ -8286,11 +8329,11 @@
       </c>
       <c r="P76" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q76" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R76" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8330,19 +8373,31 @@
       <c r="B77" s="47">
         <v>73</v>
       </c>
-      <c r="C77" s="134"/>
+      <c r="C77" s="134" t="s">
+        <v>169</v>
+      </c>
       <c r="D77" s="75"/>
       <c r="E77" s="50"/>
       <c r="F77" s="50"/>
-      <c r="G77" s="50"/>
-      <c r="H77" s="50"/>
+      <c r="G77" s="50">
+        <v>80</v>
+      </c>
+      <c r="H77" s="50">
+        <v>160</v>
+      </c>
       <c r="I77" s="135"/>
-      <c r="J77" s="50"/>
-      <c r="K77" s="50"/>
-      <c r="L77" s="50"/>
+      <c r="J77" s="50">
+        <v>40</v>
+      </c>
+      <c r="K77" s="50">
+        <v>40</v>
+      </c>
+      <c r="L77" s="50">
+        <v>40</v>
+      </c>
       <c r="M77" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N77" s="39">
         <f t="shared" si="18"/>
@@ -8354,11 +8409,11 @@
       </c>
       <c r="P77" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q77" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R77" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8398,19 +8453,31 @@
       <c r="B78" s="47">
         <v>74</v>
       </c>
-      <c r="C78" s="134"/>
+      <c r="C78" s="134" t="s">
+        <v>209</v>
+      </c>
       <c r="D78" s="75"/>
       <c r="E78" s="50"/>
       <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
-      <c r="H78" s="50"/>
+      <c r="G78" s="50">
+        <v>40</v>
+      </c>
+      <c r="H78" s="50">
+        <v>40</v>
+      </c>
       <c r="I78" s="135"/>
-      <c r="J78" s="50"/>
-      <c r="K78" s="50"/>
-      <c r="L78" s="50"/>
+      <c r="J78" s="50">
+        <v>40</v>
+      </c>
+      <c r="K78" s="50">
+        <v>40</v>
+      </c>
+      <c r="L78" s="50">
+        <v>40</v>
+      </c>
       <c r="M78" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N78" s="39">
         <f t="shared" si="18"/>
@@ -8422,11 +8489,11 @@
       </c>
       <c r="P78" s="73">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q78" s="40">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R78" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12051,10 +12118,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="186" t="s">
+      <c r="B132" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="187"/>
+      <c r="C132" s="174"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12318,10 +12385,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="174" t="s">
+      <c r="B136" s="186" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="175"/>
+      <c r="C136" s="187"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12412,10 +12479,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="163" t="s">
+      <c r="B137" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="164"/>
+      <c r="C137" s="176"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12466,11 +12533,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>1149.9000000000001</v>
+        <v>1193.9000000000001</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>2998</v>
+        <v>3052</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12507,17 +12574,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -13438,7 +13505,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -14913,6 +14980,26 @@
       <c r="M66" s="81">
         <f t="shared" si="2"/>
         <v>360</v>
+      </c>
+    </row>
+    <row r="67" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="I67" s="197" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="I68" s="197" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="69" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="I69" s="197" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="I70" s="197" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA21E7D5-036E-4005-997F-C3655962911E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC50090-65EC-42A0-8615-4D6E515AA359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="211">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -656,6 +656,9 @@
   </si>
   <si>
     <t xml:space="preserve">Usman Canvinain </t>
+  </si>
+  <si>
+    <t>24/07/26</t>
   </si>
 </sst>
 </file>
@@ -1975,6 +1978,46 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2011,45 +2054,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2077,7 +2081,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2613,14 +2616,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="163">
+      <c r="B1" s="177">
         <f ca="1">TODAY()</f>
         <v>46228</v>
       </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2642,10 +2645,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="178" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2678,13 +2681,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="177"/>
-      <c r="N2" s="178"/>
-      <c r="O2" s="179"/>
-      <c r="P2" s="180" t="s">
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="181"/>
+      <c r="Q2" s="170"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2703,8 +2706,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="185"/>
-      <c r="B3" s="165"/>
+      <c r="A3" s="174"/>
+      <c r="B3" s="179"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2735,29 +2738,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="182" t="s">
+      <c r="M3" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="183"/>
-      <c r="O3" s="184"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="173"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="167" t="s">
+      <c r="R3" s="181" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="168"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169"/>
-      <c r="V3" s="170" t="s">
+      <c r="S3" s="182"/>
+      <c r="T3" s="182"/>
+      <c r="U3" s="183"/>
+      <c r="V3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="171"/>
-      <c r="X3" s="171"/>
-      <c r="Y3" s="172"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="186"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="185"/>
-      <c r="B4" s="166"/>
+      <c r="A4" s="174"/>
+      <c r="B4" s="180"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -8209,7 +8212,9 @@
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A75" s="78"/>
+      <c r="A75" s="78">
+        <v>24</v>
+      </c>
       <c r="B75" s="47">
         <v>71</v>
       </c>
@@ -8289,7 +8294,9 @@
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A76" s="78"/>
+      <c r="A76" s="78">
+        <v>24</v>
+      </c>
       <c r="B76" s="47">
         <v>72</v>
       </c>
@@ -8369,7 +8376,9 @@
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A77" s="78"/>
+      <c r="A77" s="78">
+        <v>24</v>
+      </c>
       <c r="B77" s="47">
         <v>73</v>
       </c>
@@ -8449,7 +8458,9 @@
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A78" s="78"/>
+      <c r="A78" s="78">
+        <v>24</v>
+      </c>
       <c r="B78" s="47">
         <v>74</v>
       </c>
@@ -12118,10 +12129,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="173" t="s">
+      <c r="B132" s="187" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="174"/>
+      <c r="C132" s="188"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12385,10 +12396,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="186" t="s">
+      <c r="B136" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="187"/>
+      <c r="C136" s="176"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12479,10 +12490,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="175" t="s">
+      <c r="B137" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="176"/>
+      <c r="C137" s="165"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12574,17 +12585,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12620,25 +12631,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="190" t="s">
+      <c r="C3" s="191" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="194" t="s">
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="193"/>
+      <c r="H3" s="195" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="195"/>
-      <c r="K3" s="196" t="s">
+      <c r="I3" s="196"/>
+      <c r="K3" s="197" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
-      <c r="N3" s="196"/>
-      <c r="O3" s="196"/>
-      <c r="P3" s="196"/>
+      <c r="L3" s="197"/>
+      <c r="M3" s="197"/>
+      <c r="N3" s="197"/>
+      <c r="O3" s="197"/>
+      <c r="P3" s="197"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12961,14 +12972,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="193" t="s">
+      <c r="C11" s="194" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="193"/>
-      <c r="F11" s="193" t="s">
+      <c r="D11" s="194"/>
+      <c r="F11" s="194" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="193"/>
+      <c r="G11" s="194"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -13070,10 +13081,10 @@
         <f>G12*40</f>
         <v>246200</v>
       </c>
-      <c r="S13" s="188" t="s">
+      <c r="S13" s="189" t="s">
         <v>152</v>
       </c>
-      <c r="T13" s="188"/>
+      <c r="T13" s="189"/>
       <c r="U13" s="141">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13189,13 +13200,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="189" t="s">
+      <c r="D20" s="190" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="189"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
+      <c r="E20" s="190"/>
+      <c r="F20" s="190"/>
+      <c r="G20" s="190"/>
+      <c r="H20" s="190"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -14983,22 +14994,34 @@
       </c>
     </row>
     <row r="67" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="I67" s="197" t="s">
+      <c r="H67" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="I67" s="163" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="68" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="I68" s="197" t="s">
+      <c r="H68" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="I68" s="163" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="69" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="I69" s="197" t="s">
+      <c r="H69" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="I69" s="163" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="70" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="I70" s="197" t="s">
+      <c r="H70" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="I70" s="163" t="s">
         <v>206</v>
       </c>
     </row>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC50090-65EC-42A0-8615-4D6E515AA359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6174056-5273-48E2-8704-66166CDA153A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="212">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -659,6 +659,9 @@
   </si>
   <si>
     <t>24/07/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Shadbagh </t>
   </si>
 </sst>
 </file>
@@ -1979,6 +1982,42 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2016,42 +2055,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2616,14 +2619,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="177">
+      <c r="B1" s="164">
         <f ca="1">TODAY()</f>
-        <v>46228</v>
-      </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
+        <v>46230</v>
+      </c>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2645,10 +2648,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="186" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="178" t="s">
+      <c r="B2" s="165" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2681,13 +2684,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169" t="s">
+      <c r="M2" s="178"/>
+      <c r="N2" s="179"/>
+      <c r="O2" s="180"/>
+      <c r="P2" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="170"/>
+      <c r="Q2" s="182"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2706,8 +2709,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="174"/>
-      <c r="B3" s="179"/>
+      <c r="A3" s="186"/>
+      <c r="B3" s="166"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2738,29 +2741,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="171" t="s">
+      <c r="M3" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="172"/>
-      <c r="O3" s="173"/>
+      <c r="N3" s="184"/>
+      <c r="O3" s="185"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="181" t="s">
+      <c r="R3" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="182"/>
-      <c r="T3" s="182"/>
-      <c r="U3" s="183"/>
-      <c r="V3" s="184" t="s">
+      <c r="S3" s="169"/>
+      <c r="T3" s="169"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="185"/>
-      <c r="X3" s="185"/>
-      <c r="Y3" s="186"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="173"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="174"/>
-      <c r="B4" s="180"/>
+      <c r="A4" s="186"/>
+      <c r="B4" s="167"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -8540,23 +8543,39 @@
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A79" s="78"/>
+      <c r="A79" s="78">
+        <v>25</v>
+      </c>
       <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="133"/>
-      <c r="D79" s="50"/>
+      <c r="C79" s="133" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" s="50">
+        <v>200</v>
+      </c>
       <c r="E79" s="50"/>
       <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
+      <c r="G79" s="50">
+        <v>200</v>
+      </c>
+      <c r="H79" s="50">
+        <v>200</v>
+      </c>
       <c r="I79" s="135"/>
-      <c r="J79" s="50"/>
-      <c r="K79" s="50"/>
-      <c r="L79" s="50"/>
+      <c r="J79" s="50">
+        <v>200</v>
+      </c>
+      <c r="K79" s="50">
+        <v>200</v>
+      </c>
+      <c r="L79" s="50">
+        <v>200</v>
+      </c>
       <c r="M79" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N79" s="39">
         <f t="shared" si="18"/>
@@ -8568,11 +8587,11 @@
       </c>
       <c r="P79" s="73">
         <f t="shared" ref="P79:P83" si="89">SUM(G79:I79)/20</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q79" s="40">
         <f t="shared" ref="Q79:Q83" si="90">SUM(J79:L79)/20</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R79" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8608,23 +8627,33 @@
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A80" s="78"/>
+      <c r="A80" s="78">
+        <v>25</v>
+      </c>
       <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="133"/>
+      <c r="C80" s="133" t="s">
+        <v>129</v>
+      </c>
       <c r="D80" s="50"/>
       <c r="E80" s="50"/>
       <c r="F80" s="50"/>
       <c r="G80" s="50"/>
       <c r="H80" s="50"/>
       <c r="I80" s="135"/>
-      <c r="J80" s="50"/>
-      <c r="K80" s="50"/>
-      <c r="L80" s="50"/>
+      <c r="J80" s="50">
+        <v>120</v>
+      </c>
+      <c r="K80" s="50">
+        <v>120</v>
+      </c>
+      <c r="L80" s="50">
+        <v>80</v>
+      </c>
       <c r="M80" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N80" s="39">
         <f t="shared" si="18"/>
@@ -8640,7 +8669,7 @@
       </c>
       <c r="Q80" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R80" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8676,11 +8705,15 @@
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A81" s="78"/>
+      <c r="A81" s="78">
+        <v>25</v>
+      </c>
       <c r="B81" s="47">
         <v>77</v>
       </c>
-      <c r="C81" s="133"/>
+      <c r="C81" s="133" t="s">
+        <v>211</v>
+      </c>
       <c r="D81" s="50"/>
       <c r="E81" s="50"/>
       <c r="F81" s="50"/>
@@ -8688,11 +8721,13 @@
       <c r="H81" s="50"/>
       <c r="I81" s="135"/>
       <c r="J81" s="50"/>
-      <c r="K81" s="50"/>
+      <c r="K81" s="50">
+        <v>80</v>
+      </c>
       <c r="L81" s="50"/>
       <c r="M81" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N81" s="39">
         <f t="shared" si="18"/>
@@ -8708,7 +8743,7 @@
       </c>
       <c r="Q81" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R81" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12129,10 +12164,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="187" t="s">
+      <c r="B132" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="188"/>
+      <c r="C132" s="175"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12396,10 +12431,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="175" t="s">
+      <c r="B136" s="187" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="176"/>
+      <c r="C136" s="188"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12490,10 +12525,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="164" t="s">
+      <c r="B137" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="165"/>
+      <c r="C137" s="177"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12544,11 +12579,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>1193.9000000000001</v>
+        <v>1213.9000000000001</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>3052</v>
+        <v>3102</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12585,17 +12620,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12695,24 +12730,24 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>817</v>
+        <v>841</v>
       </c>
       <c r="E5" s="79">
-        <v>1304</v>
+        <v>1393</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>2721</v>
+        <v>2834</v>
       </c>
       <c r="H5" s="99">
         <v>10000</v>
       </c>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>-7279</v>
+        <v>-7166</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12737,11 +12772,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>32680</v>
+        <v>33640</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>52160</v>
+        <v>55720</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12749,7 +12784,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>108840</v>
+        <v>113360</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12757,7 +12792,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>-291160</v>
+        <v>-286640</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12884,11 +12919,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-817</v>
+        <v>-841</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-1304</v>
+        <v>-1393</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -13028,7 +13063,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>6155</v>
+        <v>6268</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -13079,7 +13114,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>246200</v>
+        <v>250720</v>
       </c>
       <c r="S13" s="189" t="s">
         <v>152</v>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6174056-5273-48E2-8704-66166CDA153A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8210EB75-6ABC-4DFD-B9B4-0CA48E16C956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="213">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -662,6 +662,9 @@
   </si>
   <si>
     <t xml:space="preserve">Risen Shadbagh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Faisal Town </t>
   </si>
 </sst>
 </file>
@@ -1982,6 +1985,45 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2016,45 +2058,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2619,14 +2622,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="164">
+      <c r="B1" s="177">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
-      </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+        <v>46231</v>
+      </c>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2648,10 +2651,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="178" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2684,13 +2687,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="178"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="180"/>
-      <c r="P2" s="181" t="s">
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="182"/>
+      <c r="Q2" s="170"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2709,8 +2712,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="186"/>
-      <c r="B3" s="166"/>
+      <c r="A3" s="174"/>
+      <c r="B3" s="179"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2741,29 +2744,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="183" t="s">
+      <c r="M3" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="184"/>
-      <c r="O3" s="185"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="173"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="168" t="s">
+      <c r="R3" s="181" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="169"/>
-      <c r="T3" s="169"/>
-      <c r="U3" s="170"/>
-      <c r="V3" s="171" t="s">
+      <c r="S3" s="182"/>
+      <c r="T3" s="182"/>
+      <c r="U3" s="183"/>
+      <c r="V3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="173"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="186"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="186"/>
-      <c r="B4" s="167"/>
+      <c r="A4" s="174"/>
+      <c r="B4" s="180"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -8779,23 +8782,31 @@
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A82" s="78"/>
+      <c r="A82" s="78">
+        <v>27</v>
+      </c>
       <c r="B82" s="47">
         <v>78</v>
       </c>
-      <c r="C82" s="133"/>
+      <c r="C82" s="133" t="s">
+        <v>118</v>
+      </c>
       <c r="D82" s="50"/>
       <c r="E82" s="50"/>
       <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
+      <c r="G82" s="50">
+        <v>40</v>
+      </c>
       <c r="H82" s="50"/>
       <c r="I82" s="135"/>
       <c r="J82" s="50"/>
       <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
+      <c r="L82" s="50">
+        <v>40</v>
+      </c>
       <c r="M82" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N82" s="39">
         <f t="shared" si="18"/>
@@ -8807,11 +8818,11 @@
       </c>
       <c r="P82" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R82" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8847,23 +8858,37 @@
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A83" s="78"/>
+      <c r="A83" s="78">
+        <v>27</v>
+      </c>
       <c r="B83" s="47">
         <v>79</v>
       </c>
-      <c r="C83" s="133"/>
+      <c r="C83" s="133" t="s">
+        <v>171</v>
+      </c>
       <c r="D83" s="50"/>
       <c r="E83" s="50"/>
       <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="50"/>
+      <c r="G83" s="50">
+        <v>40</v>
+      </c>
+      <c r="H83" s="50">
+        <v>40</v>
+      </c>
       <c r="I83" s="135"/>
-      <c r="J83" s="50"/>
-      <c r="K83" s="50"/>
-      <c r="L83" s="50"/>
+      <c r="J83" s="50">
+        <v>37</v>
+      </c>
+      <c r="K83" s="50">
+        <v>40</v>
+      </c>
+      <c r="L83" s="50">
+        <v>79</v>
+      </c>
       <c r="M83" s="135">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="N83" s="39">
         <f t="shared" si="18"/>
@@ -8875,11 +8900,11 @@
       </c>
       <c r="P83" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q83" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R83" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8915,23 +8940,35 @@
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A84" s="78"/>
+      <c r="A84" s="78">
+        <v>27</v>
+      </c>
       <c r="B84" s="47">
         <v>80</v>
       </c>
-      <c r="C84" s="133"/>
+      <c r="C84" s="133" t="s">
+        <v>212</v>
+      </c>
       <c r="D84" s="50"/>
       <c r="E84" s="50"/>
       <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
+      <c r="G84" s="50">
+        <v>40</v>
+      </c>
       <c r="H84" s="50"/>
       <c r="I84" s="135"/>
-      <c r="J84" s="50"/>
-      <c r="K84" s="50"/>
-      <c r="L84" s="50"/>
+      <c r="J84" s="50">
+        <v>40</v>
+      </c>
+      <c r="K84" s="50">
+        <v>40</v>
+      </c>
+      <c r="L84" s="50">
+        <v>40</v>
+      </c>
       <c r="M84" s="135">
         <f t="shared" ref="M84:M131" si="96">SUM(D84:L84)/40</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N84" s="39">
         <f t="shared" si="18"/>
@@ -8943,11 +8980,11 @@
       </c>
       <c r="P84" s="73">
         <f t="shared" ref="P84:P131" si="97">SUM(G84:I84)/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="40">
         <f t="shared" ref="Q84:Q131" si="98">SUM(J84:L84)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R84" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12164,10 +12201,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="174" t="s">
+      <c r="B132" s="187" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="175"/>
+      <c r="C132" s="188"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12431,10 +12468,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="187" t="s">
+      <c r="B136" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="188"/>
+      <c r="C136" s="176"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12525,10 +12562,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="176" t="s">
+      <c r="B137" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="177"/>
+      <c r="C137" s="165"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12579,11 +12616,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>1213.9000000000001</v>
+        <v>1221.9000000000001</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>3102</v>
+        <v>3117.8</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12620,17 +12657,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8210EB75-6ABC-4DFD-B9B4-0CA48E16C956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B79105-161F-461B-A51E-3E2EE9BC11CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="214">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -665,6 +665,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rainbow Faisal Town </t>
+  </si>
+  <si>
+    <t>Rainbow Gujranwala</t>
   </si>
 </sst>
 </file>
@@ -2624,7 +2627,7 @@
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="177">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C1" s="177"/>
       <c r="D1" s="177"/>
@@ -9020,23 +9023,37 @@
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A85" s="78"/>
+      <c r="A85" s="78">
+        <v>28</v>
+      </c>
       <c r="B85" s="47">
         <v>81</v>
       </c>
-      <c r="C85" s="133"/>
+      <c r="C85" s="133" t="s">
+        <v>107</v>
+      </c>
       <c r="D85" s="50"/>
       <c r="E85" s="50"/>
       <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
-      <c r="H85" s="50"/>
+      <c r="G85" s="50">
+        <v>40</v>
+      </c>
+      <c r="H85" s="50">
+        <v>40</v>
+      </c>
       <c r="I85" s="135"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="50"/>
-      <c r="L85" s="50"/>
+      <c r="J85" s="50">
+        <v>40</v>
+      </c>
+      <c r="K85" s="50">
+        <v>200</v>
+      </c>
+      <c r="L85" s="50">
+        <v>120</v>
+      </c>
       <c r="M85" s="135">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N85" s="39">
         <f t="shared" si="18"/>
@@ -9048,11 +9065,11 @@
       </c>
       <c r="P85" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q85" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R85" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9088,23 +9105,35 @@
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A86" s="78"/>
+      <c r="A86" s="78">
+        <v>28</v>
+      </c>
       <c r="B86" s="47">
         <v>82</v>
       </c>
-      <c r="C86" s="133"/>
+      <c r="C86" s="133" t="s">
+        <v>213</v>
+      </c>
       <c r="D86" s="50"/>
       <c r="E86" s="50"/>
       <c r="F86" s="50"/>
       <c r="G86" s="50"/>
-      <c r="H86" s="50"/>
+      <c r="H86" s="50">
+        <v>40</v>
+      </c>
       <c r="I86" s="135"/>
-      <c r="J86" s="50"/>
-      <c r="K86" s="50"/>
-      <c r="L86" s="50"/>
+      <c r="J86" s="50">
+        <v>80</v>
+      </c>
+      <c r="K86" s="50">
+        <v>80</v>
+      </c>
+      <c r="L86" s="50">
+        <v>40</v>
+      </c>
       <c r="M86" s="135">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N86" s="39">
         <f t="shared" si="18"/>
@@ -9116,11 +9145,11 @@
       </c>
       <c r="P86" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q86" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R86" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9156,23 +9185,35 @@
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A87" s="78"/>
+      <c r="A87" s="78">
+        <v>28</v>
+      </c>
       <c r="B87" s="47">
         <v>83</v>
       </c>
-      <c r="C87" s="133"/>
+      <c r="C87" s="133" t="s">
+        <v>167</v>
+      </c>
       <c r="D87" s="50"/>
       <c r="E87" s="50"/>
       <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
-      <c r="H87" s="50"/>
+      <c r="G87" s="50">
+        <v>200</v>
+      </c>
+      <c r="H87" s="50">
+        <v>200</v>
+      </c>
       <c r="I87" s="135"/>
-      <c r="J87" s="50"/>
-      <c r="K87" s="50"/>
+      <c r="J87" s="50">
+        <v>120</v>
+      </c>
+      <c r="K87" s="50">
+        <v>40</v>
+      </c>
       <c r="L87" s="50"/>
       <c r="M87" s="135">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N87" s="39">
         <f t="shared" si="18"/>
@@ -9184,11 +9225,11 @@
       </c>
       <c r="P87" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q87" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R87" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9224,23 +9265,37 @@
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A88" s="78"/>
+      <c r="A88" s="78">
+        <v>28</v>
+      </c>
       <c r="B88" s="47">
         <v>84</v>
       </c>
-      <c r="C88" s="133"/>
+      <c r="C88" s="133" t="s">
+        <v>105</v>
+      </c>
       <c r="D88" s="50"/>
       <c r="E88" s="50"/>
       <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
-      <c r="H88" s="50"/>
+      <c r="G88" s="50">
+        <v>80</v>
+      </c>
+      <c r="H88" s="50">
+        <v>40</v>
+      </c>
       <c r="I88" s="135"/>
-      <c r="J88" s="50"/>
-      <c r="K88" s="50"/>
-      <c r="L88" s="50"/>
+      <c r="J88" s="50">
+        <v>240</v>
+      </c>
+      <c r="K88" s="50">
+        <v>240</v>
+      </c>
+      <c r="L88" s="50">
+        <v>320</v>
+      </c>
       <c r="M88" s="135">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N88" s="39">
         <f t="shared" si="18"/>
@@ -9252,11 +9307,11 @@
       </c>
       <c r="P88" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q88" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R88" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12616,11 +12671,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>1221.9000000000001</v>
+        <v>1253.9000000000001</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>3117.8</v>
+        <v>3193.8</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12767,24 +12822,24 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>841</v>
+        <v>908</v>
       </c>
       <c r="E5" s="79">
-        <v>1393</v>
+        <v>1459</v>
       </c>
       <c r="F5" s="79">
         <v>600</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>2834</v>
+        <v>2967</v>
       </c>
       <c r="H5" s="99">
         <v>10000</v>
       </c>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>-7166</v>
+        <v>-7033</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12809,11 +12864,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>33640</v>
+        <v>36320</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>55720</v>
+        <v>58360</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -12821,7 +12876,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>113360</v>
+        <v>118680</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12829,7 +12884,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>-286640</v>
+        <v>-281320</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -12956,11 +13011,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-841</v>
+        <v>-908</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-1393</v>
+        <v>-1459</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -13100,7 +13155,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>6268</v>
+        <v>6401</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -13151,7 +13206,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>250720</v>
+        <v>256040</v>
       </c>
       <c r="S13" s="189" t="s">
         <v>152</v>

--- a/july 2026/Daily Reports/LMT Orders.xlsx
+++ b/july 2026/Daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B79105-161F-461B-A51E-3E2EE9BC11CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518D7432-627C-49AF-9206-A632A5998CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="221">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -668,6 +668,27 @@
   </si>
   <si>
     <t>Rainbow Gujranwala</t>
+  </si>
+  <si>
+    <t>Hafiz Sweets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown </t>
+  </si>
+  <si>
+    <t>Euro Fateh Gher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Main Market </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Lake City </t>
+  </si>
+  <si>
+    <t>Risen Thoker Niaz Baig</t>
+  </si>
+  <si>
+    <t>Risen Al Rehman Garden</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1988,6 +2009,52 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2025,42 +2092,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2625,14 +2656,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="177">
+      <c r="B1" s="168">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
-      </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
+        <v>46235</v>
+      </c>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2654,10 +2685,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="190" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="178" t="s">
+      <c r="B2" s="169" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2690,13 +2721,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169" t="s">
+      <c r="M2" s="182"/>
+      <c r="N2" s="183"/>
+      <c r="O2" s="184"/>
+      <c r="P2" s="185" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="170"/>
+      <c r="Q2" s="186"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2715,8 +2746,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="174"/>
-      <c r="B3" s="179"/>
+      <c r="A3" s="190"/>
+      <c r="B3" s="170"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2747,29 +2778,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="171" t="s">
+      <c r="M3" s="187" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="172"/>
-      <c r="O3" s="173"/>
+      <c r="N3" s="188"/>
+      <c r="O3" s="189"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="181" t="s">
+      <c r="R3" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="182"/>
-      <c r="T3" s="182"/>
-      <c r="U3" s="183"/>
-      <c r="V3" s="184" t="s">
+      <c r="S3" s="173"/>
+      <c r="T3" s="173"/>
+      <c r="U3" s="174"/>
+      <c r="V3" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="185"/>
-      <c r="X3" s="185"/>
-      <c r="Y3" s="186"/>
+      <c r="W3" s="176"/>
+      <c r="X3" s="176"/>
+      <c r="Y3" s="177"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="174"/>
-      <c r="B4" s="180"/>
+      <c r="A4" s="190"/>
+      <c r="B4" s="171"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -9347,23 +9378,37 @@
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A89" s="78"/>
+      <c r="A89" s="78">
+        <v>29</v>
+      </c>
       <c r="B89" s="47">
         <v>85</v>
       </c>
-      <c r="C89" s="133"/>
+      <c r="C89" s="133" t="s">
+        <v>187</v>
+      </c>
       <c r="D89" s="50"/>
       <c r="E89" s="50"/>
       <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
-      <c r="H89" s="50"/>
+      <c r="G89" s="50">
+        <v>800</v>
+      </c>
+      <c r="H89" s="50">
+        <v>1200</v>
+      </c>
       <c r="I89" s="135"/>
-      <c r="J89" s="50"/>
-      <c r="K89" s="50"/>
-      <c r="L89" s="50"/>
+      <c r="J89" s="50">
+        <v>1600</v>
+      </c>
+      <c r="K89" s="50">
+        <v>2000</v>
+      </c>
+      <c r="L89" s="50">
+        <v>2000</v>
+      </c>
       <c r="M89" s="135">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="N89" s="39">
         <f t="shared" si="18"/>
@@ -9375,11 +9420,11 @@
       </c>
       <c r="P89" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q89" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="R89" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9415,23 +9460,39 @@
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A90" s="78"/>
-      <c r="B90" s="47">
+      <c r="A90" s="164">
+        <v>213</v>
+      </c>
+      <c r="B90" s="165">
         <v>86</v>
       </c>
-      <c r="C90" s="133"/>
-      <c r="D90" s="50"/>
-      <c r="E90" s="50"/>
-      <c r="F90" s="50"/>
-      <c r="G90" s="50"/>
-      <c r="H90" s="50"/>
-      <c r="I90" s="135"/>
-      <c r="J90" s="50"/>
-      <c r="K90" s="50"/>
-      <c r="L90" s="50"/>
-      <c r="M90" s="135">
+      <c r="C90" s="158" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" s="162">
+        <v>5600</v>
+      </c>
+      <c r="E90" s="162"/>
+      <c r="F90" s="162"/>
+      <c r="G90" s="162">
+        <v>600</v>
+      </c>
+      <c r="H90" s="162">
+        <v>600</v>
+      </c>
+      <c r="I90" s="166"/>
+      <c r="J90" s="162">
+        <v>800</v>
+      </c>
+      <c r="K90" s="162">
+        <v>1000</v>
+      </c>
+      <c r="L90" s="162">
+        <v>1000</v>
+      </c>
+      <c r="M90" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N90" s="39">
         <f t="shared" si="18"/>
@@ -9443,11 +9504,11 @@
       </c>
       <c r="P90" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q90" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="R90" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9483,23 +9544,37 @@
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A91" s="78"/>
-      <c r="B91" s="47">
+      <c r="A91" s="164">
+        <v>213</v>
+      </c>
+      <c r="B91" s="165">
         <v>87</v>
       </c>
-      <c r="C91" s="133"/>
-      <c r="D91" s="50"/>
-      <c r="E91" s="50"/>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50"/>
-      <c r="H91" s="50"/>
-      <c r="I91" s="135"/>
-      <c r="J91" s="50"/>
-      <c r="K91" s="50"/>
-      <c r="L91" s="50"/>
-      <c r="M91" s="135">
+      <c r="C91" s="158" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" s="162">
+        <v>4000</v>
+      </c>
+      <c r="E91" s="162"/>
+      <c r="F91" s="162"/>
+      <c r="G91" s="162"/>
+      <c r="H91" s="162"/>
+      <c r="I91" s="166">
+        <v>2000</v>
+      </c>
+      <c r="J91" s="162">
+        <v>2800</v>
+      </c>
+      <c r="K91" s="162">
+        <v>2400</v>
+      </c>
+      <c r="L91" s="162">
+        <v>2800</v>
+      </c>
+      <c r="M91" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="N91" s="39">
         <f t="shared" si="18"/>
@@ -9511,11 +9586,11 @@
       </c>
       <c r="P91" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q91" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="R91" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9551,23 +9626,39 @@
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A92" s="78"/>
-      <c r="B92" s="47">
+      <c r="A92" s="164">
+        <v>213</v>
+      </c>
+      <c r="B92" s="165">
         <v>88</v>
       </c>
-      <c r="C92" s="133"/>
-      <c r="D92" s="50"/>
-      <c r="E92" s="50"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="50"/>
-      <c r="H92" s="50"/>
-      <c r="I92" s="135"/>
-      <c r="J92" s="50"/>
-      <c r="K92" s="50"/>
-      <c r="L92" s="50"/>
-      <c r="M92" s="135">
+      <c r="C92" s="158" t="s">
+        <v>25</v>
+      </c>
+      <c r="D92" s="162"/>
+      <c r="E92" s="162"/>
+      <c r="F92" s="162"/>
+      <c r="G92" s="162">
+        <v>200</v>
+      </c>
+      <c r="H92" s="162">
+        <v>160</v>
+      </c>
+      <c r="I92" s="166">
+        <v>160</v>
+      </c>
+      <c r="J92" s="162">
+        <v>360</v>
+      </c>
+      <c r="K92" s="162">
+        <v>280</v>
+      </c>
+      <c r="L92" s="162">
+        <v>600</v>
+      </c>
+      <c r="M92" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N92" s="39">
         <f t="shared" si="18"/>
@@ -9579,11 +9670,11 @@
       </c>
       <c r="P92" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q92" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R92" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9619,23 +9710,35 @@
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A93" s="78"/>
-      <c r="B93" s="47">
+      <c r="A93" s="164">
+        <v>213</v>
+      </c>
+      <c r="B93" s="165">
         <v>89</v>
       </c>
-      <c r="C93" s="133"/>
-      <c r="D93" s="50"/>
-      <c r="E93" s="50"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
-      <c r="H93" s="50"/>
-      <c r="I93" s="135"/>
-      <c r="J93" s="50"/>
-      <c r="K93" s="50"/>
-      <c r="L93" s="50"/>
-      <c r="M93" s="135">
+      <c r="C93" s="158" t="s">
+        <v>215</v>
+      </c>
+      <c r="D93" s="162"/>
+      <c r="E93" s="162"/>
+      <c r="F93" s="162"/>
+      <c r="G93" s="162">
+        <v>40</v>
+      </c>
+      <c r="H93" s="162"/>
+      <c r="I93" s="166">
+        <v>40</v>
+      </c>
+      <c r="J93" s="162">
+        <v>80</v>
+      </c>
+      <c r="K93" s="162"/>
+      <c r="L93" s="162">
+        <v>80</v>
+      </c>
+      <c r="M93" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N93" s="39">
         <f t="shared" si="18"/>
@@ -9647,11 +9750,11 @@
       </c>
       <c r="P93" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q93" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R93" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9687,23 +9790,41 @@
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A94" s="78"/>
-      <c r="B94" s="47">
+      <c r="A94" s="164">
+        <v>213</v>
+      </c>
+      <c r="B94" s="165">
         <v>90</v>
       </c>
-      <c r="C94" s="133"/>
-      <c r="D94" s="50"/>
-      <c r="E94" s="50"/>
-      <c r="F94" s="50"/>
-      <c r="G94" s="50"/>
-      <c r="H94" s="50"/>
-      <c r="I94" s="135"/>
-      <c r="J94" s="50"/>
-      <c r="K94" s="50"/>
-      <c r="L94" s="50"/>
-      <c r="M94" s="135">
+      <c r="C94" s="158" t="s">
+        <v>216</v>
+      </c>
+      <c r="D94" s="162">
+        <v>160</v>
+      </c>
+      <c r="E94" s="162"/>
+      <c r="F94" s="162"/>
+      <c r="G94" s="162">
+        <v>160</v>
+      </c>
+      <c r="H94" s="162">
+        <v>160</v>
+      </c>
+      <c r="I94" s="166">
+        <v>160</v>
+      </c>
+      <c r="J94" s="162">
+        <v>160</v>
+      </c>
+      <c r="K94" s="162">
+        <v>160</v>
+      </c>
+      <c r="L94" s="162">
+        <v>160</v>
+      </c>
+      <c r="M94" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N94" s="39">
         <f t="shared" si="18"/>
@@ -9715,11 +9836,11 @@
       </c>
       <c r="P94" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q94" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R94" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9755,23 +9876,37 @@
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A95" s="78"/>
-      <c r="B95" s="47">
+      <c r="A95" s="164">
+        <v>213</v>
+      </c>
+      <c r="B95" s="165">
         <v>91</v>
       </c>
-      <c r="C95" s="133"/>
-      <c r="D95" s="50"/>
-      <c r="E95" s="50"/>
-      <c r="F95" s="50"/>
-      <c r="G95" s="50"/>
-      <c r="H95" s="50"/>
-      <c r="I95" s="135"/>
-      <c r="J95" s="50"/>
-      <c r="K95" s="50"/>
-      <c r="L95" s="50"/>
-      <c r="M95" s="135">
+      <c r="C95" s="158" t="s">
+        <v>217</v>
+      </c>
+      <c r="D95" s="162"/>
+      <c r="E95" s="162"/>
+      <c r="F95" s="162"/>
+      <c r="G95" s="162"/>
+      <c r="H95" s="162">
+        <v>80</v>
+      </c>
+      <c r="I95" s="166">
+        <v>120</v>
+      </c>
+      <c r="J95" s="162">
+        <v>40</v>
+      </c>
+      <c r="K95" s="162">
+        <v>80</v>
+      </c>
+      <c r="L95" s="162">
+        <v>40</v>
+      </c>
+      <c r="M95" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N95" s="39">
         <f t="shared" si="18"/>
@@ -9783,11 +9918,11 @@
       </c>
       <c r="P95" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q95" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R95" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9823,23 +9958,39 @@
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A96" s="78"/>
-      <c r="B96" s="47">
+      <c r="A96" s="164">
+        <v>213</v>
+      </c>
+      <c r="B96" s="165">
         <v>92</v>
       </c>
-      <c r="C96" s="133"/>
-      <c r="D96" s="50"/>
-      <c r="E96" s="50"/>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50"/>
-      <c r="H96" s="50"/>
-      <c r="I96" s="135"/>
-      <c r="J96" s="50"/>
-      <c r="K96" s="50"/>
-      <c r="L96" s="50"/>
-      <c r="M96" s="135">
+      <c r="C96" s="158" t="s">
+        <v>127</v>
+      </c>
+      <c r="D96" s="162"/>
+      <c r="E96" s="162"/>
+      <c r="F96" s="162"/>
+      <c r="G96" s="162">
+        <v>40</v>
+      </c>
+      <c r="H96" s="162">
+        <v>40</v>
+      </c>
+      <c r="I96" s="166">
+        <v>40</v>
+      </c>
+      <c r="J96" s="162">
+        <v>40</v>
+      </c>
+      <c r="K96" s="162">
+        <v>40</v>
+      </c>
+      <c r="L96" s="162">
+        <v>40</v>
+      </c>
+      <c r="M96" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N96" s="39">
         <f t="shared" si="18"/>
@@ -9851,11 +10002,11 @@
       </c>
       <c r="P96" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q96" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R96" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9891,23 +10042,37 @@
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
-      <c r="B97" s="47">
+      <c r="A97" s="164">
+        <v>213</v>
+      </c>
+      <c r="B97" s="165">
         <v>93</v>
       </c>
-      <c r="C97" s="133"/>
-      <c r="D97" s="50"/>
-      <c r="E97" s="50"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
-      <c r="H97" s="50"/>
-      <c r="I97" s="135"/>
-      <c r="J97" s="50"/>
-      <c r="K97" s="50"/>
-      <c r="L97" s="50"/>
-      <c r="M97" s="135">
+      <c r="C97" s="158" t="s">
+        <v>218</v>
+      </c>
+      <c r="D97" s="162"/>
+      <c r="E97" s="162"/>
+      <c r="F97" s="162"/>
+      <c r="G97" s="162"/>
+      <c r="H97" s="162">
+        <v>38</v>
+      </c>
+      <c r="I97" s="166">
+        <v>80</v>
+      </c>
+      <c r="J97" s="162">
+        <v>40</v>
+      </c>
+      <c r="K97" s="162">
+        <v>77</v>
+      </c>
+      <c r="L97" s="162">
+        <v>79</v>
+      </c>
+      <c r="M97" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="N97" s="39">
         <f t="shared" si="18"/>
@@ -9919,11 +10084,11 @@
       </c>
       <c r="P97" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q97" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="R97" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9959,23 +10124,31 @@
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A98" s="78"/>
-      <c r="B98" s="47">
+      <c r="A98" s="164">
+        <v>213</v>
+      </c>
+      <c r="B98" s="165">
         <v>94</v>
       </c>
-      <c r="C98" s="133"/>
-      <c r="D98" s="50"/>
-      <c r="E98" s="50"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="50"/>
-      <c r="H98" s="50"/>
-      <c r="I98" s="135"/>
-      <c r="J98" s="50"/>
-      <c r="K98" s="50"/>
-      <c r="L98" s="50"/>
-      <c r="M98" s="135">
+      <c r="C98" s="158" t="s">
+        <v>190</v>
+      </c>
+      <c r="D98" s="162"/>
+      <c r="E98" s="162"/>
+      <c r="F98" s="162"/>
+      <c r="G98" s="162"/>
+      <c r="H98" s="162"/>
+      <c r="I98" s="166">
+        <v>80</v>
+      </c>
+      <c r="J98" s="162">
+        <v>40</v>
+      </c>
+      <c r="K98" s="162"/>
+      <c r="L98" s="162"/>
+      <c r="M98" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N98" s="39">
         <f t="shared" si="18"/>
@@ -9987,11 +10160,11 @@
       </c>
       <c r="P98" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q98" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R98" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10027,23 +10200,39 @@
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A99" s="78"/>
-      <c r="B99" s="47">
+      <c r="A99" s="164">
+        <v>213</v>
+      </c>
+      <c r="B99" s="165">
         <v>95</v>
       </c>
-      <c r="C99" s="133"/>
-      <c r="D99" s="50"/>
-      <c r="E99" s="50"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
-      <c r="H99" s="50"/>
-      <c r="I99" s="135"/>
-      <c r="J99" s="50"/>
-      <c r="K99" s="50"/>
-      <c r="L99" s="50"/>
-      <c r="M99" s="135">
+      <c r="C99" s="158" t="s">
+        <v>219</v>
+      </c>
+      <c r="D99" s="162"/>
+      <c r="E99" s="162"/>
+      <c r="F99" s="162"/>
+      <c r="G99" s="162">
+        <v>40</v>
+      </c>
+      <c r="H99" s="162">
+        <v>40</v>
+      </c>
+      <c r="I99" s="166">
+        <v>80</v>
+      </c>
+      <c r="J99" s="162">
+        <v>40</v>
+      </c>
+      <c r="K99" s="162">
+        <v>40</v>
+      </c>
+      <c r="L99" s="162">
+        <v>80</v>
+      </c>
+      <c r="M99" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N99" s="39">
         <f t="shared" si="18"/>
@@ -10055,11 +10244,11 @@
       </c>
       <c r="P99" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q99" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R99" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10095,23 +10284,33 @@
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A100" s="78"/>
-      <c r="B100" s="47">
+      <c r="A100" s="164">
+        <v>213</v>
+      </c>
+      <c r="B100" s="165">
         <v>96</v>
       </c>
-      <c r="C100" s="133"/>
-      <c r="D100" s="50"/>
-      <c r="E100" s="50"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
-      <c r="H100" s="50"/>
-      <c r="I100" s="135"/>
-      <c r="J100" s="50"/>
-      <c r="K100" s="50"/>
-      <c r="L100" s="50"/>
-      <c r="M100" s="135">
+      <c r="C100" s="158" t="s">
+        <v>211</v>
+      </c>
+      <c r="D100" s="162"/>
+      <c r="E100" s="162"/>
+      <c r="F100" s="162"/>
+      <c r="G100" s="162"/>
+      <c r="H100" s="162"/>
+      <c r="I100" s="166"/>
+      <c r="J100" s="162">
+        <v>120</v>
+      </c>
+      <c r="K100" s="162">
+        <v>120</v>
+      </c>
+      <c r="L100" s="162">
+        <v>120</v>
+      </c>
+      <c r="M100" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N100" s="39">
         <f t="shared" si="18"/>
@@ -10127,7 +10326,7 @@
       </c>
       <c r="Q100" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R100" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10163,23 +10362,33 @@
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A101" s="78"/>
-      <c r="B101" s="47">
+      <c r="A101" s="164">
+        <v>213</v>
+      </c>
+      <c r="B101" s="165">
         <v>97</v>
       </c>
-      <c r="C101" s="133"/>
-      <c r="D101" s="50"/>
-      <c r="E101" s="50"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
-      <c r="H101" s="50"/>
-      <c r="I101" s="135"/>
-      <c r="J101" s="50"/>
-      <c r="K101" s="50"/>
-      <c r="L101" s="50"/>
-      <c r="M101" s="135">
+      <c r="C101" s="158" t="s">
+        <v>220</v>
+      </c>
+      <c r="D101" s="162"/>
+      <c r="E101" s="162"/>
+      <c r="F101" s="162"/>
+      <c r="G101" s="162"/>
+      <c r="H101" s="162"/>
+      <c r="I101" s="166">
+        <v>200</v>
+      </c>
+      <c r="J101" s="162">
+        <v>120</v>
+      </c>
+      <c r="K101" s="162">
+        <v>40</v>
+      </c>
+      <c r="L101" s="162"/>
+      <c r="M101" s="167">
         <f t="shared" si="96"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N101" s="39">
         <f t="shared" si="18"/>
@@ -10191,11 +10400,11 @@
       </c>
       <c r="P101" s="73">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q101" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R101" s="51" t="e">
         <f t="shared" si="4"/>
@@ -12256,10 +12465,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="187" t="s">
+      <c r="B132" s="178" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="188"/>
+      <c r="C132" s="179"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>2440</v>
@@ -12523,10 +12732,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="175" t="s">
+      <c r="B136" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="176"/>
+      <c r="C136" s="192"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -12617,10 +12826,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="164" t="s">
+      <c r="B137" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="165"/>
+      <c r="C137" s="181"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>2440</v>
@@ -12671,11 +12880,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>1253.9000000000001</v>
+        <v>1611.8000000000002</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>3193.8</v>
+        <v>4167.6000000000004</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -12712,17 +12921,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12758,25 +12967,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="191" t="s">
+      <c r="C3" s="195" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
-      <c r="G3" s="193"/>
-      <c r="H3" s="195" t="s">
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="199" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="196"/>
-      <c r="K3" s="197" t="s">
+      <c r="I3" s="200"/>
+      <c r="K3" s="201" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="197"/>
-      <c r="M3" s="197"/>
-      <c r="N3" s="197"/>
-      <c r="O3" s="197"/>
-      <c r="P3" s="197"/>
+      <c r="L3" s="201"/>
+      <c r="M3" s="201"/>
+      <c r="N3" s="201"/>
+      <c r="O3" s="201"/>
+      <c r="P3" s="201"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -12822,24 +13031,24 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>908</v>
+        <v>989</v>
       </c>
       <c r="E5" s="79">
-        <v>1459</v>
+        <v>2261</v>
       </c>
       <c r="F5" s="79">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>2967</v>
+        <v>4200</v>
       </c>
       <c r="H5" s="99">
         <v>10000</v>
       </c>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>-7033</v>
+        <v>-5800</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -12864,19 +13073,19 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>36320</v>
+        <v>39560</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>58360</v>
+        <v>90440</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
-        <v>24000</v>
+        <v>38000</v>
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>118680</v>
+        <v>168000</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -12884,7 +13093,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>-281320</v>
+        <v>-232000</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -13011,11 +13220,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-908</v>
+        <v>-989</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-1459</v>
+        <v>-2261</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -13099,14 +13308,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="194" t="s">
+      <c r="C11" s="198" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="194"/>
-      <c r="F11" s="194" t="s">
+      <c r="D11" s="198"/>
+      <c r="F11" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="194"/>
+      <c r="G11" s="198"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -13155,7 +13364,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>6401</v>
+        <v>7634</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -13206,12 +13415,12 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>256040</v>
-      </c>
-      <c r="S13" s="189" t="s">
+        <v>305360</v>
+      </c>
+      <c r="S13" s="193" t="s">
         <v>152</v>
       </c>
-      <c r="T13" s="189"/>
+      <c r="T13" s="193"/>
       <c r="U13" s="141">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13327,13 +13536,13 @@
       </c>
     </row>
     <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="190" t="s">
+      <c r="D20" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="190"/>
-      <c r="F20" s="190"/>
-      <c r="G20" s="190"/>
-      <c r="H20" s="190"/>
+      <c r="E20" s="194"/>
+      <c r="F20" s="194"/>
+      <c r="G20" s="194"/>
+      <c r="H20" s="194"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
